--- a/Results/Phase 2/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
@@ -886,7 +886,7 @@
         <v>36.03117426429043</v>
       </c>
       <c r="N5" t="n">
-        <v>372.2804942320394</v>
+        <v>36.03117426429048</v>
       </c>
       <c r="O5" t="n">
         <v>36.03117426429048</v>
@@ -974,7 +974,7 @@
         <v>233.9339774453795</v>
       </c>
       <c r="N6" t="n">
-        <v>372.2804942320394</v>
+        <v>149.6560677477016</v>
       </c>
       <c r="O6" t="n">
         <v>149.6560965414554</v>
@@ -1062,7 +1062,7 @@
         <v>65.25031317851796</v>
       </c>
       <c r="N7" t="n">
-        <v>372.2804942320394</v>
+        <v>65.25031317851796</v>
       </c>
       <c r="O7" t="n">
         <v>65.24974031452194</v>
@@ -1150,7 +1150,7 @@
         <v>217.9062083460311</v>
       </c>
       <c r="N8" t="n">
-        <v>372.2804942320394</v>
+        <v>161.7265442759345</v>
       </c>
       <c r="O8" t="n">
         <v>177.165203764661</v>
@@ -1238,7 +1238,7 @@
         <v>180.5696019762792</v>
       </c>
       <c r="N9" t="n">
-        <v>372.2804942320394</v>
+        <v>180.5696019762792</v>
       </c>
       <c r="O9" t="n">
         <v>191.2814138222665</v>
@@ -1922,7 +1922,7 @@
         <v>33.20000377062532</v>
       </c>
       <c r="N5" t="n">
-        <v>196.3720176340112</v>
+        <v>33.20000377062531</v>
       </c>
       <c r="O5" t="n">
         <v>33.20000377062531</v>
@@ -2010,7 +2010,7 @@
         <v>131.5935296908576</v>
       </c>
       <c r="N6" t="n">
-        <v>196.3720176340112</v>
+        <v>131.6343269226511</v>
       </c>
       <c r="O6" t="n">
         <v>198.7029384254844</v>
@@ -2098,7 +2098,7 @@
         <v>55.58189174603514</v>
       </c>
       <c r="N7" t="n">
-        <v>196.3720176340112</v>
+        <v>55.58189174603514</v>
       </c>
       <c r="O7" t="n">
         <v>55.58142864078161</v>
@@ -2186,7 +2186,7 @@
         <v>181.629643139773</v>
       </c>
       <c r="N8" t="n">
-        <v>196.3720176340112</v>
+        <v>136.0405371577702</v>
       </c>
       <c r="O8" t="n">
         <v>148.5688193280012</v>
@@ -2274,7 +2274,7 @@
         <v>118.2000505788256</v>
       </c>
       <c r="N9" t="n">
-        <v>196.3720176340112</v>
+        <v>118.2000505788256</v>
       </c>
       <c r="O9" t="n">
         <v>124.5139046517715</v>
@@ -2958,7 +2958,7 @@
         <v>35.34996068932326</v>
       </c>
       <c r="N5" t="n">
-        <v>323.4482662573186</v>
+        <v>35.34996068932323</v>
       </c>
       <c r="O5" t="n">
         <v>35.34996068932323</v>
@@ -3046,7 +3046,7 @@
         <v>220.0449825624596</v>
       </c>
       <c r="N6" t="n">
-        <v>323.4482662573186</v>
+        <v>141.4457494953691</v>
       </c>
       <c r="O6" t="n">
         <v>141.4469461365568</v>
@@ -3134,7 +3134,7 @@
         <v>62.34250143646324</v>
       </c>
       <c r="N7" t="n">
-        <v>323.4482662573186</v>
+        <v>62.34250143646324</v>
       </c>
       <c r="O7" t="n">
         <v>62.3419718052467</v>
@@ -3222,7 +3222,7 @@
         <v>204.7195346526039</v>
       </c>
       <c r="N8" t="n">
-        <v>323.4482662573186</v>
+        <v>152.4245911789441</v>
       </c>
       <c r="O8" t="n">
         <v>166.7956957171676</v>
@@ -3310,7 +3310,7 @@
         <v>158.6449663668477</v>
       </c>
       <c r="N9" t="n">
-        <v>323.4482662573186</v>
+        <v>158.6449663668477</v>
       </c>
       <c r="O9" t="n">
         <v>167.8033804147106</v>
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.79176685787203</v>
+        <v>89.79176685787199</v>
       </c>
       <c r="C2" t="n">
-        <v>88.86526563166692</v>
+        <v>88.86526563166694</v>
       </c>
       <c r="D2" t="n">
-        <v>90.1765386785162</v>
+        <v>90.17653867851621</v>
       </c>
       <c r="E2" t="n">
-        <v>35.78184945075695</v>
+        <v>35.78184945075692</v>
       </c>
       <c r="F2" t="n">
         <v>90.07708145921988</v>
       </c>
       <c r="G2" t="n">
-        <v>93.12135519719892</v>
+        <v>93.12135519719888</v>
       </c>
       <c r="H2" t="n">
         <v>88.94584718926359</v>
       </c>
       <c r="I2" t="n">
-        <v>89.70156231591019</v>
+        <v>89.70156231591017</v>
       </c>
       <c r="J2" t="n">
-        <v>91.2390089929989</v>
+        <v>91.23900899299886</v>
       </c>
       <c r="K2" t="n">
-        <v>89.79705095819884</v>
+        <v>89.79705095819887</v>
       </c>
       <c r="L2" t="n">
-        <v>89.28417081161579</v>
+        <v>89.28417081161578</v>
       </c>
       <c r="M2" t="n">
-        <v>94.45237684049742</v>
+        <v>94.45237684049738</v>
       </c>
       <c r="N2" t="n">
         <v>89.30581621544404</v>
       </c>
       <c r="O2" t="n">
-        <v>89.95343899269106</v>
+        <v>89.95343899269105</v>
       </c>
       <c r="P2" t="n">
         <v>91.0526405482008</v>
       </c>
       <c r="Q2" t="n">
-        <v>89.43088016651289</v>
+        <v>89.43088016651294</v>
       </c>
       <c r="R2" t="n">
-        <v>88.97148561338025</v>
+        <v>88.97148561338028</v>
       </c>
       <c r="S2" t="n">
-        <v>90.20216620557882</v>
+        <v>90.20216620557878</v>
       </c>
       <c r="T2" t="n">
-        <v>89.27302178112174</v>
+        <v>89.2730217811217</v>
       </c>
       <c r="U2" t="n">
-        <v>89.67286331762088</v>
+        <v>89.67286331762091</v>
       </c>
       <c r="V2" t="n">
-        <v>55.57657922116934</v>
+        <v>55.57657922116941</v>
       </c>
       <c r="W2" t="n">
-        <v>90.03671867527936</v>
+        <v>90.03671867527933</v>
       </c>
       <c r="X2" t="n">
-        <v>90.1589340695035</v>
+        <v>90.15893406950356</v>
       </c>
       <c r="Y2" t="n">
-        <v>91.43808493143099</v>
+        <v>91.43808493143104</v>
       </c>
       <c r="Z2" t="n">
-        <v>90.03259622952565</v>
+        <v>90.03259622952571</v>
       </c>
       <c r="AA2" t="n">
-        <v>89.51005540883443</v>
+        <v>89.51005540883445</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.01511286759063</v>
+        <v>95.01511286759066</v>
       </c>
     </row>
     <row r="3">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.37403602161814</v>
+        <v>89.37403602161811</v>
       </c>
       <c r="C3" t="n">
-        <v>89.37403215241251</v>
+        <v>89.37403215241247</v>
       </c>
       <c r="D3" t="n">
-        <v>89.37403602161814</v>
+        <v>89.37403602161811</v>
       </c>
       <c r="E3" t="n">
-        <v>35.37790436536103</v>
+        <v>35.377904365361</v>
       </c>
       <c r="F3" t="n">
-        <v>89.37403408209322</v>
+        <v>89.37403408209317</v>
       </c>
       <c r="G3" t="n">
-        <v>89.37403522791874</v>
+        <v>89.37403522791871</v>
       </c>
       <c r="H3" t="n">
-        <v>89.37403602161814</v>
+        <v>89.37403602161811</v>
       </c>
       <c r="I3" t="n">
-        <v>89.37403602161814</v>
+        <v>89.37403602161811</v>
       </c>
       <c r="J3" t="n">
-        <v>89.24043671146414</v>
+        <v>89.24043671146413</v>
       </c>
       <c r="K3" t="n">
-        <v>89.37403487518426</v>
+        <v>89.37403487518422</v>
       </c>
       <c r="L3" t="n">
-        <v>89.37403602161814</v>
+        <v>89.37403602161811</v>
       </c>
       <c r="M3" t="n">
-        <v>89.374033447716</v>
+        <v>89.37403344771596</v>
       </c>
       <c r="N3" t="n">
-        <v>89.37403602161814</v>
+        <v>89.37403602161811</v>
       </c>
       <c r="O3" t="n">
-        <v>89.37403305924197</v>
+        <v>89.37403305924194</v>
       </c>
       <c r="P3" t="n">
-        <v>89.3740356866377</v>
+        <v>89.37403568663765</v>
       </c>
       <c r="Q3" t="n">
-        <v>89.37403598397444</v>
+        <v>89.37403598397439</v>
       </c>
       <c r="R3" t="n">
-        <v>89.37404031576087</v>
+        <v>89.37404031576084</v>
       </c>
       <c r="S3" t="n">
-        <v>89.37403602161814</v>
+        <v>89.37403602161811</v>
       </c>
       <c r="T3" t="n">
-        <v>89.37403262333351</v>
+        <v>89.37403262333348</v>
       </c>
       <c r="U3" t="n">
-        <v>89.37404009489804</v>
+        <v>89.37404009489801</v>
       </c>
       <c r="V3" t="n">
         <v>54.7838621347782</v>
       </c>
       <c r="W3" t="n">
-        <v>89.37403602161814</v>
+        <v>89.37403602161811</v>
       </c>
       <c r="X3" t="n">
-        <v>89.37406185306811</v>
+        <v>89.37406185306807</v>
       </c>
       <c r="Y3" t="n">
-        <v>89.37402870036443</v>
+        <v>89.37402870036439</v>
       </c>
       <c r="Z3" t="n">
-        <v>89.37403567599202</v>
+        <v>89.37403567599199</v>
       </c>
       <c r="AA3" t="n">
-        <v>89.37403602161814</v>
+        <v>89.37403602161811</v>
       </c>
       <c r="AB3" t="n">
-        <v>89.37407525756234</v>
+        <v>89.37407525756231</v>
       </c>
     </row>
     <row r="4">
@@ -3870,85 +3870,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>362.1148161128713</v>
+        <v>362.1148161128722</v>
       </c>
       <c r="C4" t="n">
-        <v>155.8653086161103</v>
+        <v>155.86530861611</v>
       </c>
       <c r="D4" t="n">
-        <v>494.2303785584398</v>
+        <v>494.2303785584405</v>
       </c>
       <c r="E4" t="n">
-        <v>128.1708057931058</v>
+        <v>128.1708057931051</v>
       </c>
       <c r="F4" t="n">
-        <v>468.7939705715476</v>
+        <v>468.7939705715474</v>
       </c>
       <c r="G4" t="n">
-        <v>1144.865539654936</v>
+        <v>1144.865539654938</v>
       </c>
       <c r="H4" t="n">
-        <v>176.2326126181454</v>
+        <v>176.2326126181445</v>
       </c>
       <c r="I4" t="n">
-        <v>373.7098601593136</v>
+        <v>373.7098601593128</v>
       </c>
       <c r="J4" t="n">
-        <v>760.0093793831422</v>
+        <v>760.0093793831425</v>
       </c>
       <c r="K4" t="n">
-        <v>377.1408757589593</v>
+        <v>377.1408757589594</v>
       </c>
       <c r="L4" t="n">
-        <v>249.3637225992292</v>
+        <v>249.3637225992221</v>
       </c>
       <c r="M4" t="n">
-        <v>1642.486731141414</v>
+        <v>1642.486731141408</v>
       </c>
       <c r="N4" t="n">
         <v>260.6078274636787</v>
       </c>
       <c r="O4" t="n">
-        <v>390.584109693405</v>
+        <v>390.5841096934057</v>
       </c>
       <c r="P4" t="n">
-        <v>656.6656191303459</v>
+        <v>656.6656191303455</v>
       </c>
       <c r="Q4" t="n">
-        <v>291.5957043766222</v>
+        <v>291.5957043766215</v>
       </c>
       <c r="R4" t="n">
-        <v>180.0267356212372</v>
+        <v>180.0267356212371</v>
       </c>
       <c r="S4" t="n">
-        <v>461.4313836276175</v>
+        <v>461.4313836276157</v>
       </c>
       <c r="T4" t="n">
-        <v>257.8381984496572</v>
+        <v>257.8381984496579</v>
       </c>
       <c r="U4" t="n">
-        <v>342.5821826281951</v>
+        <v>342.5821826282106</v>
       </c>
       <c r="V4" t="n">
-        <v>321.5355785047281</v>
+        <v>321.5355785047305</v>
       </c>
       <c r="W4" t="n">
-        <v>442.1940281056643</v>
+        <v>442.1940281056636</v>
       </c>
       <c r="X4" t="n">
-        <v>484.2317630174099</v>
+        <v>484.2317630174118</v>
       </c>
       <c r="Y4" t="n">
         <v>793.5578707742075</v>
       </c>
       <c r="Z4" t="n">
-        <v>407.3302477907168</v>
+        <v>407.3302477907157</v>
       </c>
       <c r="AA4" t="n">
-        <v>309.4795398853603</v>
+        <v>309.4795398853591</v>
       </c>
       <c r="AB4" t="n">
-        <v>1872.260279518296</v>
+        <v>1872.260279518294</v>
       </c>
     </row>
     <row r="5">
@@ -3958,85 +3958,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.07620429110349</v>
+        <v>35.07620429110343</v>
       </c>
       <c r="C5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="D5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="E5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="F5" t="n">
-        <v>35.0762042911035</v>
+        <v>35.07620429110341</v>
       </c>
       <c r="G5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="H5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="I5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="J5" t="n">
-        <v>34.89654318608413</v>
+        <v>34.89654318608402</v>
       </c>
       <c r="K5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="L5" t="n">
-        <v>35.07620429110353</v>
+        <v>35.07620429110338</v>
       </c>
       <c r="M5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="N5" t="n">
-        <v>260.6078274636787</v>
+        <v>35.07620429110341</v>
       </c>
       <c r="O5" t="n">
-        <v>35.0762042911035</v>
+        <v>35.07620429110341</v>
       </c>
       <c r="P5" t="n">
-        <v>35.0762042911035</v>
+        <v>35.07620429110341</v>
       </c>
       <c r="Q5" t="n">
-        <v>35.0762042911035</v>
+        <v>35.07620429110341</v>
       </c>
       <c r="R5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="S5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="T5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="U5" t="n">
-        <v>34.28821665296609</v>
+        <v>34.28821665296601</v>
       </c>
       <c r="V5" t="n">
-        <v>33.9355145526881</v>
+        <v>33.93551455268808</v>
       </c>
       <c r="W5" t="n">
-        <v>35.0762042911035</v>
+        <v>35.07620429110341</v>
       </c>
       <c r="X5" t="n">
-        <v>35.07620429110349</v>
+        <v>35.07620429110343</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.28821665296609</v>
+        <v>34.28821665296601</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="AA5" t="n">
-        <v>35.07620429110352</v>
+        <v>35.07620429110337</v>
       </c>
       <c r="AB5" t="n">
-        <v>35.0762042911035</v>
+        <v>35.07620429110341</v>
       </c>
     </row>
     <row r="6">
@@ -4046,85 +4046,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207.0329647127557</v>
+        <v>207.0329647127556</v>
       </c>
       <c r="C6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="D6" t="n">
-        <v>207.0329647127557</v>
+        <v>207.0329647127555</v>
       </c>
       <c r="E6" t="n">
-        <v>207.0329647127557</v>
+        <v>207.0329647127555</v>
       </c>
       <c r="F6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="G6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="H6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="I6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="J6" t="n">
         <v>206.8533036077361</v>
       </c>
       <c r="K6" t="n">
-        <v>207.0329647127557</v>
+        <v>207.0329647127555</v>
       </c>
       <c r="L6" t="n">
-        <v>207.0329647127557</v>
+        <v>207.0329647127556</v>
       </c>
       <c r="M6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="N6" t="n">
-        <v>260.6078274636787</v>
+        <v>134.0828162064553</v>
       </c>
       <c r="O6" t="n">
-        <v>205.2195597994179</v>
+        <v>205.2195597994177</v>
       </c>
       <c r="P6" t="n">
-        <v>205.2200959470824</v>
+        <v>205.2200959470822</v>
       </c>
       <c r="Q6" t="n">
-        <v>207.0329647127557</v>
+        <v>207.0329647127555</v>
       </c>
       <c r="R6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="S6" t="n">
-        <v>207.0329647127557</v>
+        <v>207.0329647127555</v>
       </c>
       <c r="T6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="U6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="V6" t="n">
-        <v>205.89227497434</v>
+        <v>205.8922749743399</v>
       </c>
       <c r="W6" t="n">
-        <v>205.2193322500515</v>
+        <v>205.2193322500513</v>
       </c>
       <c r="X6" t="n">
-        <v>134.0212313287855</v>
+        <v>134.0212313287851</v>
       </c>
       <c r="Y6" t="n">
-        <v>138.4836573405243</v>
+        <v>138.4836573405246</v>
       </c>
       <c r="Z6" t="n">
-        <v>207.0329647127557</v>
+        <v>207.0329647127555</v>
       </c>
       <c r="AA6" t="n">
-        <v>207.0329647127557</v>
+        <v>207.0329647127555</v>
       </c>
       <c r="AB6" t="n">
-        <v>134.5278727916477</v>
+        <v>134.5278727916476</v>
       </c>
     </row>
     <row r="7">
@@ -4134,85 +4134,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.84847481445293</v>
+        <v>59.84847481445292</v>
       </c>
       <c r="C7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="D7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="E7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="F7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="G7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="H7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="I7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="J7" t="n">
-        <v>59.66881370943363</v>
+        <v>59.66881370943348</v>
       </c>
       <c r="K7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="L7" t="n">
-        <v>59.84847481445293</v>
+        <v>59.84847481445292</v>
       </c>
       <c r="M7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="N7" t="n">
-        <v>260.6078274636787</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="O7" t="n">
-        <v>59.8479816471597</v>
+        <v>59.84798164715961</v>
       </c>
       <c r="P7" t="n">
-        <v>59.8479816471597</v>
+        <v>59.84798164715961</v>
       </c>
       <c r="Q7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="R7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="S7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="T7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="U7" t="n">
-        <v>59.828036721911</v>
+        <v>59.82803672191089</v>
       </c>
       <c r="V7" t="n">
-        <v>58.70778507603765</v>
+        <v>58.70778507603763</v>
       </c>
       <c r="W7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="X7" t="n">
-        <v>59.84847481445293</v>
+        <v>59.84847481445292</v>
       </c>
       <c r="Y7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="Z7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="AA7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
       <c r="AB7" t="n">
-        <v>59.84847481445291</v>
+        <v>59.8484748144529</v>
       </c>
     </row>
     <row r="8">
@@ -4222,7 +4222,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>129.4069479997759</v>
+        <v>129.4069479997758</v>
       </c>
       <c r="C8" t="n">
         <v>191.7956301935666</v>
@@ -4231,7 +4231,7 @@
         <v>191.7956301935666</v>
       </c>
       <c r="E8" t="n">
-        <v>158.5754972755704</v>
+        <v>158.5754972755703</v>
       </c>
       <c r="F8" t="n">
         <v>139.1263755341063</v>
@@ -4255,19 +4255,19 @@
         <v>191.7956301935667</v>
       </c>
       <c r="M8" t="n">
-        <v>191.7956301935754</v>
+        <v>191.7956301935753</v>
       </c>
       <c r="N8" t="n">
-        <v>260.6078274636787</v>
+        <v>143.4339640952395</v>
       </c>
       <c r="O8" t="n">
-        <v>156.7241698585132</v>
+        <v>156.7241698585131</v>
       </c>
       <c r="P8" t="n">
         <v>153.4664192893102</v>
       </c>
       <c r="Q8" t="n">
-        <v>117.1461479954814</v>
+        <v>117.1461479954813</v>
       </c>
       <c r="R8" t="n">
         <v>191.7956301935666</v>
@@ -4279,16 +4279,16 @@
         <v>191.7956301935666</v>
       </c>
       <c r="U8" t="n">
-        <v>161.3290902821206</v>
+        <v>161.3290902821207</v>
       </c>
       <c r="V8" t="n">
         <v>173.5861244781616</v>
       </c>
       <c r="W8" t="n">
-        <v>191.807891361257</v>
+        <v>191.8078913612569</v>
       </c>
       <c r="X8" t="n">
-        <v>122.8641946891855</v>
+        <v>122.8641946891857</v>
       </c>
       <c r="Y8" t="n">
         <v>253.8008347070412</v>
@@ -4300,7 +4300,7 @@
         <v>191.7956301935666</v>
       </c>
       <c r="AB8" t="n">
-        <v>256.9658256054655</v>
+        <v>256.9658256054653</v>
       </c>
     </row>
     <row r="9">
@@ -4310,85 +4310,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>118.183675659208</v>
+        <v>118.1836756592077</v>
       </c>
       <c r="C9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="D9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="E9" t="n">
-        <v>136.6838359724062</v>
+        <v>136.6838359724061</v>
       </c>
       <c r="F9" t="n">
-        <v>86.79050050175823</v>
+        <v>86.79050050175803</v>
       </c>
       <c r="G9" t="n">
-        <v>142.234718574949</v>
+        <v>142.2347185749487</v>
       </c>
       <c r="H9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="I9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="J9" t="n">
-        <v>142.0550602942463</v>
+        <v>142.0550602942462</v>
       </c>
       <c r="K9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="L9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992655</v>
       </c>
       <c r="M9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="N9" t="n">
-        <v>260.6078274636787</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="O9" t="n">
-        <v>150.2052027051024</v>
+        <v>150.2052027051021</v>
       </c>
       <c r="P9" t="n">
         <v>151.9386462529072</v>
       </c>
       <c r="Q9" t="n">
-        <v>142.234718574949</v>
+        <v>142.2347185749487</v>
       </c>
       <c r="R9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="S9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="T9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="U9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="V9" t="n">
         <v>168.8483964035044</v>
       </c>
       <c r="W9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="X9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992655</v>
       </c>
       <c r="Y9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="Z9" t="n">
-        <v>127.73407839894</v>
+        <v>127.7340783989398</v>
       </c>
       <c r="AA9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
       <c r="AB9" t="n">
-        <v>142.2347213992657</v>
+        <v>142.2347213992654</v>
       </c>
     </row>
     <row r="10">
@@ -4398,85 +4398,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82.45699880058679</v>
+        <v>82.45699880058673</v>
       </c>
       <c r="C10" t="n">
-        <v>87.99033290388661</v>
+        <v>87.99033290388667</v>
       </c>
       <c r="D10" t="n">
-        <v>80.31124152356027</v>
+        <v>80.31124152356028</v>
       </c>
       <c r="E10" t="n">
-        <v>33.34777658879916</v>
+        <v>33.34777658879914</v>
       </c>
       <c r="F10" t="n">
-        <v>80.93567259051315</v>
+        <v>80.93567259051314</v>
       </c>
       <c r="G10" t="n">
-        <v>62.6636133094662</v>
+        <v>62.66361330946611</v>
       </c>
       <c r="H10" t="n">
-        <v>87.53325320614513</v>
+        <v>87.5332532061451</v>
       </c>
       <c r="I10" t="n">
-        <v>83.10537002121153</v>
+        <v>83.10537002121147</v>
       </c>
       <c r="J10" t="n">
-        <v>73.02079064241141</v>
+        <v>73.02079064241143</v>
       </c>
       <c r="K10" t="n">
-        <v>82.52426616862917</v>
+        <v>82.52426616862918</v>
       </c>
       <c r="L10" t="n">
-        <v>85.50184457618762</v>
+        <v>85.50184457618764</v>
       </c>
       <c r="M10" t="n">
-        <v>55.39517827188592</v>
+        <v>55.39517827188594</v>
       </c>
       <c r="N10" t="n">
-        <v>85.39435347793753</v>
+        <v>85.39435347793757</v>
       </c>
       <c r="O10" t="n">
-        <v>81.4864731914431</v>
+        <v>81.48647319144311</v>
       </c>
       <c r="P10" t="n">
-        <v>74.9271255096518</v>
+        <v>74.92712550965179</v>
       </c>
       <c r="Q10" t="n">
-        <v>84.66669985478444</v>
+        <v>84.66669985478445</v>
       </c>
       <c r="R10" t="n">
-        <v>87.37819030213144</v>
+        <v>87.37819030213139</v>
       </c>
       <c r="S10" t="n">
-        <v>80.04465742000784</v>
+        <v>80.04465742000775</v>
       </c>
       <c r="T10" t="n">
-        <v>85.60605733788911</v>
+        <v>85.60605733788903</v>
       </c>
       <c r="U10" t="n">
-        <v>83.19772815980359</v>
+        <v>83.19772815980345</v>
       </c>
       <c r="V10" t="n">
-        <v>48.82654479803421</v>
+        <v>48.82654479803426</v>
       </c>
       <c r="W10" t="n">
         <v>81.06694412146553</v>
       </c>
       <c r="X10" t="n">
-        <v>80.4058004603755</v>
+        <v>80.40580046037553</v>
       </c>
       <c r="Y10" t="n">
-        <v>72.82299708758551</v>
+        <v>72.82299708758548</v>
       </c>
       <c r="Z10" t="n">
-        <v>81.0336237292334</v>
+        <v>81.03362372923341</v>
       </c>
       <c r="AA10" t="n">
-        <v>84.17961689481466</v>
+        <v>84.17961689481464</v>
       </c>
       <c r="AB10" t="n">
-        <v>51.97791001246359</v>
+        <v>51.97791001246355</v>
       </c>
     </row>
     <row r="11">
@@ -4486,55 +4486,55 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86.64449287901306</v>
+        <v>86.64449287901301</v>
       </c>
       <c r="C11" t="n">
-        <v>88.2356780639998</v>
+        <v>88.23567806399981</v>
       </c>
       <c r="D11" t="n">
-        <v>86.05293830048748</v>
+        <v>86.05293830048754</v>
       </c>
       <c r="E11" t="n">
-        <v>34.85813484278795</v>
+        <v>34.85813484278792</v>
       </c>
       <c r="F11" t="n">
-        <v>86.23760008908843</v>
+        <v>86.23760008908847</v>
       </c>
       <c r="G11" t="n">
-        <v>80.96802810323891</v>
+        <v>80.96802810323892</v>
       </c>
       <c r="H11" t="n">
-        <v>88.10828514199657</v>
+        <v>88.10828514199655</v>
       </c>
       <c r="I11" t="n">
-        <v>86.84929930867196</v>
+        <v>86.84929930867197</v>
       </c>
       <c r="J11" t="n">
-        <v>83.85901834263478</v>
+        <v>83.85901834263476</v>
       </c>
       <c r="K11" t="n">
-        <v>86.68038436779864</v>
+        <v>86.68038436779862</v>
       </c>
       <c r="L11" t="n">
-        <v>87.52231136400295</v>
+        <v>87.52231136400292</v>
       </c>
       <c r="M11" t="n">
-        <v>78.99188945130824</v>
+        <v>78.9918894513082</v>
       </c>
       <c r="N11" t="n">
         <v>87.49504797557363</v>
       </c>
       <c r="O11" t="n">
-        <v>86.36457411668076</v>
+        <v>86.36457411668081</v>
       </c>
       <c r="P11" t="n">
-        <v>84.47925037810117</v>
+        <v>84.47925037810109</v>
       </c>
       <c r="Q11" t="n">
-        <v>87.28902722634132</v>
+        <v>87.28902722634135</v>
       </c>
       <c r="R11" t="n">
-        <v>88.06336749678225</v>
+        <v>88.06336749678221</v>
       </c>
       <c r="S11" t="n">
         <v>85.9572692108805</v>
@@ -4543,28 +4543,28 @@
         <v>87.55858101841972</v>
       </c>
       <c r="U11" t="n">
-        <v>86.86262170441468</v>
+        <v>86.86262170441471</v>
       </c>
       <c r="V11" t="n">
-        <v>52.86598084810691</v>
+        <v>52.86598084810697</v>
       </c>
       <c r="W11" t="n">
-        <v>86.25696538757879</v>
+        <v>86.25696538757875</v>
       </c>
       <c r="X11" t="n">
-        <v>86.07834655567508</v>
+        <v>86.07834655567513</v>
       </c>
       <c r="Y11" t="n">
-        <v>83.90731280260844</v>
+        <v>83.90731280260842</v>
       </c>
       <c r="Z11" t="n">
-        <v>86.23768221443467</v>
+        <v>86.23768221443473</v>
       </c>
       <c r="AA11" t="n">
-        <v>87.14657815250725</v>
+        <v>87.1465781525073</v>
       </c>
       <c r="AB11" t="n">
-        <v>77.9997385065632</v>
+        <v>77.99973850656319</v>
       </c>
     </row>
   </sheetData>
@@ -4730,49 +4730,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.56455547067587</v>
+        <v>89.56455547067596</v>
       </c>
       <c r="C2" t="n">
-        <v>88.73786709013137</v>
+        <v>88.7378670901314</v>
       </c>
       <c r="D2" t="n">
-        <v>89.64596257286023</v>
+        <v>89.64596257286037</v>
       </c>
       <c r="E2" t="n">
-        <v>35.48632968067113</v>
+        <v>35.48632968067116</v>
       </c>
       <c r="F2" t="n">
-        <v>90.10839331485329</v>
+        <v>90.1083933148533</v>
       </c>
       <c r="G2" t="n">
-        <v>92.36444162062089</v>
+        <v>92.36444162062106</v>
       </c>
       <c r="H2" t="n">
-        <v>88.79592002034207</v>
+        <v>88.79592002034209</v>
       </c>
       <c r="I2" t="n">
-        <v>89.64126716700861</v>
+        <v>89.64126716700872</v>
       </c>
       <c r="J2" t="n">
-        <v>90.79050019288476</v>
+        <v>90.79050019288482</v>
       </c>
       <c r="K2" t="n">
-        <v>89.70848138103007</v>
+        <v>89.70848138103017</v>
       </c>
       <c r="L2" t="n">
-        <v>89.10392294095921</v>
+        <v>89.10392294095925</v>
       </c>
       <c r="M2" t="n">
-        <v>93.36913930835668</v>
+        <v>93.36913930835675</v>
       </c>
       <c r="N2" t="n">
-        <v>89.00500056268019</v>
+        <v>89.00500056268034</v>
       </c>
       <c r="O2" t="n">
-        <v>89.42812042101939</v>
+        <v>89.4281204210195</v>
       </c>
       <c r="P2" t="n">
-        <v>90.64185538708131</v>
+        <v>90.64185538708132</v>
       </c>
       <c r="Q2" t="n">
         <v>89.15875797525369</v>
@@ -4781,34 +4781,34 @@
         <v>89.1675191714276</v>
       </c>
       <c r="S2" t="n">
-        <v>89.93666824404929</v>
+        <v>89.93666824404946</v>
       </c>
       <c r="T2" t="n">
-        <v>89.20430912980102</v>
+        <v>89.20430912980106</v>
       </c>
       <c r="U2" t="n">
-        <v>89.22110094667133</v>
+        <v>89.22110094667141</v>
       </c>
       <c r="V2" t="n">
-        <v>56.03896625636498</v>
+        <v>56.03896625636501</v>
       </c>
       <c r="W2" t="n">
-        <v>89.82358240411619</v>
+        <v>89.82358240411622</v>
       </c>
       <c r="X2" t="n">
-        <v>90.05423800885723</v>
+        <v>90.05423800885731</v>
       </c>
       <c r="Y2" t="n">
-        <v>92.53126284083082</v>
+        <v>92.53126284083086</v>
       </c>
       <c r="Z2" t="n">
-        <v>89.67786003207864</v>
+        <v>89.67786003207868</v>
       </c>
       <c r="AA2" t="n">
-        <v>89.40188387572911</v>
+        <v>89.40188387572915</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.23901186571739</v>
+        <v>94.23901186571754</v>
       </c>
     </row>
     <row r="3">
@@ -4818,85 +4818,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.17527330906847</v>
+        <v>89.1752733090686</v>
       </c>
       <c r="C3" t="n">
-        <v>89.17526945499617</v>
+        <v>89.17526945499628</v>
       </c>
       <c r="D3" t="n">
-        <v>89.17527330906847</v>
+        <v>89.1752733090686</v>
       </c>
       <c r="E3" t="n">
-        <v>35.1882154278377</v>
+        <v>35.18821542783775</v>
       </c>
       <c r="F3" t="n">
-        <v>89.17527073479643</v>
+        <v>89.17527073479654</v>
       </c>
       <c r="G3" t="n">
-        <v>89.17527208157766</v>
+        <v>89.17527208157777</v>
       </c>
       <c r="H3" t="n">
-        <v>89.17527330906847</v>
+        <v>89.1752733090686</v>
       </c>
       <c r="I3" t="n">
-        <v>89.17527330906847</v>
+        <v>89.1752733090686</v>
       </c>
       <c r="J3" t="n">
-        <v>89.07322031597894</v>
+        <v>89.07322031597899</v>
       </c>
       <c r="K3" t="n">
-        <v>89.17527183938742</v>
+        <v>89.17527183938753</v>
       </c>
       <c r="L3" t="n">
-        <v>89.17527330906847</v>
+        <v>89.1752733090686</v>
       </c>
       <c r="M3" t="n">
-        <v>89.17526663774291</v>
+        <v>89.17526663774302</v>
       </c>
       <c r="N3" t="n">
-        <v>89.17527330906847</v>
+        <v>89.1752733090686</v>
       </c>
       <c r="O3" t="n">
-        <v>89.17526992014766</v>
+        <v>89.17526992014777</v>
       </c>
       <c r="P3" t="n">
-        <v>89.17526692971609</v>
+        <v>89.1752669297162</v>
       </c>
       <c r="Q3" t="n">
-        <v>89.17527327142476</v>
+        <v>89.17527327142489</v>
       </c>
       <c r="R3" t="n">
-        <v>89.17528158681479</v>
+        <v>89.1752815868149</v>
       </c>
       <c r="S3" t="n">
-        <v>89.17527330906847</v>
+        <v>89.1752733090686</v>
       </c>
       <c r="T3" t="n">
-        <v>89.17526842873556</v>
+        <v>89.17526842873568</v>
       </c>
       <c r="U3" t="n">
-        <v>89.17528488978157</v>
+        <v>89.17528488978168</v>
       </c>
       <c r="V3" t="n">
-        <v>54.89288856102955</v>
+        <v>54.89288856102949</v>
       </c>
       <c r="W3" t="n">
-        <v>89.17527330906847</v>
+        <v>89.1752733090686</v>
       </c>
       <c r="X3" t="n">
-        <v>89.17528515148926</v>
+        <v>89.17528515148938</v>
       </c>
       <c r="Y3" t="n">
-        <v>89.17526046386236</v>
+        <v>89.17526046386247</v>
       </c>
       <c r="Z3" t="n">
-        <v>89.17527296899318</v>
+        <v>89.1752729689933</v>
       </c>
       <c r="AA3" t="n">
-        <v>89.17527330906847</v>
+        <v>89.1752733090686</v>
       </c>
       <c r="AB3" t="n">
-        <v>89.17531254501267</v>
+        <v>89.17531254501279</v>
       </c>
     </row>
     <row r="4">
@@ -4906,22 +4906,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>349.6952359953227</v>
+        <v>349.6952359953237</v>
       </c>
       <c r="C4" t="n">
-        <v>173.0542838856739</v>
+        <v>173.0542838856735</v>
       </c>
       <c r="D4" t="n">
-        <v>399.5503495935282</v>
+        <v>399.5503495935298</v>
       </c>
       <c r="E4" t="n">
-        <v>106.7881352382317</v>
+        <v>106.7881352382319</v>
       </c>
       <c r="F4" t="n">
-        <v>524.7869248975685</v>
+        <v>524.7869248975671</v>
       </c>
       <c r="G4" t="n">
-        <v>984.887897514883</v>
+        <v>984.8878975148805</v>
       </c>
       <c r="H4" t="n">
         <v>188.8741362908013</v>
@@ -4930,13 +4930,13 @@
         <v>406.9773366388869</v>
       </c>
       <c r="J4" t="n">
-        <v>677.6499481480205</v>
+        <v>677.6499481480182</v>
       </c>
       <c r="K4" t="n">
-        <v>401.7672162822136</v>
+        <v>401.7672162822134</v>
       </c>
       <c r="L4" t="n">
-        <v>253.1160921891667</v>
+        <v>253.116092189167</v>
       </c>
       <c r="M4" t="n">
         <v>1353.889775492377</v>
@@ -4948,43 +4948,43 @@
         <v>316.967967008206</v>
       </c>
       <c r="P4" t="n">
-        <v>591.7987828212608</v>
+        <v>591.7987828212592</v>
       </c>
       <c r="Q4" t="n">
-        <v>270.0084489249779</v>
+        <v>270.0084489249778</v>
       </c>
       <c r="R4" t="n">
-        <v>286.6341327448109</v>
+        <v>286.6341327448108</v>
       </c>
       <c r="S4" t="n">
-        <v>441.3011010347781</v>
+        <v>441.3011010347797</v>
       </c>
       <c r="T4" t="n">
-        <v>291.8342618222951</v>
+        <v>291.8342618222958</v>
       </c>
       <c r="U4" t="n">
-        <v>279.0259724670701</v>
+        <v>279.0259724670696</v>
       </c>
       <c r="V4" t="n">
-        <v>398.4814152531639</v>
+        <v>398.4814152531627</v>
       </c>
       <c r="W4" t="n">
-        <v>438.3856615636747</v>
+        <v>438.3856615636737</v>
       </c>
       <c r="X4" t="n">
-        <v>497.8139974165139</v>
+        <v>497.8139974165123</v>
       </c>
       <c r="Y4" t="n">
-        <v>1136.237687028504</v>
+        <v>1136.237687028501</v>
       </c>
       <c r="Z4" t="n">
-        <v>361.2538891537787</v>
+        <v>361.253889153779</v>
       </c>
       <c r="AA4" t="n">
-        <v>332.454248912915</v>
+        <v>332.4542489129146</v>
       </c>
       <c r="AB4" t="n">
-        <v>1687.203858413659</v>
+        <v>1687.203858413657</v>
       </c>
     </row>
     <row r="5">
@@ -4994,85 +4994,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>35.20697156934828</v>
+        <v>35.20697156934853</v>
       </c>
       <c r="C5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="D5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="E5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="F5" t="n">
-        <v>35.20697156934825</v>
+        <v>35.20697156934838</v>
       </c>
       <c r="G5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="H5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="I5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="J5" t="n">
-        <v>35.03392725977954</v>
+        <v>35.03392725977972</v>
       </c>
       <c r="K5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="L5" t="n">
-        <v>35.20697156934828</v>
+        <v>35.20697156934858</v>
       </c>
       <c r="M5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="N5" t="n">
-        <v>233.8924126184962</v>
+        <v>35.20697156934838</v>
       </c>
       <c r="O5" t="n">
-        <v>35.20697156934825</v>
+        <v>35.20697156934838</v>
       </c>
       <c r="P5" t="n">
-        <v>35.20697156934825</v>
+        <v>35.20697156934838</v>
       </c>
       <c r="Q5" t="n">
-        <v>35.20697156934825</v>
+        <v>35.20697156934838</v>
       </c>
       <c r="R5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="S5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="T5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="U5" t="n">
-        <v>34.54421013448493</v>
+        <v>34.54421013448513</v>
       </c>
       <c r="V5" t="n">
         <v>34.10859497659128</v>
       </c>
       <c r="W5" t="n">
-        <v>35.20697156934825</v>
+        <v>35.20697156934838</v>
       </c>
       <c r="X5" t="n">
-        <v>35.20697156934828</v>
+        <v>35.2069715693484</v>
       </c>
       <c r="Y5" t="n">
-        <v>34.54421013448493</v>
+        <v>34.54421013448513</v>
       </c>
       <c r="Z5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="AA5" t="n">
-        <v>35.20697156934826</v>
+        <v>35.20697156934857</v>
       </c>
       <c r="AB5" t="n">
-        <v>35.20697156934825</v>
+        <v>35.20697156934838</v>
       </c>
     </row>
     <row r="6">
@@ -5088,10 +5088,10 @@
         <v>134.3541605287602</v>
       </c>
       <c r="D6" t="n">
-        <v>206.8689820596699</v>
+        <v>206.8689820596703</v>
       </c>
       <c r="E6" t="n">
-        <v>206.8689820596699</v>
+        <v>206.8689820596703</v>
       </c>
       <c r="F6" t="n">
         <v>134.3541605287602</v>
@@ -5100,7 +5100,7 @@
         <v>134.3541605287602</v>
       </c>
       <c r="H6" t="n">
-        <v>206.8689820596699</v>
+        <v>206.8689820596703</v>
       </c>
       <c r="I6" t="n">
         <v>134.3541605287602</v>
@@ -5109,7 +5109,7 @@
         <v>206.6959377501011</v>
       </c>
       <c r="K6" t="n">
-        <v>206.8689820596699</v>
+        <v>206.8689820596703</v>
       </c>
       <c r="L6" t="n">
         <v>134.3541605287602</v>
@@ -5118,31 +5118,31 @@
         <v>134.3541605287602</v>
       </c>
       <c r="N6" t="n">
-        <v>233.8924126184962</v>
+        <v>134.4414411201271</v>
       </c>
       <c r="O6" t="n">
-        <v>134.4428241184221</v>
+        <v>134.4428241184222</v>
       </c>
       <c r="P6" t="n">
-        <v>205.0653338513186</v>
+        <v>205.0653338513188</v>
       </c>
       <c r="Q6" t="n">
-        <v>206.8689820596699</v>
+        <v>206.8689820596703</v>
       </c>
       <c r="R6" t="n">
-        <v>206.8689820596699</v>
+        <v>206.8689820596703</v>
       </c>
       <c r="S6" t="n">
         <v>134.3541605287602</v>
       </c>
       <c r="T6" t="n">
-        <v>206.8689820596699</v>
+        <v>206.8689820596703</v>
       </c>
       <c r="U6" t="n">
-        <v>206.8689820596699</v>
+        <v>206.8689820596703</v>
       </c>
       <c r="V6" t="n">
-        <v>133.2557839360034</v>
+        <v>133.255783936003</v>
       </c>
       <c r="W6" t="n">
         <v>139.6742456642116</v>
@@ -5151,16 +5151,16 @@
         <v>134.3541605287602</v>
       </c>
       <c r="Y6" t="n">
-        <v>138.8747970200619</v>
+        <v>138.8747970200615</v>
       </c>
       <c r="Z6" t="n">
         <v>134.3541605287602</v>
       </c>
       <c r="AA6" t="n">
-        <v>206.8689820596699</v>
+        <v>206.8689820596703</v>
       </c>
       <c r="AB6" t="n">
-        <v>134.8217578450459</v>
+        <v>134.8217578450461</v>
       </c>
     </row>
     <row r="7">
@@ -5170,85 +5170,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59.70915601633246</v>
+        <v>59.70915601633253</v>
       </c>
       <c r="C7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="D7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="E7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="F7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="G7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="H7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="I7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="J7" t="n">
-        <v>59.53611170676362</v>
+        <v>59.53611170676371</v>
       </c>
       <c r="K7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="L7" t="n">
-        <v>59.70915601633246</v>
+        <v>59.70915601633253</v>
       </c>
       <c r="M7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="N7" t="n">
-        <v>233.8924126184962</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="O7" t="n">
-        <v>59.7086603946797</v>
+        <v>59.70866039467981</v>
       </c>
       <c r="P7" t="n">
-        <v>59.7086603946797</v>
+        <v>59.70866039467981</v>
       </c>
       <c r="Q7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="R7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="S7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="T7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="U7" t="n">
-        <v>59.69280694993893</v>
+        <v>59.69280694993886</v>
       </c>
       <c r="V7" t="n">
-        <v>58.61077942357543</v>
+        <v>58.61077942357528</v>
       </c>
       <c r="W7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="X7" t="n">
-        <v>59.70915601633246</v>
+        <v>59.70915601633253</v>
       </c>
       <c r="Y7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="Z7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="AA7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
       <c r="AB7" t="n">
-        <v>59.70915601633239</v>
+        <v>59.70915601633251</v>
       </c>
     </row>
     <row r="8">
@@ -5258,43 +5258,43 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>128.9431639726357</v>
+        <v>128.9431639726355</v>
       </c>
       <c r="C8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="D8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="E8" t="n">
-        <v>157.9010290745879</v>
+        <v>157.9010290745878</v>
       </c>
       <c r="F8" t="n">
-        <v>138.5923881677385</v>
+        <v>138.5923881677383</v>
       </c>
       <c r="G8" t="n">
-        <v>203.7244712761093</v>
+        <v>203.7244712761091</v>
       </c>
       <c r="H8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="I8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="J8" t="n">
         <v>190.7081689563832</v>
       </c>
       <c r="K8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="L8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="M8" t="n">
-        <v>190.881213265965</v>
+        <v>190.8812132659648</v>
       </c>
       <c r="N8" t="n">
-        <v>233.8924126184962</v>
+        <v>142.8688630547602</v>
       </c>
       <c r="O8" t="n">
         <v>156.0630737792532</v>
@@ -5303,40 +5303,40 @@
         <v>152.8288539136126</v>
       </c>
       <c r="Q8" t="n">
-        <v>116.7709236184334</v>
+        <v>116.7709236184336</v>
       </c>
       <c r="R8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="S8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="T8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="U8" t="n">
-        <v>160.6377920557192</v>
+        <v>160.637792055719</v>
       </c>
       <c r="V8" t="n">
-        <v>172.8406827589411</v>
+        <v>172.8406827589409</v>
       </c>
       <c r="W8" t="n">
-        <v>190.8933858714857</v>
+        <v>190.8933858714855</v>
       </c>
       <c r="X8" t="n">
         <v>122.4476689114663</v>
       </c>
       <c r="Y8" t="n">
-        <v>252.4437880546701</v>
+        <v>252.4437880546699</v>
       </c>
       <c r="Z8" t="n">
-        <v>127.7926329076187</v>
+        <v>127.7926329076188</v>
       </c>
       <c r="AA8" t="n">
-        <v>190.8812132659522</v>
+        <v>190.8812132659519</v>
       </c>
       <c r="AB8" t="n">
-        <v>255.5806849321269</v>
+        <v>255.5806849321266</v>
       </c>
     </row>
     <row r="9">
@@ -5349,82 +5349,82 @@
         <v>112.9189690457042</v>
       </c>
       <c r="C9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="D9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="E9" t="n">
         <v>130.2469707333638</v>
       </c>
       <c r="F9" t="n">
-        <v>83.5148458975803</v>
+        <v>83.51484589758041</v>
       </c>
       <c r="G9" t="n">
-        <v>135.4461528743019</v>
+        <v>135.4461528743018</v>
       </c>
       <c r="H9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="I9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="J9" t="n">
-        <v>135.2731104885549</v>
+        <v>135.2731104885547</v>
       </c>
       <c r="K9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="L9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="M9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="N9" t="n">
-        <v>233.8924126184962</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="O9" t="n">
         <v>142.9116320982992</v>
       </c>
       <c r="P9" t="n">
-        <v>144.53524574344</v>
+        <v>144.5352457434399</v>
       </c>
       <c r="Q9" t="n">
-        <v>135.4461528743019</v>
+        <v>135.4461528743018</v>
       </c>
       <c r="R9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="S9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="T9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="U9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="V9" t="n">
-        <v>160.3436461730325</v>
+        <v>160.343646173032</v>
       </c>
       <c r="W9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="X9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="Y9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="Z9" t="n">
         <v>121.8642642210031</v>
       </c>
       <c r="AA9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
       <c r="AB9" t="n">
-        <v>135.4461547981234</v>
+        <v>135.4461547981236</v>
       </c>
     </row>
     <row r="10">
@@ -5434,85 +5434,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>82.4426996695834</v>
+        <v>82.44269966958358</v>
       </c>
       <c r="C10" t="n">
-        <v>87.38806566629827</v>
+        <v>87.38806566629835</v>
       </c>
       <c r="D10" t="n">
-        <v>82.07106670661469</v>
+        <v>82.07106670661496</v>
       </c>
       <c r="E10" t="n">
-        <v>33.79828249176758</v>
+        <v>33.79828249176766</v>
       </c>
       <c r="F10" t="n">
-        <v>79.4107196232052</v>
+        <v>79.41071962320535</v>
       </c>
       <c r="G10" t="n">
-        <v>65.79874709303976</v>
+        <v>65.79874709303992</v>
       </c>
       <c r="H10" t="n">
-        <v>87.06524206704506</v>
+        <v>87.06524206704509</v>
       </c>
       <c r="I10" t="n">
-        <v>82.11199960138477</v>
+        <v>82.11199960138485</v>
       </c>
       <c r="J10" t="n">
-        <v>74.54615206863514</v>
+        <v>74.54615206863531</v>
       </c>
       <c r="K10" t="n">
-        <v>81.69412849559983</v>
+        <v>81.69412849559994</v>
       </c>
       <c r="L10" t="n">
-        <v>85.20874603727086</v>
+        <v>85.20874603727101</v>
       </c>
       <c r="M10" t="n">
-        <v>60.37249081042361</v>
+        <v>60.37249081042379</v>
       </c>
       <c r="N10" t="n">
-        <v>85.81094266074693</v>
+        <v>85.81094266074702</v>
       </c>
       <c r="O10" t="n">
-        <v>83.24779483347527</v>
+        <v>83.24779483347535</v>
       </c>
       <c r="P10" t="n">
-        <v>76.00742531097553</v>
+        <v>76.00742531097563</v>
       </c>
       <c r="Q10" t="n">
-        <v>84.91376058679776</v>
+        <v>84.91376058679786</v>
       </c>
       <c r="R10" t="n">
-        <v>84.8909540248805</v>
+        <v>84.89095402488054</v>
       </c>
       <c r="S10" t="n">
-        <v>80.25685848082897</v>
+        <v>80.2568584808291</v>
       </c>
       <c r="T10" t="n">
-        <v>84.66096741744627</v>
+        <v>84.66096741744636</v>
       </c>
       <c r="U10" t="n">
-        <v>84.51133621415211</v>
+        <v>84.51133621415219</v>
       </c>
       <c r="V10" t="n">
         <v>46.83242535420376</v>
       </c>
       <c r="W10" t="n">
-        <v>80.96810923337489</v>
+        <v>80.96810923337497</v>
       </c>
       <c r="X10" t="n">
-        <v>79.67041538299956</v>
+        <v>79.67041538299969</v>
       </c>
       <c r="Y10" t="n">
-        <v>65.02658163249291</v>
+        <v>65.02658163249305</v>
       </c>
       <c r="Z10" t="n">
-        <v>81.77694689622868</v>
+        <v>81.77694689622878</v>
       </c>
       <c r="AA10" t="n">
-        <v>83.46170482981694</v>
+        <v>83.46170482981699</v>
       </c>
       <c r="AB10" t="n">
-        <v>55.17512866659498</v>
+        <v>55.17512866659504</v>
       </c>
     </row>
     <row r="11">
@@ -5522,85 +5522,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>86.50121300927094</v>
+        <v>86.50121300927104</v>
       </c>
       <c r="C11" t="n">
-        <v>87.92468367079326</v>
+        <v>87.92468367079329</v>
       </c>
       <c r="D11" t="n">
-        <v>86.41352592898062</v>
+        <v>86.41352592898075</v>
       </c>
       <c r="E11" t="n">
-        <v>34.85390576530576</v>
+        <v>34.8539057653058</v>
       </c>
       <c r="F11" t="n">
-        <v>85.66549144130114</v>
+        <v>85.66549144130131</v>
       </c>
       <c r="G11" t="n">
-        <v>81.72804825427129</v>
+        <v>81.7280482542714</v>
       </c>
       <c r="H11" t="n">
-        <v>87.83584908095077</v>
+        <v>87.83584908095082</v>
       </c>
       <c r="I11" t="n">
-        <v>86.42745512069484</v>
+        <v>86.42745512069486</v>
       </c>
       <c r="J11" t="n">
-        <v>84.18063784532374</v>
+        <v>84.18063784532383</v>
       </c>
       <c r="K11" t="n">
-        <v>86.30453731861752</v>
+        <v>86.30453731861762</v>
       </c>
       <c r="L11" t="n">
-        <v>87.29914039171886</v>
+        <v>87.29914039171894</v>
       </c>
       <c r="M11" t="n">
-        <v>80.26378451792598</v>
+        <v>80.2637845179261</v>
       </c>
       <c r="N11" t="n">
-        <v>87.47421939620828</v>
+        <v>87.47421939620837</v>
       </c>
       <c r="O11" t="n">
-        <v>86.7311003668412</v>
+        <v>86.73110036684132</v>
       </c>
       <c r="P11" t="n">
-        <v>84.65044548713293</v>
+        <v>84.65044548713296</v>
       </c>
       <c r="Q11" t="n">
-        <v>87.21975612311324</v>
+        <v>87.21975612311336</v>
       </c>
       <c r="R11" t="n">
-        <v>87.21813647740558</v>
+        <v>87.21813647740569</v>
       </c>
       <c r="S11" t="n">
-        <v>85.87876107589874</v>
+        <v>85.87876107589889</v>
       </c>
       <c r="T11" t="n">
-        <v>87.15028778344065</v>
+        <v>87.15028778344076</v>
       </c>
       <c r="U11" t="n">
-        <v>87.0989894361374</v>
+        <v>87.09898943613747</v>
       </c>
       <c r="V11" t="n">
-        <v>52.37142981008712</v>
+        <v>52.37142981008716</v>
       </c>
       <c r="W11" t="n">
-        <v>86.08929659499556</v>
+        <v>86.08929659499555</v>
       </c>
       <c r="X11" t="n">
-        <v>85.72949197397169</v>
+        <v>85.72949197397183</v>
       </c>
       <c r="Y11" t="n">
-        <v>81.54353701528443</v>
+        <v>81.54353701528451</v>
       </c>
       <c r="Z11" t="n">
-        <v>86.31159809190456</v>
+        <v>86.31159809190464</v>
       </c>
       <c r="AA11" t="n">
-        <v>86.80219200960725</v>
+        <v>86.80219200960734</v>
       </c>
       <c r="AB11" t="n">
-        <v>78.76881984888028</v>
+        <v>78.76881984888041</v>
       </c>
     </row>
   </sheetData>
@@ -6066,7 +6066,7 @@
         <v>33.71737644528067</v>
       </c>
       <c r="N5" t="n">
-        <v>264.0610506442065</v>
+        <v>33.7173764452807</v>
       </c>
       <c r="O5" t="n">
         <v>33.7173764452807</v>
@@ -6154,7 +6154,7 @@
         <v>214.4238311334842</v>
       </c>
       <c r="N6" t="n">
-        <v>264.0610506442065</v>
+        <v>139.4586972830458</v>
       </c>
       <c r="O6" t="n">
         <v>212.4583403575064</v>
@@ -6242,7 +6242,7 @@
         <v>58.32071344479857</v>
       </c>
       <c r="N7" t="n">
-        <v>264.0610506442065</v>
+        <v>58.32071344479857</v>
       </c>
       <c r="O7" t="n">
         <v>58.32021315565487</v>
@@ -6330,7 +6330,7 @@
         <v>195.1461784028579</v>
       </c>
       <c r="N8" t="n">
-        <v>264.0610506442065</v>
+        <v>145.5127924796942</v>
       </c>
       <c r="O8" t="n">
         <v>159.1524778936152</v>
@@ -6418,7 +6418,7 @@
         <v>139.0414973725467</v>
       </c>
       <c r="N9" t="n">
-        <v>264.0610506442065</v>
+        <v>139.0414973725467</v>
       </c>
       <c r="O9" t="n">
         <v>146.8453347999501</v>
@@ -6820,7 +6820,7 @@
         <v>86.64071952038353</v>
       </c>
       <c r="H2" t="n">
-        <v>86.72694017419028</v>
+        <v>86.72694017419029</v>
       </c>
       <c r="I2" t="n">
         <v>86.61636727525502</v>
@@ -6835,7 +6835,7 @@
         <v>86.50394214976643</v>
       </c>
       <c r="M2" t="n">
-        <v>86.47429863806522</v>
+        <v>86.47429863806524</v>
       </c>
       <c r="N2" t="n">
         <v>86.67554206013543</v>
@@ -6868,7 +6868,7 @@
         <v>87.04806866088613</v>
       </c>
       <c r="X2" t="n">
-        <v>87.52164006924107</v>
+        <v>87.52164006924106</v>
       </c>
       <c r="Y2" t="n">
         <v>86.99298573858346</v>
@@ -7102,7 +7102,7 @@
         <v>33.17289678830826</v>
       </c>
       <c r="N5" t="n">
-        <v>221.029178647898</v>
+        <v>33.17289678830819</v>
       </c>
       <c r="O5" t="n">
         <v>33.17289678830819</v>
@@ -7190,7 +7190,7 @@
         <v>200.5605401871848</v>
       </c>
       <c r="N6" t="n">
-        <v>221.029178647898</v>
+        <v>131.6617323365675</v>
       </c>
       <c r="O6" t="n">
         <v>198.7210641090788</v>
@@ -7278,7 +7278,7 @@
         <v>55.39610465189996</v>
       </c>
       <c r="N7" t="n">
-        <v>221.029178647898</v>
+        <v>55.39610465189996</v>
       </c>
       <c r="O7" t="n">
         <v>55.39564060675652</v>
@@ -7366,7 +7366,7 @@
         <v>181.0864134733855</v>
       </c>
       <c r="N8" t="n">
-        <v>221.029178647898</v>
+        <v>135.6707891070816</v>
       </c>
       <c r="O8" t="n">
         <v>148.1513970229724</v>
@@ -7454,7 +7454,7 @@
         <v>121.8655338187662</v>
       </c>
       <c r="N9" t="n">
-        <v>221.029178647898</v>
+        <v>121.8655338187662</v>
       </c>
       <c r="O9" t="n">
         <v>128.4401972004737</v>
@@ -7597,7 +7597,7 @@
         <v>85.00989965611733</v>
       </c>
       <c r="C11" t="n">
-        <v>85.74721674947423</v>
+        <v>85.74721674947425</v>
       </c>
       <c r="D11" t="n">
         <v>85.77702035154219</v>
@@ -7642,7 +7642,7 @@
         <v>85.1889927516456</v>
       </c>
       <c r="R11" t="n">
-        <v>85.42985527550924</v>
+        <v>85.42985527550923</v>
       </c>
       <c r="S11" t="n">
         <v>85.29334199844384</v>
@@ -7669,7 +7669,7 @@
         <v>85.12137232864171</v>
       </c>
       <c r="AA11" t="n">
-        <v>85.14544495709673</v>
+        <v>85.14544495709674</v>
       </c>
       <c r="AB11" t="n">
         <v>85.59728707456321</v>
@@ -8138,7 +8138,7 @@
         <v>33.08180923743376</v>
       </c>
       <c r="N5" t="n">
-        <v>182.1154705515551</v>
+        <v>33.08180923743379</v>
       </c>
       <c r="O5" t="n">
         <v>33.08180923743379</v>
@@ -8226,7 +8226,7 @@
         <v>200.3242839753265</v>
       </c>
       <c r="N6" t="n">
-        <v>182.1154705515551</v>
+        <v>131.4905031404909</v>
       </c>
       <c r="O6" t="n">
         <v>131.4923116902907</v>
@@ -8314,7 +8314,7 @@
         <v>55.17332374279864</v>
       </c>
       <c r="N7" t="n">
-        <v>182.1154705515551</v>
+        <v>55.17332374279864</v>
       </c>
       <c r="O7" t="n">
         <v>55.1728630710364</v>
@@ -8402,7 +8402,7 @@
         <v>180.5180976910165</v>
       </c>
       <c r="N8" t="n">
-        <v>182.1154705515551</v>
+        <v>135.2555278389731</v>
       </c>
       <c r="O8" t="n">
         <v>147.6940750454476</v>
@@ -8490,7 +8490,7 @@
         <v>117.2455244275365</v>
       </c>
       <c r="N9" t="n">
-        <v>182.1154705515551</v>
+        <v>117.2455244275365</v>
       </c>
       <c r="O9" t="n">
         <v>123.4928101856966</v>
@@ -9174,7 +9174,7 @@
         <v>34.95920871264246</v>
       </c>
       <c r="N5" t="n">
-        <v>347.5899552816235</v>
+        <v>34.95920871264246</v>
       </c>
       <c r="O5" t="n">
         <v>34.95920871264246</v>
@@ -9262,7 +9262,7 @@
         <v>140.8529951744851</v>
       </c>
       <c r="N6" t="n">
-        <v>347.5899552816235</v>
+        <v>140.8980066117452</v>
       </c>
       <c r="O6" t="n">
         <v>217.1465121512078</v>
@@ -9350,7 +9350,7 @@
         <v>61.26476776780652</v>
       </c>
       <c r="N7" t="n">
-        <v>347.5899552816235</v>
+        <v>61.26476776780652</v>
       </c>
       <c r="O7" t="n">
         <v>61.26424885533973</v>
@@ -9438,7 +9438,7 @@
         <v>202.1964728405683</v>
       </c>
       <c r="N8" t="n">
-        <v>347.5899552816235</v>
+        <v>150.6052070736215</v>
       </c>
       <c r="O8" t="n">
         <v>164.7829348681192</v>
@@ -9526,7 +9526,7 @@
         <v>155.9207064563176</v>
       </c>
       <c r="N9" t="n">
-        <v>347.5899552816235</v>
+        <v>155.9207064563176</v>
       </c>
       <c r="O9" t="n">
         <v>164.8969287624324</v>
@@ -10210,7 +10210,7 @@
         <v>34.01904587181392</v>
       </c>
       <c r="N5" t="n">
-        <v>234.7467019374956</v>
+        <v>34.01904587181391</v>
       </c>
       <c r="O5" t="n">
         <v>34.01904587181391</v>
@@ -10298,7 +10298,7 @@
         <v>132.3990430161217</v>
       </c>
       <c r="N6" t="n">
-        <v>234.7467019374956</v>
+        <v>132.4358717253004</v>
       </c>
       <c r="O6" t="n">
         <v>202.1375094945908</v>
@@ -10386,7 +10386,7 @@
         <v>57.37114311331518</v>
       </c>
       <c r="N7" t="n">
-        <v>234.7467019374956</v>
+        <v>57.37114311331518</v>
       </c>
       <c r="O7" t="n">
         <v>57.37066732261343</v>
@@ -10474,7 +10474,7 @@
         <v>186.0609955818102</v>
       </c>
       <c r="N8" t="n">
-        <v>234.7467019374956</v>
+        <v>139.2315839096072</v>
       </c>
       <c r="O8" t="n">
         <v>152.1007128524292</v>
@@ -10562,7 +10562,7 @@
         <v>134.0687625549342</v>
       </c>
       <c r="N9" t="n">
-        <v>234.7467019374956</v>
+        <v>134.0687625549342</v>
       </c>
       <c r="O9" t="n">
         <v>141.4994336172825</v>

--- a/Results/Phase 2/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
+++ b/Results/Phase 2/Hydrogen/hydrogen ecotoxicity freshwater results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90.36142538980944</v>
+        <v>90.36142538980441</v>
       </c>
       <c r="C2" t="n">
-        <v>89.62762110557762</v>
+        <v>89.62762110557264</v>
       </c>
       <c r="D2" t="n">
-        <v>90.11496139244883</v>
+        <v>90.11496139244713</v>
       </c>
       <c r="E2" t="n">
-        <v>36.18284131574414</v>
+        <v>36.18284131573892</v>
       </c>
       <c r="F2" t="n">
-        <v>90.36910387354142</v>
+        <v>90.36910387353744</v>
       </c>
       <c r="G2" t="n">
-        <v>94.10356570204047</v>
+        <v>94.10356570203686</v>
       </c>
       <c r="H2" t="n">
-        <v>89.71291281496738</v>
+        <v>89.71291281497939</v>
       </c>
       <c r="I2" t="n">
-        <v>90.27804415784247</v>
+        <v>90.27804415784156</v>
       </c>
       <c r="J2" t="n">
-        <v>91.8550181345485</v>
+        <v>91.85501813454401</v>
       </c>
       <c r="K2" t="n">
-        <v>90.21462639274466</v>
+        <v>90.21462639273734</v>
       </c>
       <c r="L2" t="n">
-        <v>90.04290173712033</v>
+        <v>90.04290173711345</v>
       </c>
       <c r="M2" t="n">
-        <v>96.27261552581594</v>
+        <v>96.27261552581238</v>
       </c>
       <c r="N2" t="n">
-        <v>90.11994313651476</v>
+        <v>90.11994313650814</v>
       </c>
       <c r="O2" t="n">
-        <v>90.75247310564379</v>
+        <v>90.7524731056379</v>
       </c>
       <c r="P2" t="n">
-        <v>91.24957039155385</v>
+        <v>91.24957039155203</v>
       </c>
       <c r="Q2" t="n">
-        <v>89.83870806623223</v>
+        <v>89.83870806622603</v>
       </c>
       <c r="R2" t="n">
-        <v>89.73035840688607</v>
+        <v>89.73035840688014</v>
       </c>
       <c r="S2" t="n">
-        <v>90.88849165300955</v>
+        <v>90.88849165300584</v>
       </c>
       <c r="T2" t="n">
-        <v>89.89782391711373</v>
+        <v>89.89782391710659</v>
       </c>
       <c r="U2" t="n">
-        <v>91.62164787671026</v>
+        <v>91.62164787670643</v>
       </c>
       <c r="V2" t="n">
-        <v>56.22672122076568</v>
+        <v>56.2267212207656</v>
       </c>
       <c r="W2" t="n">
-        <v>90.88858487767331</v>
+        <v>90.88858487766711</v>
       </c>
       <c r="X2" t="n">
-        <v>90.38434282734798</v>
+        <v>90.38434282733738</v>
       </c>
       <c r="Y2" t="n">
-        <v>91.00285748411291</v>
+        <v>91.00285748410785</v>
       </c>
       <c r="Z2" t="n">
-        <v>90.82478762934565</v>
+        <v>90.82478762933791</v>
       </c>
       <c r="AA2" t="n">
-        <v>91.12544678640376</v>
+        <v>91.12544678639733</v>
       </c>
       <c r="AB2" t="n">
-        <v>96.22597878069863</v>
+        <v>96.22597878069351</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="C3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="D3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="E3" t="n">
-        <v>35.68588289664952</v>
+        <v>35.68588289664567</v>
       </c>
       <c r="F3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="G3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="H3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="I3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="J3" t="n">
-        <v>89.78907206836989</v>
+        <v>89.7890720683647</v>
       </c>
       <c r="K3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="L3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="M3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="N3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="O3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="P3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="Q3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="R3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="S3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="T3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="U3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="V3" t="n">
-        <v>55.36941395131014</v>
+        <v>55.36941395131011</v>
       </c>
       <c r="W3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="X3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="Y3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="Z3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="AA3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
       <c r="AB3" t="n">
-        <v>89.9314673953387</v>
+        <v>89.93146739532855</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>414.4056839131032</v>
+        <v>414.405683913089</v>
       </c>
       <c r="C4" t="n">
-        <v>230.2542584999979</v>
+        <v>230.254258499988</v>
       </c>
       <c r="D4" t="n">
-        <v>379.0487900849755</v>
+        <v>379.0487900849967</v>
       </c>
       <c r="E4" t="n">
-        <v>170.3203446795025</v>
+        <v>170.3203446795156</v>
       </c>
       <c r="F4" t="n">
-        <v>466.1411679252996</v>
+        <v>466.1411679252785</v>
       </c>
       <c r="G4" t="n">
-        <v>1457.847485053602</v>
+        <v>1457.847485053584</v>
       </c>
       <c r="H4" t="n">
-        <v>266.4611116718801</v>
+        <v>266.4611116718663</v>
       </c>
       <c r="I4" t="n">
-        <v>432.7394845135783</v>
+        <v>432.7394845135614</v>
       </c>
       <c r="J4" t="n">
-        <v>895.4091230945542</v>
+        <v>895.4091230945344</v>
       </c>
       <c r="K4" t="n">
-        <v>406.7441945067513</v>
+        <v>406.7441945067408</v>
       </c>
       <c r="L4" t="n">
-        <v>341.6520198572987</v>
+        <v>341.6520198572688</v>
       </c>
       <c r="M4" t="n">
-        <v>2275.427938391163</v>
+        <v>2275.427938391148</v>
       </c>
       <c r="N4" t="n">
-        <v>372.2804942320403</v>
+        <v>372.2804942320314</v>
       </c>
       <c r="O4" t="n">
-        <v>513.0787371276165</v>
+        <v>513.0787371276035</v>
       </c>
       <c r="P4" t="n">
-        <v>659.8569324077924</v>
+        <v>659.856932407803</v>
       </c>
       <c r="Q4" t="n">
-        <v>291.0946435385109</v>
+        <v>291.0946435384851</v>
       </c>
       <c r="R4" t="n">
-        <v>266.8798139839951</v>
+        <v>266.8798139839593</v>
       </c>
       <c r="S4" t="n">
-        <v>568.7685840561177</v>
+        <v>568.7685840560996</v>
       </c>
       <c r="T4" t="n">
-        <v>313.9394061339414</v>
+        <v>313.9394061339339</v>
       </c>
       <c r="U4" t="n">
-        <v>785.8504565000138</v>
+        <v>785.8504565000039</v>
       </c>
       <c r="V4" t="n">
-        <v>389.5068847097338</v>
+        <v>389.5068847097324</v>
       </c>
       <c r="W4" t="n">
-        <v>590.2658631549343</v>
+        <v>590.2658631549209</v>
       </c>
       <c r="X4" t="n">
-        <v>456.8998166094777</v>
+        <v>456.8998166094858</v>
       </c>
       <c r="Y4" t="n">
-        <v>625.1396420399788</v>
+        <v>625.1396420399655</v>
       </c>
       <c r="Z4" t="n">
-        <v>548.8089413790682</v>
+        <v>548.8089413790507</v>
       </c>
       <c r="AA4" t="n">
-        <v>662.7268253046225</v>
+        <v>662.7268253046137</v>
       </c>
       <c r="AB4" t="n">
-        <v>2344.090464370045</v>
+        <v>2344.090464370024</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>145.4319639662837</v>
+        <v>145.4319639662906</v>
       </c>
       <c r="C5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="D5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="E5" t="n">
-        <v>179.3158110693907</v>
+        <v>179.3158110694163</v>
       </c>
       <c r="F5" t="n">
-        <v>156.7226042168006</v>
+        <v>156.7226042167974</v>
       </c>
       <c r="G5" t="n">
-        <v>232.9342150442844</v>
+        <v>232.9342150442731</v>
       </c>
       <c r="H5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="I5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="J5" t="n">
-        <v>217.7247966864313</v>
+        <v>217.7247966864151</v>
       </c>
       <c r="K5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="L5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="M5" t="n">
-        <v>217.9062083460311</v>
+        <v>217.9062083459925</v>
       </c>
       <c r="N5" t="n">
-        <v>372.2804942320403</v>
+        <v>161.7265442759108</v>
       </c>
       <c r="O5" t="n">
-        <v>177.1652037646611</v>
+        <v>177.1652037646599</v>
       </c>
       <c r="P5" t="n">
-        <v>173.3808152733918</v>
+        <v>173.3808152734011</v>
       </c>
       <c r="Q5" t="n">
-        <v>131.1891208006062</v>
+        <v>131.1891208005802</v>
       </c>
       <c r="R5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="S5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="T5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="U5" t="n">
-        <v>182.5175104973922</v>
+        <v>182.5175104973859</v>
       </c>
       <c r="V5" t="n">
         <v>196.9295395597705</v>
       </c>
       <c r="W5" t="n">
-        <v>217.9204516161926</v>
+        <v>217.920451616183</v>
       </c>
       <c r="X5" t="n">
-        <v>137.8315293092818</v>
+        <v>137.8315293092801</v>
       </c>
       <c r="Y5" t="n">
-        <v>289.9400624193885</v>
+        <v>289.9400624193688</v>
       </c>
       <c r="Z5" t="n">
-        <v>144.0857176682338</v>
+        <v>144.0857176682427</v>
       </c>
       <c r="AA5" t="n">
-        <v>217.9062083460274</v>
+        <v>217.9062083459941</v>
       </c>
       <c r="AB5" t="n">
-        <v>293.6116168025803</v>
+        <v>293.6116168025735</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>148.2465376366235</v>
+        <v>148.2465376366368</v>
       </c>
       <c r="C6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="D6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="E6" t="n">
-        <v>173.1095651665766</v>
+        <v>173.1095651665481</v>
       </c>
       <c r="F6" t="n">
-        <v>106.0561260413601</v>
+        <v>106.0561260413455</v>
       </c>
       <c r="G6" t="n">
-        <v>180.5695949515115</v>
+        <v>180.5695949515063</v>
       </c>
       <c r="H6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="I6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="J6" t="n">
-        <v>180.3881903166836</v>
+        <v>180.3881903166666</v>
       </c>
       <c r="K6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="L6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="M6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="N6" t="n">
-        <v>372.2804942320403</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="O6" t="n">
-        <v>191.2814138222667</v>
+        <v>191.2814138222524</v>
       </c>
       <c r="P6" t="n">
-        <v>193.611050642766</v>
+        <v>193.611050642736</v>
       </c>
       <c r="Q6" t="n">
-        <v>180.5695949515115</v>
+        <v>180.5695949515063</v>
       </c>
       <c r="R6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="S6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="T6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="U6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="V6" t="n">
-        <v>216.7178506881716</v>
+        <v>216.7178506881714</v>
       </c>
       <c r="W6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="X6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="Y6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="Z6" t="n">
-        <v>161.0816656690371</v>
+        <v>161.0816656690236</v>
       </c>
       <c r="AA6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
       <c r="AB6" t="n">
-        <v>180.5696019762795</v>
+        <v>180.5696019762833</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82.90418614746373</v>
+        <v>82.90418614746507</v>
       </c>
       <c r="C7" t="n">
-        <v>87.30908304052693</v>
+        <v>87.30908304052869</v>
       </c>
       <c r="D7" t="n">
-        <v>84.45761429491154</v>
+        <v>84.45761429490483</v>
       </c>
       <c r="E7" t="n">
-        <v>33.09137674503624</v>
+        <v>33.09137674503174</v>
       </c>
       <c r="F7" t="n">
-        <v>83.00343135877671</v>
+        <v>83.00343135877016</v>
       </c>
       <c r="G7" t="n">
-        <v>60.65788835180917</v>
+        <v>60.65788835179869</v>
       </c>
       <c r="H7" t="n">
-        <v>86.83435528261535</v>
+        <v>86.83435528259801</v>
       </c>
       <c r="I7" t="n">
-        <v>83.51456977841933</v>
+        <v>83.51456977840493</v>
       </c>
       <c r="J7" t="n">
-        <v>73.11194641413456</v>
+        <v>73.11194641412426</v>
       </c>
       <c r="K7" t="n">
-        <v>83.86510286075469</v>
+        <v>83.86510286074537</v>
       </c>
       <c r="L7" t="n">
-        <v>84.83195963796933</v>
+        <v>84.83195963796247</v>
       </c>
       <c r="M7" t="n">
-        <v>48.5469828489238</v>
+        <v>48.54698284891298</v>
       </c>
       <c r="N7" t="n">
-        <v>84.4047428445388</v>
+        <v>84.40474284452911</v>
       </c>
       <c r="O7" t="n">
-        <v>80.5674783192449</v>
+        <v>80.56747831924226</v>
       </c>
       <c r="P7" t="n">
-        <v>77.59591065343102</v>
+        <v>77.5959106534186</v>
       </c>
       <c r="Q7" t="n">
-        <v>86.06566290968401</v>
+        <v>86.06566290967713</v>
       </c>
       <c r="R7" t="n">
-        <v>86.72351941073116</v>
+        <v>86.72351941072807</v>
       </c>
       <c r="S7" t="n">
-        <v>79.80025704935038</v>
+        <v>79.80025704935051</v>
       </c>
       <c r="T7" t="n">
-        <v>85.73223674932984</v>
+        <v>85.73223674932409</v>
       </c>
       <c r="U7" t="n">
-        <v>75.48416238890061</v>
+        <v>75.4841623888928</v>
       </c>
       <c r="V7" t="n">
-        <v>48.98586282782565</v>
+        <v>48.98586282782564</v>
       </c>
       <c r="W7" t="n">
-        <v>79.84942525383448</v>
+        <v>79.84942525383018</v>
       </c>
       <c r="X7" t="n">
-        <v>82.8728146244046</v>
+        <v>82.872814624401</v>
       </c>
       <c r="Y7" t="n">
-        <v>79.19251933481858</v>
+        <v>79.1925193348093</v>
       </c>
       <c r="Z7" t="n">
-        <v>80.15851560461057</v>
+        <v>80.15851560461013</v>
       </c>
       <c r="AA7" t="n">
-        <v>78.46089644319842</v>
+        <v>78.46089644318852</v>
       </c>
       <c r="AB7" t="n">
-        <v>48.67154067571729</v>
+        <v>48.67154067570937</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>87.16399002740968</v>
+        <v>87.16399002740438</v>
       </c>
       <c r="C8" t="n">
-        <v>88.43442786709517</v>
+        <v>88.43442786708518</v>
       </c>
       <c r="D8" t="n">
-        <v>87.62434078761966</v>
+        <v>87.62434078760441</v>
       </c>
       <c r="E8" t="n">
-        <v>35.00233274855958</v>
+        <v>35.00233274854561</v>
       </c>
       <c r="F8" t="n">
-        <v>87.21682539856481</v>
+        <v>87.21682539854962</v>
       </c>
       <c r="G8" t="n">
-        <v>80.78399394787328</v>
+        <v>80.78399394787029</v>
       </c>
       <c r="H8" t="n">
-        <v>88.30371693376756</v>
+        <v>88.30371693376325</v>
       </c>
       <c r="I8" t="n">
-        <v>87.35833529270481</v>
+        <v>87.35833529271062</v>
       </c>
       <c r="J8" t="n">
-        <v>84.26687281502531</v>
+        <v>84.26687281500854</v>
       </c>
       <c r="K8" t="n">
-        <v>87.4544111971522</v>
+        <v>87.45441119713986</v>
       </c>
       <c r="L8" t="n">
-        <v>87.72260945635024</v>
+        <v>87.72260945635334</v>
       </c>
       <c r="M8" t="n">
-        <v>77.44254317267011</v>
+        <v>77.4425431726649</v>
       </c>
       <c r="N8" t="n">
-        <v>87.60526585327463</v>
+        <v>87.60526585326066</v>
       </c>
       <c r="O8" t="n">
-        <v>86.49182823475847</v>
+        <v>86.49182823474088</v>
       </c>
       <c r="P8" t="n">
-        <v>85.63685276289897</v>
+        <v>85.63685276289837</v>
       </c>
       <c r="Q8" t="n">
-        <v>88.07975470567136</v>
+        <v>88.07975470566313</v>
       </c>
       <c r="R8" t="n">
-        <v>88.27073185076605</v>
+        <v>88.27073185075379</v>
       </c>
       <c r="S8" t="n">
-        <v>86.27875865933314</v>
+        <v>86.27875865932697</v>
       </c>
       <c r="T8" t="n">
-        <v>87.98716059102563</v>
+        <v>87.98716059102411</v>
       </c>
       <c r="U8" t="n">
-        <v>85.04807805795163</v>
+        <v>85.04807805793642</v>
       </c>
       <c r="V8" t="n">
-        <v>53.32218511640983</v>
+        <v>53.32218511640978</v>
       </c>
       <c r="W8" t="n">
-        <v>86.30122357372693</v>
+        <v>86.30122357372045</v>
       </c>
       <c r="X8" t="n">
-        <v>87.17263332198124</v>
+        <v>87.17263332198227</v>
       </c>
       <c r="Y8" t="n">
-        <v>86.1166018935793</v>
+        <v>86.11660189356557</v>
       </c>
       <c r="Z8" t="n">
-        <v>86.37806342001491</v>
+        <v>86.37806341999817</v>
       </c>
       <c r="AA8" t="n">
-        <v>85.90630044863923</v>
+        <v>85.90630044863157</v>
       </c>
       <c r="AB8" t="n">
-        <v>77.45258063568609</v>
+        <v>77.45258063567954</v>
       </c>
     </row>
   </sheetData>
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86.83408604190956</v>
+        <v>86.8340860419096</v>
       </c>
       <c r="C2" t="n">
-        <v>86.40052319157809</v>
+        <v>86.40052319157803</v>
       </c>
       <c r="D2" t="n">
-        <v>86.47401253855935</v>
+        <v>86.47401253855939</v>
       </c>
       <c r="E2" t="n">
-        <v>34.22829329789434</v>
+        <v>34.22829329789429</v>
       </c>
       <c r="F2" t="n">
-        <v>86.53605052645413</v>
+        <v>86.53605052645416</v>
       </c>
       <c r="G2" t="n">
-        <v>86.75843056304956</v>
+        <v>86.7584305630496</v>
       </c>
       <c r="H2" t="n">
-        <v>86.72239947397614</v>
+        <v>86.72239947397611</v>
       </c>
       <c r="I2" t="n">
-        <v>86.88010550852104</v>
+        <v>86.88010550852105</v>
       </c>
       <c r="J2" t="n">
-        <v>86.67970973274683</v>
+        <v>86.67970973274682</v>
       </c>
       <c r="K2" t="n">
-        <v>86.78868720834349</v>
+        <v>86.78868720834353</v>
       </c>
       <c r="L2" t="n">
         <v>86.65225705896805</v>
       </c>
       <c r="M2" t="n">
-        <v>86.65959790380046</v>
+        <v>86.65959790380047</v>
       </c>
       <c r="N2" t="n">
-        <v>86.62937876376331</v>
+        <v>86.62937876376328</v>
       </c>
       <c r="O2" t="n">
-        <v>86.67711625713235</v>
+        <v>86.67711625713233</v>
       </c>
       <c r="P2" t="n">
-        <v>86.73727909071401</v>
+        <v>86.737279090714</v>
       </c>
       <c r="Q2" t="n">
-        <v>86.7432604170537</v>
+        <v>86.74326041705372</v>
       </c>
       <c r="R2" t="n">
-        <v>86.81200450186157</v>
+        <v>86.81200450186147</v>
       </c>
       <c r="S2" t="n">
-        <v>86.69374951559358</v>
+        <v>86.69374951559361</v>
       </c>
       <c r="T2" t="n">
-        <v>86.49825888064318</v>
+        <v>86.49825888064321</v>
       </c>
       <c r="U2" t="n">
-        <v>86.78248412837095</v>
+        <v>86.7824841283709</v>
       </c>
       <c r="V2" t="n">
-        <v>53.10201242267693</v>
+        <v>53.10201242267688</v>
       </c>
       <c r="W2" t="n">
-        <v>87.18568261347453</v>
+        <v>87.18568261347457</v>
       </c>
       <c r="X2" t="n">
         <v>87.6701307528011</v>
       </c>
       <c r="Y2" t="n">
-        <v>87.54284094446393</v>
+        <v>87.54284094446388</v>
       </c>
       <c r="Z2" t="n">
-        <v>86.58861471905567</v>
+        <v>86.58861471905578</v>
       </c>
       <c r="AA2" t="n">
         <v>86.93957987155454</v>
       </c>
       <c r="AB2" t="n">
-        <v>86.55134715292431</v>
+        <v>86.55134715292432</v>
       </c>
     </row>
     <row r="3">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86.91847736692094</v>
+        <v>86.91847736692097</v>
       </c>
       <c r="C3" t="n">
-        <v>86.91847351284864</v>
+        <v>86.91847351284866</v>
       </c>
       <c r="D3" t="n">
-        <v>86.91847736692094</v>
+        <v>86.91847736692097</v>
       </c>
       <c r="E3" t="n">
-        <v>34.02855113970153</v>
+        <v>34.02855113970149</v>
       </c>
       <c r="F3" t="n">
-        <v>86.91847479264889</v>
+        <v>86.91847479264891</v>
       </c>
       <c r="G3" t="n">
-        <v>86.91847613943011</v>
+        <v>86.91847613943014</v>
       </c>
       <c r="H3" t="n">
-        <v>86.91847736692094</v>
+        <v>86.91847736692097</v>
       </c>
       <c r="I3" t="n">
-        <v>86.91847736692094</v>
+        <v>86.91847736692097</v>
       </c>
       <c r="J3" t="n">
-        <v>86.88336889289073</v>
+        <v>86.88336889289083</v>
       </c>
       <c r="K3" t="n">
-        <v>86.91847589723989</v>
+        <v>86.9184758972399</v>
       </c>
       <c r="L3" t="n">
-        <v>86.91847736692094</v>
+        <v>86.91847736692097</v>
       </c>
       <c r="M3" t="n">
-        <v>86.91847069559536</v>
+        <v>86.91847069559539</v>
       </c>
       <c r="N3" t="n">
-        <v>86.91847736692094</v>
+        <v>86.91847736692097</v>
       </c>
       <c r="O3" t="n">
-        <v>86.91847397800012</v>
+        <v>86.91847397800015</v>
       </c>
       <c r="P3" t="n">
-        <v>86.91847098756855</v>
+        <v>86.91847098756857</v>
       </c>
       <c r="Q3" t="n">
-        <v>86.91847732927722</v>
+        <v>86.91847732927725</v>
       </c>
       <c r="R3" t="n">
-        <v>86.91848564466726</v>
+        <v>86.91848564466727</v>
       </c>
       <c r="S3" t="n">
-        <v>86.91847736692094</v>
+        <v>86.91847736692097</v>
       </c>
       <c r="T3" t="n">
-        <v>86.91847248658803</v>
+        <v>86.91847248658804</v>
       </c>
       <c r="U3" t="n">
-        <v>86.91848894763403</v>
+        <v>86.91848894763405</v>
       </c>
       <c r="V3" t="n">
-        <v>52.78374000256662</v>
+        <v>52.78374000256653</v>
       </c>
       <c r="W3" t="n">
-        <v>86.91847736692094</v>
+        <v>86.91847736692097</v>
       </c>
       <c r="X3" t="n">
-        <v>86.91848920934171</v>
+        <v>86.91848920934174</v>
       </c>
       <c r="Y3" t="n">
-        <v>86.91846452171482</v>
+        <v>86.91846452171485</v>
       </c>
       <c r="Z3" t="n">
-        <v>86.91847702684565</v>
+        <v>86.91847702684566</v>
       </c>
       <c r="AA3" t="n">
-        <v>86.91847736692094</v>
+        <v>86.91847736692097</v>
       </c>
       <c r="AB3" t="n">
-        <v>86.91851660286514</v>
+        <v>86.91851660286515</v>
       </c>
     </row>
     <row r="4">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>234.4876222586907</v>
+        <v>234.4876222586905</v>
       </c>
       <c r="C4" t="n">
-        <v>145.7284965294076</v>
+        <v>145.7284965294075</v>
       </c>
       <c r="D4" t="n">
         <v>163.5091022196574</v>
       </c>
       <c r="E4" t="n">
-        <v>82.40760817498948</v>
+        <v>82.40760817498939</v>
       </c>
       <c r="F4" t="n">
-        <v>178.5323848683464</v>
+        <v>178.5323848683462</v>
       </c>
       <c r="G4" t="n">
-        <v>219.8901309133283</v>
+        <v>219.8901309133278</v>
       </c>
       <c r="H4" t="n">
         <v>232.7806751145374</v>
       </c>
       <c r="I4" t="n">
-        <v>267.3962990080381</v>
+        <v>267.3962990080385</v>
       </c>
       <c r="J4" t="n">
-        <v>214.7006213969638</v>
+        <v>214.7006213969636</v>
       </c>
       <c r="K4" t="n">
-        <v>239.2407594355823</v>
+        <v>239.2407594355822</v>
       </c>
       <c r="L4" t="n">
-        <v>200.6383578212073</v>
+        <v>200.6383578212074</v>
       </c>
       <c r="M4" t="n">
-        <v>213.0535768469111</v>
+        <v>213.0535768469108</v>
       </c>
       <c r="N4" t="n">
         <v>196.3720176340113</v>
       </c>
       <c r="O4" t="n">
-        <v>199.1570023400224</v>
+        <v>199.1570023400225</v>
       </c>
       <c r="P4" t="n">
         <v>211.3376182550034</v>
       </c>
       <c r="Q4" t="n">
-        <v>222.7086010578018</v>
+        <v>222.7086010578019</v>
       </c>
       <c r="R4" t="n">
-        <v>252.5861472560333</v>
+        <v>252.586147256033</v>
       </c>
       <c r="S4" t="n">
-        <v>203.3611015080733</v>
+        <v>203.3611015080731</v>
       </c>
       <c r="T4" t="n">
-        <v>166.4938908807607</v>
+        <v>166.4938908807606</v>
       </c>
       <c r="U4" t="n">
-        <v>228.8859014877047</v>
+        <v>228.8859014877041</v>
       </c>
       <c r="V4" t="n">
-        <v>207.8671615075367</v>
+        <v>207.8671615075366</v>
       </c>
       <c r="W4" t="n">
-        <v>333.8014541201188</v>
+        <v>333.8014541201185</v>
       </c>
       <c r="X4" t="n">
-        <v>451.7311295587426</v>
+        <v>451.731129558743</v>
       </c>
       <c r="Y4" t="n">
-        <v>429.0650893230859</v>
+        <v>429.0650893230858</v>
       </c>
       <c r="Z4" t="n">
-        <v>178.4005125489668</v>
+        <v>178.4005125489669</v>
       </c>
       <c r="AA4" t="n">
-        <v>273.3712623704567</v>
+        <v>273.3712623704565</v>
       </c>
       <c r="AB4" t="n">
-        <v>187.3056558001928</v>
+        <v>187.3056558001927</v>
       </c>
     </row>
     <row r="5">
@@ -1625,79 +1625,79 @@
         <v>122.8176857756397</v>
       </c>
       <c r="C5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="D5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="E5" t="n">
         <v>150.3140106865148</v>
       </c>
       <c r="F5" t="n">
-        <v>131.9799013837061</v>
+        <v>131.979901383706</v>
       </c>
       <c r="G5" t="n">
-        <v>193.82468562388</v>
+        <v>193.8246856238799</v>
       </c>
       <c r="H5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="I5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="J5" t="n">
-        <v>181.4708606237402</v>
+        <v>181.47086062374</v>
       </c>
       <c r="K5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="L5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="M5" t="n">
-        <v>181.6296431397733</v>
+        <v>181.6296431397729</v>
       </c>
       <c r="N5" t="n">
-        <v>196.3720176340113</v>
+        <v>136.0405371577702</v>
       </c>
       <c r="O5" t="n">
-        <v>148.5688193280011</v>
+        <v>148.5688193280012</v>
       </c>
       <c r="P5" t="n">
-        <v>145.4978346420314</v>
+        <v>145.4978346420312</v>
       </c>
       <c r="Q5" t="n">
-        <v>111.2597938347592</v>
+        <v>111.2597938347593</v>
       </c>
       <c r="R5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="S5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="T5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="U5" t="n">
-        <v>152.9184007822152</v>
+        <v>152.9184007822151</v>
       </c>
       <c r="V5" t="n">
-        <v>164.5416276473932</v>
+        <v>164.5416276473931</v>
       </c>
       <c r="W5" t="n">
-        <v>181.6412013798179</v>
+        <v>181.6412013798175</v>
       </c>
       <c r="X5" t="n">
-        <v>116.6500265915544</v>
+        <v>116.6500265915546</v>
       </c>
       <c r="Y5" t="n">
-        <v>240.0949218276506</v>
+        <v>240.0949218276505</v>
       </c>
       <c r="Z5" t="n">
         <v>121.7252234730307</v>
       </c>
       <c r="AA5" t="n">
-        <v>181.6296431397722</v>
+        <v>181.6296431397721</v>
       </c>
       <c r="AB5" t="n">
         <v>243.0636503874238</v>
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>99.14793267733754</v>
+        <v>99.14793267733751</v>
       </c>
       <c r="C6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="D6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="E6" t="n">
         <v>113.8029036084357</v>
       </c>
       <c r="F6" t="n">
-        <v>74.27971199282814</v>
+        <v>74.27971199282808</v>
       </c>
       <c r="G6" t="n">
-        <v>118.2000559468517</v>
+        <v>118.2000559468515</v>
       </c>
       <c r="H6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="I6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="J6" t="n">
-        <v>118.0412680627937</v>
+        <v>118.0412680627936</v>
       </c>
       <c r="K6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="L6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="M6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="N6" t="n">
-        <v>196.3720176340113</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="O6" t="n">
-        <v>124.5139046517716</v>
+        <v>124.5139046517715</v>
       </c>
       <c r="P6" t="n">
-        <v>125.8870584176653</v>
+        <v>125.8870584176652</v>
       </c>
       <c r="Q6" t="n">
-        <v>118.2000559468517</v>
+        <v>118.2000559468515</v>
       </c>
       <c r="R6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="S6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="T6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="U6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="V6" t="n">
-        <v>139.1784887864063</v>
+        <v>139.1784887864062</v>
       </c>
       <c r="W6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="X6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="Y6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="Z6" t="n">
         <v>106.7133197962382</v>
       </c>
       <c r="AA6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
       <c r="AB6" t="n">
-        <v>118.2000505788259</v>
+        <v>118.2000505788257</v>
       </c>
     </row>
     <row r="7">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.11363370487368</v>
+        <v>83.11363370487364</v>
       </c>
       <c r="C7" t="n">
-        <v>85.71181060558487</v>
+        <v>85.71181060558494</v>
       </c>
       <c r="D7" t="n">
-        <v>85.28286959720154</v>
+        <v>85.28286959720155</v>
       </c>
       <c r="E7" t="n">
-        <v>33.23040442436344</v>
+        <v>33.2304044243634</v>
       </c>
       <c r="F7" t="n">
-        <v>84.92970002612017</v>
+        <v>84.92970002612023</v>
       </c>
       <c r="G7" t="n">
-        <v>83.56563868409498</v>
+        <v>83.56563868409501</v>
       </c>
       <c r="H7" t="n">
-        <v>83.84946185250088</v>
+        <v>83.84946185250091</v>
       </c>
       <c r="I7" t="n">
         <v>82.91186184555883</v>
       </c>
       <c r="J7" t="n">
-        <v>83.80730913788352</v>
+        <v>83.80730913788348</v>
       </c>
       <c r="K7" t="n">
-        <v>83.43458119315406</v>
+        <v>83.43458119315416</v>
       </c>
       <c r="L7" t="n">
         <v>84.21305773796735</v>
       </c>
       <c r="M7" t="n">
-        <v>84.2064521971698</v>
+        <v>84.20645219716988</v>
       </c>
       <c r="N7" t="n">
-        <v>84.36163467880894</v>
+        <v>84.36163467880904</v>
       </c>
       <c r="O7" t="n">
-        <v>84.0442159712604</v>
+        <v>84.04421597126046</v>
       </c>
       <c r="P7" t="n">
         <v>83.6829366624259</v>
       </c>
       <c r="Q7" t="n">
-        <v>83.69727568177569</v>
+        <v>83.69727568177571</v>
       </c>
       <c r="R7" t="n">
-        <v>83.31775203928234</v>
+        <v>83.31775203928224</v>
       </c>
       <c r="S7" t="n">
-        <v>83.95798676986719</v>
+        <v>83.95798676986718</v>
       </c>
       <c r="T7" t="n">
-        <v>85.1420074431025</v>
+        <v>85.14200744310256</v>
       </c>
       <c r="U7" t="n">
-        <v>83.43968711840969</v>
+        <v>83.43968711840975</v>
       </c>
       <c r="V7" t="n">
-        <v>49.75485155186193</v>
+        <v>49.75485155186185</v>
       </c>
       <c r="W7" t="n">
-        <v>81.06946271440503</v>
+        <v>81.06946271440499</v>
       </c>
       <c r="X7" t="n">
-        <v>78.26822712642473</v>
+        <v>78.26822712642486</v>
       </c>
       <c r="Y7" t="n">
         <v>78.97444593565478</v>
       </c>
       <c r="Z7" t="n">
-        <v>84.57669190583192</v>
+        <v>84.57669190583189</v>
       </c>
       <c r="AA7" t="n">
-        <v>82.5256209753698</v>
+        <v>82.52562097536979</v>
       </c>
       <c r="AB7" t="n">
-        <v>84.83057707885756</v>
+        <v>84.83057707885759</v>
       </c>
     </row>
     <row r="8">
@@ -1892,79 +1892,79 @@
         <v>85.85148772336656</v>
       </c>
       <c r="D8" t="n">
-        <v>85.72980579096439</v>
+        <v>85.72980579096441</v>
       </c>
       <c r="E8" t="n">
-        <v>33.86513399887284</v>
+        <v>33.86513399887279</v>
       </c>
       <c r="F8" t="n">
-        <v>85.63115166983442</v>
+        <v>85.63115166983444</v>
       </c>
       <c r="G8" t="n">
-        <v>85.23287883601303</v>
+        <v>85.23287883601306</v>
       </c>
       <c r="H8" t="n">
-        <v>85.3259876345429</v>
+        <v>85.32598763454287</v>
       </c>
       <c r="I8" t="n">
-        <v>85.0570826779753</v>
+        <v>85.05708267797537</v>
       </c>
       <c r="J8" t="n">
-        <v>85.28009274139777</v>
+        <v>85.28009274139778</v>
       </c>
       <c r="K8" t="n">
-        <v>85.20350401547091</v>
+        <v>85.20350401547084</v>
       </c>
       <c r="L8" t="n">
-        <v>85.42128250613339</v>
+        <v>85.42128250613335</v>
       </c>
       <c r="M8" t="n">
-        <v>85.42562084432674</v>
+        <v>85.42562084432682</v>
       </c>
       <c r="N8" t="n">
-        <v>85.46600719249811</v>
+        <v>85.4660071924981</v>
       </c>
       <c r="O8" t="n">
-        <v>85.36931970434908</v>
+        <v>85.36931970434914</v>
       </c>
       <c r="P8" t="n">
-        <v>85.26510066173799</v>
+        <v>85.26510066173807</v>
       </c>
       <c r="Q8" t="n">
-        <v>85.27760340207993</v>
+        <v>85.27760340208005</v>
       </c>
       <c r="R8" t="n">
-        <v>85.17365923655429</v>
+        <v>85.17365923655419</v>
       </c>
       <c r="S8" t="n">
-        <v>85.34671685941034</v>
+        <v>85.34671685941036</v>
       </c>
       <c r="T8" t="n">
-        <v>85.68996162459915</v>
+        <v>85.68996162459916</v>
       </c>
       <c r="U8" t="n">
         <v>85.19961820979023</v>
       </c>
       <c r="V8" t="n">
-        <v>51.72385852511154</v>
+        <v>51.72385852511148</v>
       </c>
       <c r="W8" t="n">
-        <v>84.52436230687606</v>
+        <v>84.52436230687609</v>
       </c>
       <c r="X8" t="n">
-        <v>83.73423393832432</v>
+        <v>83.73423393832434</v>
       </c>
       <c r="Y8" t="n">
-        <v>83.92828717172149</v>
+        <v>83.92828717172146</v>
       </c>
       <c r="Z8" t="n">
         <v>85.52309502616805</v>
       </c>
       <c r="AA8" t="n">
-        <v>84.94081621419615</v>
+        <v>84.94081621419609</v>
       </c>
       <c r="AB8" t="n">
-        <v>85.60132801563242</v>
+        <v>85.60132801563246</v>
       </c>
     </row>
   </sheetData>
@@ -2130,7 +2130,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.9898634172806</v>
+        <v>89.9898634172808</v>
       </c>
       <c r="C2" t="n">
         <v>89.06338261011456</v>
@@ -2139,73 +2139,73 @@
         <v>90.15128728073552</v>
       </c>
       <c r="E2" t="n">
-        <v>35.95948053270202</v>
+        <v>35.9594805327021</v>
       </c>
       <c r="F2" t="n">
-        <v>89.881034246333</v>
+        <v>89.88103424633302</v>
       </c>
       <c r="G2" t="n">
-        <v>93.59604217459759</v>
+        <v>93.59604217459773</v>
       </c>
       <c r="H2" t="n">
-        <v>89.1258030037712</v>
+        <v>89.12580300377118</v>
       </c>
       <c r="I2" t="n">
-        <v>89.45254311301147</v>
+        <v>89.45254311301149</v>
       </c>
       <c r="J2" t="n">
-        <v>91.55200939021388</v>
+        <v>91.55200939021397</v>
       </c>
       <c r="K2" t="n">
-        <v>89.8537390619481</v>
+        <v>89.85373906194813</v>
       </c>
       <c r="L2" t="n">
-        <v>89.54866855060261</v>
+        <v>89.54866855060277</v>
       </c>
       <c r="M2" t="n">
-        <v>95.4377957787145</v>
+        <v>95.43779577871453</v>
       </c>
       <c r="N2" t="n">
-        <v>89.65908428216228</v>
+        <v>89.65908428216227</v>
       </c>
       <c r="O2" t="n">
-        <v>90.27516096651729</v>
+        <v>90.27516096651732</v>
       </c>
       <c r="P2" t="n">
-        <v>91.27737329083736</v>
+        <v>91.27737329083737</v>
       </c>
       <c r="Q2" t="n">
-        <v>89.52194123728259</v>
+        <v>89.52194123728263</v>
       </c>
       <c r="R2" t="n">
-        <v>89.21191171802988</v>
+        <v>89.21191171802985</v>
       </c>
       <c r="S2" t="n">
-        <v>90.50359008792586</v>
+        <v>90.50359008792583</v>
       </c>
       <c r="T2" t="n">
         <v>89.45635677811914</v>
       </c>
       <c r="U2" t="n">
-        <v>90.8808739668128</v>
+        <v>90.88087396681277</v>
       </c>
       <c r="V2" t="n">
-        <v>55.4366060833204</v>
+        <v>55.43660608332041</v>
       </c>
       <c r="W2" t="n">
-        <v>90.41437233969259</v>
+        <v>90.41437233969262</v>
       </c>
       <c r="X2" t="n">
-        <v>90.0889103269059</v>
+        <v>90.08891032690603</v>
       </c>
       <c r="Y2" t="n">
         <v>90.51235785330242</v>
       </c>
       <c r="Z2" t="n">
-        <v>90.21905973453568</v>
+        <v>90.21905973453585</v>
       </c>
       <c r="AA2" t="n">
-        <v>89.94942885297213</v>
+        <v>89.9494288529722</v>
       </c>
       <c r="AB2" t="n">
         <v>95.66665173790545</v>
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.5629611047639</v>
+        <v>89.56296110476391</v>
       </c>
       <c r="C3" t="n">
-        <v>89.56295742053847</v>
+        <v>89.56295742053848</v>
       </c>
       <c r="D3" t="n">
-        <v>89.5629611047639</v>
+        <v>89.56296110476391</v>
       </c>
       <c r="E3" t="n">
-        <v>35.51705662313498</v>
+        <v>35.517056623135</v>
       </c>
       <c r="F3" t="n">
-        <v>89.56295973057983</v>
+        <v>89.56295973057985</v>
       </c>
       <c r="G3" t="n">
-        <v>89.56296068228467</v>
+        <v>89.56296068228468</v>
       </c>
       <c r="H3" t="n">
-        <v>89.5629611047639</v>
+        <v>89.56296110476391</v>
       </c>
       <c r="I3" t="n">
-        <v>89.5629611047639</v>
+        <v>89.56296110476391</v>
       </c>
       <c r="J3" t="n">
-        <v>89.41442203198386</v>
+        <v>89.41442203198392</v>
       </c>
       <c r="K3" t="n">
-        <v>89.56296029652208</v>
+        <v>89.56296029652209</v>
       </c>
       <c r="L3" t="n">
-        <v>89.5629611047639</v>
+        <v>89.56296110476391</v>
       </c>
       <c r="M3" t="n">
-        <v>89.56296015318817</v>
+        <v>89.5629601531882</v>
       </c>
       <c r="N3" t="n">
-        <v>89.5629611047639</v>
+        <v>89.56296110476391</v>
       </c>
       <c r="O3" t="n">
-        <v>89.56295845195208</v>
+        <v>89.5629584519521</v>
       </c>
       <c r="P3" t="n">
-        <v>89.56296044075164</v>
+        <v>89.56296044075165</v>
       </c>
       <c r="Q3" t="n">
-        <v>89.56296106712017</v>
+        <v>89.5629610671202</v>
       </c>
       <c r="R3" t="n">
-        <v>89.56296095534874</v>
+        <v>89.56296095534877</v>
       </c>
       <c r="S3" t="n">
-        <v>89.5629611047639</v>
+        <v>89.56296110476391</v>
       </c>
       <c r="T3" t="n">
-        <v>89.56295995084361</v>
+        <v>89.56295995084363</v>
       </c>
       <c r="U3" t="n">
-        <v>89.56296371020642</v>
+        <v>89.56296371020643</v>
       </c>
       <c r="V3" t="n">
-        <v>54.8578653940971</v>
+        <v>54.85786539409713</v>
       </c>
       <c r="W3" t="n">
-        <v>89.5629611047639</v>
+        <v>89.56296110476391</v>
       </c>
       <c r="X3" t="n">
-        <v>89.56296326886461</v>
+        <v>89.56296326886464</v>
       </c>
       <c r="Y3" t="n">
-        <v>89.5629550136694</v>
+        <v>89.56295501366942</v>
       </c>
       <c r="Z3" t="n">
-        <v>89.56296089921236</v>
+        <v>89.56296089921238</v>
       </c>
       <c r="AA3" t="n">
-        <v>89.5629611047639</v>
+        <v>89.56296110476391</v>
       </c>
       <c r="AB3" t="n">
-        <v>89.56300034070809</v>
+        <v>89.5630003407081</v>
       </c>
     </row>
     <row r="4">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>386.5151927164824</v>
+        <v>386.5151927164866</v>
       </c>
       <c r="C4" t="n">
-        <v>164.6282376411488</v>
+        <v>164.6282376411489</v>
       </c>
       <c r="D4" t="n">
-        <v>470.6301852549633</v>
+        <v>470.6301852549626</v>
       </c>
       <c r="E4" t="n">
-        <v>146.4075578360004</v>
+        <v>146.4075578360157</v>
       </c>
       <c r="F4" t="n">
-        <v>397.4389238935503</v>
+        <v>397.4389238935516</v>
       </c>
       <c r="G4" t="n">
-        <v>1317.761884344767</v>
+        <v>1317.761884344769</v>
       </c>
       <c r="H4" t="n">
-        <v>185.7899444777282</v>
+        <v>185.7899444777286</v>
       </c>
       <c r="I4" t="n">
-        <v>274.0745263849897</v>
+        <v>274.0745263849902</v>
       </c>
       <c r="J4" t="n">
-        <v>855.344304266303</v>
+        <v>855.3443042662859</v>
       </c>
       <c r="K4" t="n">
-        <v>375.8669951933322</v>
+        <v>375.8669951933342</v>
       </c>
       <c r="L4" t="n">
-        <v>286.4561288362488</v>
+        <v>286.4561288363336</v>
       </c>
       <c r="M4" t="n">
-        <v>1985.90619759301</v>
+        <v>1985.906197593004</v>
       </c>
       <c r="N4" t="n">
-        <v>323.4482662573181</v>
+        <v>323.4482662573197</v>
       </c>
       <c r="O4" t="n">
-        <v>451.9262062234799</v>
+        <v>451.92620622348</v>
       </c>
       <c r="P4" t="n">
-        <v>718.6330873376768</v>
+        <v>718.6330873376817</v>
       </c>
       <c r="Q4" t="n">
-        <v>286.9701704555177</v>
+        <v>286.9701704555259</v>
       </c>
       <c r="R4" t="n">
-        <v>206.7045401863865</v>
+        <v>206.7045401863863</v>
       </c>
       <c r="S4" t="n">
-        <v>525.3402656604136</v>
+        <v>525.3402656604173</v>
       </c>
       <c r="T4" t="n">
-        <v>273.6409748266918</v>
+        <v>273.6409748266982</v>
       </c>
       <c r="U4" t="n">
-        <v>636.5623525217532</v>
+        <v>636.5623525217536</v>
       </c>
       <c r="V4" t="n">
-        <v>292.9579210358995</v>
+        <v>292.9579210358994</v>
       </c>
       <c r="W4" t="n">
-        <v>524.2947559198639</v>
+        <v>524.2947559198636</v>
       </c>
       <c r="X4" t="n">
-        <v>447.4808031478282</v>
+        <v>447.4808031478399</v>
       </c>
       <c r="Y4" t="n">
-        <v>549.1449149997601</v>
+        <v>549.1449149997597</v>
       </c>
       <c r="Z4" t="n">
-        <v>450.7919101751453</v>
+        <v>450.7919101751506</v>
       </c>
       <c r="AA4" t="n">
-        <v>398.4302589398262</v>
+        <v>398.4302589398342</v>
       </c>
       <c r="AB4" t="n">
-        <v>2138.840619478518</v>
+        <v>2138.840619478528</v>
       </c>
     </row>
     <row r="5">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>137.2567511726855</v>
+        <v>137.2567511726852</v>
       </c>
       <c r="C5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525994</v>
       </c>
       <c r="D5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525994</v>
       </c>
       <c r="E5" t="n">
-        <v>168.7975924763209</v>
+        <v>168.7975924763208</v>
       </c>
       <c r="F5" t="n">
-        <v>147.7666643851543</v>
+        <v>147.7666643851541</v>
       </c>
       <c r="G5" t="n">
-        <v>218.7083822866542</v>
+        <v>218.7083822866536</v>
       </c>
       <c r="H5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525994</v>
       </c>
       <c r="I5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525994</v>
       </c>
       <c r="J5" t="n">
-        <v>204.5368156280959</v>
+        <v>204.5368156280954</v>
       </c>
       <c r="K5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525994</v>
       </c>
       <c r="L5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525994</v>
       </c>
       <c r="M5" t="n">
-        <v>204.7195346526041</v>
+        <v>204.7195346526039</v>
       </c>
       <c r="N5" t="n">
-        <v>323.4482662573181</v>
+        <v>152.4245911789442</v>
       </c>
       <c r="O5" t="n">
-        <v>166.795695717168</v>
+        <v>166.7956957171678</v>
       </c>
       <c r="P5" t="n">
         <v>163.2729907400331</v>
       </c>
       <c r="Q5" t="n">
-        <v>123.9987744549021</v>
+        <v>123.9987744549018</v>
       </c>
       <c r="R5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525993</v>
       </c>
       <c r="S5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525994</v>
       </c>
       <c r="T5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525994</v>
       </c>
       <c r="U5" t="n">
-        <v>171.7762731446671</v>
+        <v>171.7762731446667</v>
       </c>
       <c r="V5" t="n">
-        <v>185.1035376982172</v>
+        <v>185.1035376982168</v>
       </c>
       <c r="W5" t="n">
-        <v>204.7327930268334</v>
+        <v>204.7327930268331</v>
       </c>
       <c r="X5" t="n">
-        <v>130.181872614024</v>
+        <v>130.1818726140235</v>
       </c>
       <c r="Y5" t="n">
-        <v>271.7695964709925</v>
+        <v>271.7695964709922</v>
       </c>
       <c r="Z5" t="n">
         <v>136.0035953337554</v>
       </c>
       <c r="AA5" t="n">
-        <v>204.7195346525995</v>
+        <v>204.7195346525994</v>
       </c>
       <c r="AB5" t="n">
-        <v>275.1900531475079</v>
+        <v>275.1900531475077</v>
       </c>
     </row>
     <row r="6">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>131.0093068124564</v>
+        <v>131.0093068124557</v>
       </c>
       <c r="C6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="D6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="E6" t="n">
-        <v>152.2667646233155</v>
+        <v>152.2667646233157</v>
       </c>
       <c r="F6" t="n">
-        <v>94.93723580546796</v>
+        <v>94.93723580546771</v>
       </c>
       <c r="G6" t="n">
-        <v>158.6449608518313</v>
+        <v>158.6449608518314</v>
       </c>
       <c r="H6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="I6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="J6" t="n">
-        <v>158.4622473423443</v>
+        <v>158.4622473423433</v>
       </c>
       <c r="K6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="L6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="M6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="N6" t="n">
-        <v>323.4482662573181</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="O6" t="n">
-        <v>167.8033804147107</v>
+        <v>167.8033804147106</v>
       </c>
       <c r="P6" t="n">
-        <v>169.7951795375924</v>
+        <v>169.795179537592</v>
       </c>
       <c r="Q6" t="n">
-        <v>158.6449608518313</v>
+        <v>158.6449608518314</v>
       </c>
       <c r="R6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="S6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="T6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="U6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="V6" t="n">
-        <v>189.3756708274952</v>
+        <v>189.3756708274951</v>
       </c>
       <c r="W6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="X6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="Y6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="Z6" t="n">
-        <v>141.9831189243289</v>
+        <v>141.9831189243287</v>
       </c>
       <c r="AA6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
       <c r="AB6" t="n">
-        <v>158.644966366848</v>
+        <v>158.6449663668472</v>
       </c>
     </row>
     <row r="7">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82.57450165420114</v>
+        <v>82.5745016542007</v>
       </c>
       <c r="C7" t="n">
-        <v>88.10873772195686</v>
+        <v>88.10873772195689</v>
       </c>
       <c r="D7" t="n">
-        <v>81.73811429662985</v>
+        <v>81.73811429662992</v>
       </c>
       <c r="E7" t="n">
-        <v>33.24708146296462</v>
+        <v>33.2470814629642</v>
       </c>
       <c r="F7" t="n">
         <v>83.35206877167312</v>
       </c>
       <c r="G7" t="n">
-        <v>61.13658871491659</v>
+        <v>61.13658871491667</v>
       </c>
       <c r="H7" t="n">
-        <v>87.7578768435107</v>
+        <v>87.75787684351076</v>
       </c>
       <c r="I7" t="n">
-        <v>85.83819910302064</v>
+        <v>85.83819910302067</v>
       </c>
       <c r="J7" t="n">
-        <v>72.34416220266247</v>
+        <v>72.34416220266246</v>
       </c>
       <c r="K7" t="n">
-        <v>83.47225233742509</v>
+        <v>83.47225233742516</v>
       </c>
       <c r="L7" t="n">
-        <v>85.22724338113863</v>
+        <v>85.22724338113727</v>
       </c>
       <c r="M7" t="n">
-        <v>50.91979668135454</v>
+        <v>50.91979668135457</v>
       </c>
       <c r="N7" t="n">
-        <v>84.59989314912713</v>
+        <v>84.59989314912721</v>
       </c>
       <c r="O7" t="n">
-        <v>80.86763024616175</v>
+        <v>80.86763024616187</v>
       </c>
       <c r="P7" t="n">
-        <v>74.88570794339114</v>
+        <v>74.88570794339117</v>
       </c>
       <c r="Q7" t="n">
-        <v>85.41369166940066</v>
+        <v>85.41369166940068</v>
       </c>
       <c r="R7" t="n">
-        <v>87.25007518134468</v>
+        <v>87.25007518134474</v>
       </c>
       <c r="S7" t="n">
-        <v>79.54956692646763</v>
+        <v>79.54956692646738</v>
       </c>
       <c r="T7" t="n">
-        <v>85.81113281939675</v>
+        <v>85.81113281939665</v>
       </c>
       <c r="U7" t="n">
-        <v>77.33918959940712</v>
+        <v>77.33918959940715</v>
       </c>
       <c r="V7" t="n">
         <v>50.16094276845764</v>
       </c>
       <c r="W7" t="n">
-        <v>80.1252730819388</v>
+        <v>80.12527308193881</v>
       </c>
       <c r="X7" t="n">
-        <v>82.09622143162204</v>
+        <v>82.0962214316219</v>
       </c>
       <c r="Y7" t="n">
-        <v>79.56325838032187</v>
+        <v>79.56325838032193</v>
       </c>
       <c r="Z7" t="n">
-        <v>81.22033714741715</v>
+        <v>81.22033714741706</v>
       </c>
       <c r="AA7" t="n">
-        <v>82.87489225285026</v>
+        <v>82.87489225285027</v>
       </c>
       <c r="AB7" t="n">
-        <v>49.44108559604516</v>
+        <v>49.44108559604517</v>
       </c>
     </row>
     <row r="8">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86.81009209637571</v>
+        <v>86.81009209637574</v>
       </c>
       <c r="C8" t="n">
-        <v>88.40170801293675</v>
+        <v>88.40170801293674</v>
       </c>
       <c r="D8" t="n">
-        <v>86.59095704672737</v>
+        <v>86.59095704672733</v>
       </c>
       <c r="E8" t="n">
-        <v>34.92663460084286</v>
+        <v>34.92663460084281</v>
       </c>
       <c r="F8" t="n">
-        <v>87.05505906709539</v>
+        <v>87.0550590670954</v>
       </c>
       <c r="G8" t="n">
-        <v>80.66195233997269</v>
+        <v>80.66195233997273</v>
       </c>
       <c r="H8" t="n">
-        <v>88.30448391243878</v>
+        <v>88.3044839124388</v>
       </c>
       <c r="I8" t="n">
-        <v>87.75776453210611</v>
+        <v>87.75776453210614</v>
       </c>
       <c r="J8" t="n">
-        <v>83.78498676818236</v>
+        <v>83.78498676818239</v>
       </c>
       <c r="K8" t="n">
-        <v>87.08244753062435</v>
+        <v>87.08244753062438</v>
       </c>
       <c r="L8" t="n">
-        <v>87.57590316924048</v>
+        <v>87.57590316924056</v>
       </c>
       <c r="M8" t="n">
-        <v>77.85503325057502</v>
+        <v>77.85503325057509</v>
       </c>
       <c r="N8" t="n">
-        <v>87.40087254598842</v>
+        <v>87.40087254598848</v>
       </c>
       <c r="O8" t="n">
-        <v>86.31875892251578</v>
+        <v>86.31875892251584</v>
       </c>
       <c r="P8" t="n">
-        <v>84.59917663090982</v>
+        <v>84.59917663090989</v>
       </c>
       <c r="Q8" t="n">
-        <v>87.63401043838319</v>
+        <v>87.63401043838321</v>
       </c>
       <c r="R8" t="n">
-        <v>88.15954132012843</v>
+        <v>88.15954132012837</v>
       </c>
       <c r="S8" t="n">
-        <v>85.94746382600722</v>
+        <v>85.94746382600725</v>
       </c>
       <c r="T8" t="n">
-        <v>87.74926347694712</v>
+        <v>87.74926347694708</v>
       </c>
       <c r="U8" t="n">
-        <v>85.31901779154236</v>
+        <v>85.31901779154231</v>
       </c>
       <c r="V8" t="n">
-        <v>53.29949132045016</v>
+        <v>53.29949132045014</v>
       </c>
       <c r="W8" t="n">
-        <v>86.12019421317996</v>
+        <v>86.12019421317991</v>
       </c>
       <c r="X8" t="n">
-        <v>86.69151899586613</v>
+        <v>86.69151899586603</v>
       </c>
       <c r="Y8" t="n">
-        <v>85.96246401798693</v>
+        <v>85.96246401798695</v>
       </c>
       <c r="Z8" t="n">
-        <v>86.42313934110449</v>
+        <v>86.42313934110462</v>
       </c>
       <c r="AA8" t="n">
-        <v>86.90633621174059</v>
+        <v>86.90633621174067</v>
       </c>
       <c r="AB8" t="n">
-        <v>77.41105266812805</v>
+        <v>77.41105266812799</v>
       </c>
     </row>
   </sheetData>
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.79176685787188</v>
+        <v>89.79176685787203</v>
       </c>
       <c r="C2" t="n">
-        <v>88.86526563166689</v>
+        <v>88.86526563166694</v>
       </c>
       <c r="D2" t="n">
-        <v>90.1765386785161</v>
+        <v>90.17653867851621</v>
       </c>
       <c r="E2" t="n">
         <v>35.78184945075697</v>
       </c>
       <c r="F2" t="n">
-        <v>90.0770814592198</v>
+        <v>90.07708145921984</v>
       </c>
       <c r="G2" t="n">
-        <v>93.12135519719884</v>
+        <v>93.12135519719888</v>
       </c>
       <c r="H2" t="n">
-        <v>88.94584718926347</v>
+        <v>88.94584718926359</v>
       </c>
       <c r="I2" t="n">
         <v>89.70156231591015</v>
       </c>
       <c r="J2" t="n">
-        <v>91.23900899299875</v>
+        <v>91.23900899299886</v>
       </c>
       <c r="K2" t="n">
-        <v>89.79705095819878</v>
+        <v>89.79705095819882</v>
       </c>
       <c r="L2" t="n">
-        <v>89.28417081161571</v>
+        <v>89.28417081161577</v>
       </c>
       <c r="M2" t="n">
-        <v>94.45237684049731</v>
+        <v>94.45237684049741</v>
       </c>
       <c r="N2" t="n">
-        <v>89.30581621544393</v>
+        <v>89.305816215444</v>
       </c>
       <c r="O2" t="n">
-        <v>89.95343899269113</v>
+        <v>89.95343899269106</v>
       </c>
       <c r="P2" t="n">
-        <v>91.05264054820073</v>
+        <v>91.05264054820078</v>
       </c>
       <c r="Q2" t="n">
-        <v>89.43088016651282</v>
+        <v>89.43088016651294</v>
       </c>
       <c r="R2" t="n">
-        <v>88.97148561338018</v>
+        <v>88.97148561338024</v>
       </c>
       <c r="S2" t="n">
-        <v>90.20216620557872</v>
+        <v>90.20216620557879</v>
       </c>
       <c r="T2" t="n">
         <v>89.27302178112168</v>
       </c>
       <c r="U2" t="n">
-        <v>89.67286331762077</v>
+        <v>89.67286331762087</v>
       </c>
       <c r="V2" t="n">
-        <v>55.57657922116925</v>
+        <v>55.57657922116934</v>
       </c>
       <c r="W2" t="n">
-        <v>90.03671867527927</v>
+        <v>90.03671867527932</v>
       </c>
       <c r="X2" t="n">
-        <v>90.15893406950345</v>
+        <v>90.1589340695035</v>
       </c>
       <c r="Y2" t="n">
-        <v>91.43808493143098</v>
+        <v>91.43808493143101</v>
       </c>
       <c r="Z2" t="n">
-        <v>90.03259622952561</v>
+        <v>90.03259622952568</v>
       </c>
       <c r="AA2" t="n">
-        <v>89.51005540883436</v>
+        <v>89.51005540883442</v>
       </c>
       <c r="AB2" t="n">
-        <v>95.01511286759059</v>
+        <v>95.01511286759066</v>
       </c>
     </row>
     <row r="3">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.37403602161812</v>
+        <v>89.37403602161808</v>
       </c>
       <c r="C3" t="n">
-        <v>89.37403215241248</v>
+        <v>89.37403215241245</v>
       </c>
       <c r="D3" t="n">
-        <v>89.37403602161812</v>
+        <v>89.37403602161808</v>
       </c>
       <c r="E3" t="n">
-        <v>35.37790436536099</v>
+        <v>35.37790436536103</v>
       </c>
       <c r="F3" t="n">
-        <v>89.37403408209319</v>
+        <v>89.37403408209316</v>
       </c>
       <c r="G3" t="n">
-        <v>89.37403522791872</v>
+        <v>89.37403522791868</v>
       </c>
       <c r="H3" t="n">
-        <v>89.37403602161812</v>
+        <v>89.37403602161808</v>
       </c>
       <c r="I3" t="n">
-        <v>89.37403602161812</v>
+        <v>89.37403602161808</v>
       </c>
       <c r="J3" t="n">
-        <v>89.24043671146408</v>
+        <v>89.24043671146414</v>
       </c>
       <c r="K3" t="n">
-        <v>89.37403487518424</v>
+        <v>89.37403487518421</v>
       </c>
       <c r="L3" t="n">
-        <v>89.37403602161812</v>
+        <v>89.37403602161808</v>
       </c>
       <c r="M3" t="n">
-        <v>89.37403344771597</v>
+        <v>89.37403344771593</v>
       </c>
       <c r="N3" t="n">
-        <v>89.37403602161812</v>
+        <v>89.37403602161808</v>
       </c>
       <c r="O3" t="n">
-        <v>89.37403305924195</v>
+        <v>89.37403305924191</v>
       </c>
       <c r="P3" t="n">
-        <v>89.37403568663768</v>
+        <v>89.37403568663764</v>
       </c>
       <c r="Q3" t="n">
-        <v>89.37403598397441</v>
+        <v>89.37403598397437</v>
       </c>
       <c r="R3" t="n">
-        <v>89.37404031576085</v>
+        <v>89.37404031576081</v>
       </c>
       <c r="S3" t="n">
-        <v>89.37403602161812</v>
+        <v>89.37403602161808</v>
       </c>
       <c r="T3" t="n">
-        <v>89.37403262333349</v>
+        <v>89.37403262333345</v>
       </c>
       <c r="U3" t="n">
-        <v>89.37404009489802</v>
+        <v>89.37404009489798</v>
       </c>
       <c r="V3" t="n">
-        <v>54.78386213477823</v>
+        <v>54.78386213477818</v>
       </c>
       <c r="W3" t="n">
-        <v>89.37403602161812</v>
+        <v>89.37403602161808</v>
       </c>
       <c r="X3" t="n">
-        <v>89.37406185306808</v>
+        <v>89.37406185306804</v>
       </c>
       <c r="Y3" t="n">
-        <v>89.37402870036441</v>
+        <v>89.37402870036436</v>
       </c>
       <c r="Z3" t="n">
-        <v>89.374035675992</v>
+        <v>89.37403567599196</v>
       </c>
       <c r="AA3" t="n">
-        <v>89.37403602161812</v>
+        <v>89.37403602161808</v>
       </c>
       <c r="AB3" t="n">
-        <v>89.37407525756231</v>
+        <v>89.37407525756228</v>
       </c>
     </row>
     <row r="4">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>362.1148161128706</v>
+        <v>362.1148161128714</v>
       </c>
       <c r="C4" t="n">
-        <v>155.8653086161102</v>
+        <v>155.8653086161101</v>
       </c>
       <c r="D4" t="n">
-        <v>494.2303785584392</v>
+        <v>494.2303785584402</v>
       </c>
       <c r="E4" t="n">
-        <v>128.1708057931053</v>
+        <v>128.1708057931056</v>
       </c>
       <c r="F4" t="n">
-        <v>468.7939705715469</v>
+        <v>468.7939705715474</v>
       </c>
       <c r="G4" t="n">
-        <v>1144.865539654936</v>
+        <v>1144.865539654939</v>
       </c>
       <c r="H4" t="n">
-        <v>176.2326126181438</v>
+        <v>176.2326126181441</v>
       </c>
       <c r="I4" t="n">
         <v>373.7098601593128</v>
       </c>
       <c r="J4" t="n">
-        <v>760.0093793831437</v>
+        <v>760.0093793831436</v>
       </c>
       <c r="K4" t="n">
-        <v>377.1408757589591</v>
+        <v>377.1408757589587</v>
       </c>
       <c r="L4" t="n">
-        <v>249.3637225992283</v>
+        <v>249.3637225992289</v>
       </c>
       <c r="M4" t="n">
-        <v>1642.486731141412</v>
+        <v>1642.486731141411</v>
       </c>
       <c r="N4" t="n">
-        <v>260.6078274636782</v>
+        <v>260.6078274636786</v>
       </c>
       <c r="O4" t="n">
-        <v>390.5841096934042</v>
+        <v>390.5841096934046</v>
       </c>
       <c r="P4" t="n">
-        <v>656.6656191303438</v>
+        <v>656.6656191303459</v>
       </c>
       <c r="Q4" t="n">
-        <v>291.5957043766209</v>
+        <v>291.5957043766215</v>
       </c>
       <c r="R4" t="n">
-        <v>180.026735621237</v>
+        <v>180.0267356212371</v>
       </c>
       <c r="S4" t="n">
-        <v>461.4313836276156</v>
+        <v>461.4313836276163</v>
       </c>
       <c r="T4" t="n">
-        <v>257.8381984496567</v>
+        <v>257.8381984496576</v>
       </c>
       <c r="U4" t="n">
-        <v>342.5821826281948</v>
+        <v>342.5821826281949</v>
       </c>
       <c r="V4" t="n">
-        <v>321.5355785047233</v>
+        <v>321.535578504728</v>
       </c>
       <c r="W4" t="n">
-        <v>442.1940281056628</v>
+        <v>442.1940281056623</v>
       </c>
       <c r="X4" t="n">
-        <v>484.2317630174092</v>
+        <v>484.2317630174095</v>
       </c>
       <c r="Y4" t="n">
-        <v>793.557870774205</v>
+        <v>793.5578707742079</v>
       </c>
       <c r="Z4" t="n">
-        <v>407.3302477907165</v>
+        <v>407.330247790716</v>
       </c>
       <c r="AA4" t="n">
-        <v>309.47953988536</v>
+        <v>309.4795398853603</v>
       </c>
       <c r="AB4" t="n">
-        <v>1872.260279518296</v>
+        <v>1872.260279518297</v>
       </c>
     </row>
     <row r="5">
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>129.4069479997755</v>
+        <v>129.4069479997759</v>
       </c>
       <c r="C5" t="n">
-        <v>191.7956301935662</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="D5" t="n">
-        <v>191.7956301935662</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="E5" t="n">
         <v>158.5754972755704</v>
       </c>
       <c r="F5" t="n">
-        <v>139.1263755341063</v>
+        <v>139.1263755341062</v>
       </c>
       <c r="G5" t="n">
-        <v>204.7323298712308</v>
+        <v>204.7323298712314</v>
       </c>
       <c r="H5" t="n">
-        <v>191.7956301935662</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="I5" t="n">
-        <v>191.7956301935662</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="J5" t="n">
-        <v>191.6159690885473</v>
+        <v>191.6159690885474</v>
       </c>
       <c r="K5" t="n">
-        <v>191.7956301935662</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="L5" t="n">
-        <v>191.7956301935663</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="M5" t="n">
-        <v>191.7956301935749</v>
+        <v>191.7956301935755</v>
       </c>
       <c r="N5" t="n">
-        <v>260.6078274636782</v>
+        <v>143.4339640952394</v>
       </c>
       <c r="O5" t="n">
-        <v>156.7241698585127</v>
+        <v>156.7241698585132</v>
       </c>
       <c r="P5" t="n">
-        <v>153.4664192893099</v>
+        <v>153.4664192893101</v>
       </c>
       <c r="Q5" t="n">
-        <v>117.1461479954812</v>
+        <v>117.1461479954814</v>
       </c>
       <c r="R5" t="n">
-        <v>191.7956301935662</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="S5" t="n">
-        <v>191.7956301935662</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="T5" t="n">
-        <v>191.7956301935662</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="U5" t="n">
-        <v>161.3290902821206</v>
+        <v>161.3290902821207</v>
       </c>
       <c r="V5" t="n">
-        <v>173.5861244781613</v>
+        <v>173.5861244781617</v>
       </c>
       <c r="W5" t="n">
-        <v>191.8078913612565</v>
+        <v>191.8078913612568</v>
       </c>
       <c r="X5" t="n">
         <v>122.8641946891856</v>
       </c>
       <c r="Y5" t="n">
-        <v>253.8008347070406</v>
+        <v>253.8008347070411</v>
       </c>
       <c r="Z5" t="n">
-        <v>128.2480461972966</v>
+        <v>128.248046197297</v>
       </c>
       <c r="AA5" t="n">
-        <v>191.7956301935662</v>
+        <v>191.7956301935667</v>
       </c>
       <c r="AB5" t="n">
-        <v>256.9658256054652</v>
+        <v>256.9658256054653</v>
       </c>
     </row>
     <row r="6">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>118.1836756592085</v>
+        <v>118.1836756592079</v>
       </c>
       <c r="C6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="D6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="E6" t="n">
-        <v>136.6838359724064</v>
+        <v>136.6838359724062</v>
       </c>
       <c r="F6" t="n">
-        <v>86.79050050175778</v>
+        <v>86.79050050175823</v>
       </c>
       <c r="G6" t="n">
-        <v>142.2347185749488</v>
+        <v>142.234718574949</v>
       </c>
       <c r="H6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="I6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="J6" t="n">
-        <v>142.0550602942474</v>
+        <v>142.0550602942463</v>
       </c>
       <c r="K6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="L6" t="n">
-        <v>142.2347213992653</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="M6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="N6" t="n">
-        <v>260.6078274636782</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="O6" t="n">
         <v>150.2052027051024</v>
       </c>
       <c r="P6" t="n">
-        <v>151.9386462529081</v>
+        <v>151.9386462529071</v>
       </c>
       <c r="Q6" t="n">
-        <v>142.2347185749488</v>
+        <v>142.234718574949</v>
       </c>
       <c r="R6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="S6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="T6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="U6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="V6" t="n">
-        <v>168.8483964035038</v>
+        <v>168.8483964035046</v>
       </c>
       <c r="W6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="X6" t="n">
-        <v>142.2347213992653</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="Y6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="Z6" t="n">
-        <v>127.7340783989402</v>
+        <v>127.73407839894</v>
       </c>
       <c r="AA6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
       <c r="AB6" t="n">
-        <v>142.2347213992652</v>
+        <v>142.2347213992657</v>
       </c>
     </row>
     <row r="7">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82.45699880058675</v>
+        <v>82.45699880058679</v>
       </c>
       <c r="C7" t="n">
-        <v>87.9903329038867</v>
+        <v>87.99033290388661</v>
       </c>
       <c r="D7" t="n">
-        <v>80.31124152356016</v>
+        <v>80.31124152356026</v>
       </c>
       <c r="E7" t="n">
         <v>33.34777658879916</v>
       </c>
       <c r="F7" t="n">
-        <v>80.93567259051304</v>
+        <v>80.93567259051309</v>
       </c>
       <c r="G7" t="n">
-        <v>62.66361330946611</v>
+        <v>62.66361330946616</v>
       </c>
       <c r="H7" t="n">
-        <v>87.53325320614502</v>
+        <v>87.53325320614509</v>
       </c>
       <c r="I7" t="n">
-        <v>83.10537002121148</v>
+        <v>83.10537002121146</v>
       </c>
       <c r="J7" t="n">
-        <v>73.02079064241143</v>
+        <v>73.02079064241144</v>
       </c>
       <c r="K7" t="n">
-        <v>82.5242661686292</v>
+        <v>82.52426616862915</v>
       </c>
       <c r="L7" t="n">
-        <v>85.50184457618754</v>
+        <v>85.50184457618759</v>
       </c>
       <c r="M7" t="n">
-        <v>55.3951782718859</v>
+        <v>55.39517827188592</v>
       </c>
       <c r="N7" t="n">
-        <v>85.3943534779375</v>
+        <v>85.39435347793756</v>
       </c>
       <c r="O7" t="n">
-        <v>81.48647319144311</v>
+        <v>81.48647319144307</v>
       </c>
       <c r="P7" t="n">
-        <v>74.92712550965165</v>
+        <v>74.9271255096517</v>
       </c>
       <c r="Q7" t="n">
         <v>84.66669985478444</v>
       </c>
       <c r="R7" t="n">
-        <v>87.37819030213137</v>
+        <v>87.37819030213139</v>
       </c>
       <c r="S7" t="n">
-        <v>80.04465742000775</v>
+        <v>80.04465742000778</v>
       </c>
       <c r="T7" t="n">
-        <v>85.60605733788896</v>
+        <v>85.60605733788906</v>
       </c>
       <c r="U7" t="n">
-        <v>83.19772815980359</v>
+        <v>83.19772815980357</v>
       </c>
       <c r="V7" t="n">
-        <v>48.82654479803431</v>
+        <v>48.82654479803421</v>
       </c>
       <c r="W7" t="n">
-        <v>81.06694412146544</v>
+        <v>81.06694412146551</v>
       </c>
       <c r="X7" t="n">
-        <v>80.40580046037545</v>
+        <v>80.40580046037546</v>
       </c>
       <c r="Y7" t="n">
-        <v>72.82299708758539</v>
+        <v>72.82299708758549</v>
       </c>
       <c r="Z7" t="n">
         <v>81.03362372923337</v>
       </c>
       <c r="AA7" t="n">
-        <v>84.17961689481456</v>
+        <v>84.17961689481459</v>
       </c>
       <c r="AB7" t="n">
-        <v>51.97791001246357</v>
+        <v>51.97791001246355</v>
       </c>
     </row>
     <row r="8">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86.644492879013</v>
+        <v>86.64449287901307</v>
       </c>
       <c r="C8" t="n">
-        <v>88.23567806399967</v>
+        <v>88.23567806399981</v>
       </c>
       <c r="D8" t="n">
-        <v>86.05293830048731</v>
+        <v>86.05293830048741</v>
       </c>
       <c r="E8" t="n">
-        <v>34.85813484278788</v>
+        <v>34.85813484278798</v>
       </c>
       <c r="F8" t="n">
-        <v>86.23760008908839</v>
+        <v>86.23760008908842</v>
       </c>
       <c r="G8" t="n">
-        <v>80.96802810323882</v>
+        <v>80.96802810323885</v>
       </c>
       <c r="H8" t="n">
-        <v>88.1082851419965</v>
+        <v>88.10828514199657</v>
       </c>
       <c r="I8" t="n">
-        <v>86.8492993086718</v>
+        <v>86.84929930867193</v>
       </c>
       <c r="J8" t="n">
-        <v>83.85901834263456</v>
+        <v>83.85901834263473</v>
       </c>
       <c r="K8" t="n">
-        <v>86.68038436779845</v>
+        <v>86.6803843677986</v>
       </c>
       <c r="L8" t="n">
-        <v>87.52231136400285</v>
+        <v>87.5223113640029</v>
       </c>
       <c r="M8" t="n">
-        <v>78.9918894513082</v>
+        <v>78.99188945130823</v>
       </c>
       <c r="N8" t="n">
-        <v>87.49504797557354</v>
+        <v>87.4950479755736</v>
       </c>
       <c r="O8" t="n">
-        <v>86.36457411668077</v>
+        <v>86.36457411668076</v>
       </c>
       <c r="P8" t="n">
-        <v>84.47925037810114</v>
+        <v>84.47925037810113</v>
       </c>
       <c r="Q8" t="n">
-        <v>87.28902722634126</v>
+        <v>87.28902722634135</v>
       </c>
       <c r="R8" t="n">
-        <v>88.06336749678209</v>
+        <v>88.06336749678223</v>
       </c>
       <c r="S8" t="n">
-        <v>85.95726921088043</v>
+        <v>85.95726921088045</v>
       </c>
       <c r="T8" t="n">
-        <v>87.55858101841957</v>
+        <v>87.55858101841969</v>
       </c>
       <c r="U8" t="n">
-        <v>86.86262170441456</v>
+        <v>86.86262170441462</v>
       </c>
       <c r="V8" t="n">
         <v>52.8659808481069</v>
       </c>
       <c r="W8" t="n">
-        <v>86.25696538757863</v>
+        <v>86.25696538757875</v>
       </c>
       <c r="X8" t="n">
-        <v>86.07834655567497</v>
+        <v>86.07834655567508</v>
       </c>
       <c r="Y8" t="n">
-        <v>83.90731280260829</v>
+        <v>83.9073128026084</v>
       </c>
       <c r="Z8" t="n">
-        <v>86.23768221443454</v>
+        <v>86.23768221443468</v>
       </c>
       <c r="AA8" t="n">
-        <v>87.1465781525071</v>
+        <v>87.14657815250723</v>
       </c>
       <c r="AB8" t="n">
-        <v>77.99973850656312</v>
+        <v>77.9997385065632</v>
       </c>
     </row>
   </sheetData>
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.56455547068089</v>
+        <v>89.56455547067583</v>
       </c>
       <c r="C2" t="n">
-        <v>88.73786709012349</v>
+        <v>88.73786709013133</v>
       </c>
       <c r="D2" t="n">
-        <v>89.64596257285241</v>
+        <v>89.64596257286026</v>
       </c>
       <c r="E2" t="n">
-        <v>35.48632968067549</v>
+        <v>35.48632968067113</v>
       </c>
       <c r="F2" t="n">
-        <v>90.10839331484188</v>
+        <v>90.10839331485325</v>
       </c>
       <c r="G2" t="n">
-        <v>92.36444162061386</v>
+        <v>92.36444162062098</v>
       </c>
       <c r="H2" t="n">
-        <v>88.79592002034003</v>
+        <v>88.79592002034201</v>
       </c>
       <c r="I2" t="n">
-        <v>89.64126716700683</v>
+        <v>89.64126716700861</v>
       </c>
       <c r="J2" t="n">
-        <v>90.79050019288343</v>
+        <v>90.79050019288475</v>
       </c>
       <c r="K2" t="n">
-        <v>89.70848138102835</v>
+        <v>89.70848138103013</v>
       </c>
       <c r="L2" t="n">
-        <v>89.10392294096579</v>
+        <v>89.10392294095917</v>
       </c>
       <c r="M2" t="n">
-        <v>93.36913930835547</v>
+        <v>93.36913930835667</v>
       </c>
       <c r="N2" t="n">
-        <v>89.00500056267057</v>
+        <v>89.00500056268027</v>
       </c>
       <c r="O2" t="n">
-        <v>89.42812042100468</v>
+        <v>89.42812042101937</v>
       </c>
       <c r="P2" t="n">
-        <v>90.64185538707306</v>
+        <v>90.64185538708126</v>
       </c>
       <c r="Q2" t="n">
-        <v>89.15875797525203</v>
+        <v>89.15875797525366</v>
       </c>
       <c r="R2" t="n">
-        <v>89.16751917141539</v>
+        <v>89.16751917142757</v>
       </c>
       <c r="S2" t="n">
-        <v>89.93666824403246</v>
+        <v>89.9366682440494</v>
       </c>
       <c r="T2" t="n">
-        <v>89.20430912979053</v>
+        <v>89.20430912980103</v>
       </c>
       <c r="U2" t="n">
-        <v>89.22110094666043</v>
+        <v>89.2211009466713</v>
       </c>
       <c r="V2" t="n">
-        <v>56.03896625636494</v>
+        <v>56.03896625636501</v>
       </c>
       <c r="W2" t="n">
-        <v>89.82358240410773</v>
+        <v>89.82358240411617</v>
       </c>
       <c r="X2" t="n">
-        <v>90.05423800884068</v>
+        <v>90.05423800885723</v>
       </c>
       <c r="Y2" t="n">
-        <v>92.53126284083189</v>
+        <v>92.53126284083076</v>
       </c>
       <c r="Z2" t="n">
-        <v>89.67786003208067</v>
+        <v>89.67786003207866</v>
       </c>
       <c r="AA2" t="n">
-        <v>89.40188387571511</v>
+        <v>89.40188387572907</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.23901186571487</v>
+        <v>94.23901186571746</v>
       </c>
     </row>
     <row r="3">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.17527330906375</v>
+        <v>89.17527330906849</v>
       </c>
       <c r="C3" t="n">
-        <v>89.17526945499144</v>
+        <v>89.17526945499618</v>
       </c>
       <c r="D3" t="n">
-        <v>89.17527330906375</v>
+        <v>89.17527330906849</v>
       </c>
       <c r="E3" t="n">
-        <v>35.18821542782842</v>
+        <v>35.18821542783768</v>
       </c>
       <c r="F3" t="n">
-        <v>89.1752707347917</v>
+        <v>89.17527073479644</v>
       </c>
       <c r="G3" t="n">
-        <v>89.17527208157293</v>
+        <v>89.17527208157767</v>
       </c>
       <c r="H3" t="n">
-        <v>89.17527330906375</v>
+        <v>89.17527330906849</v>
       </c>
       <c r="I3" t="n">
-        <v>89.17527330906375</v>
+        <v>89.17527330906849</v>
       </c>
       <c r="J3" t="n">
-        <v>89.07322031597667</v>
+        <v>89.07322031597894</v>
       </c>
       <c r="K3" t="n">
-        <v>89.17527183938269</v>
+        <v>89.17527183938743</v>
       </c>
       <c r="L3" t="n">
-        <v>89.17527330906375</v>
+        <v>89.17527330906849</v>
       </c>
       <c r="M3" t="n">
-        <v>89.17526663773818</v>
+        <v>89.17526663774292</v>
       </c>
       <c r="N3" t="n">
-        <v>89.17527330906375</v>
+        <v>89.17527330906849</v>
       </c>
       <c r="O3" t="n">
-        <v>89.17526992014294</v>
+        <v>89.17526992014767</v>
       </c>
       <c r="P3" t="n">
-        <v>89.17526692971136</v>
+        <v>89.1752669297161</v>
       </c>
       <c r="Q3" t="n">
-        <v>89.17527327142004</v>
+        <v>89.17527327142477</v>
       </c>
       <c r="R3" t="n">
-        <v>89.17528158681006</v>
+        <v>89.1752815868148</v>
       </c>
       <c r="S3" t="n">
-        <v>89.17527330906375</v>
+        <v>89.17527330906849</v>
       </c>
       <c r="T3" t="n">
-        <v>89.17526842873083</v>
+        <v>89.17526842873558</v>
       </c>
       <c r="U3" t="n">
-        <v>89.17528488977683</v>
+        <v>89.17528488978158</v>
       </c>
       <c r="V3" t="n">
-        <v>54.89288856102944</v>
+        <v>54.89288856102947</v>
       </c>
       <c r="W3" t="n">
-        <v>89.17527330906375</v>
+        <v>89.17527330906849</v>
       </c>
       <c r="X3" t="n">
-        <v>89.17528515148453</v>
+        <v>89.17528515148928</v>
       </c>
       <c r="Y3" t="n">
-        <v>89.17526046385763</v>
+        <v>89.17526046386237</v>
       </c>
       <c r="Z3" t="n">
-        <v>89.17527296898845</v>
+        <v>89.1752729689932</v>
       </c>
       <c r="AA3" t="n">
-        <v>89.17527330906375</v>
+        <v>89.17527330906849</v>
       </c>
       <c r="AB3" t="n">
-        <v>89.17531254500794</v>
+        <v>89.17531254501269</v>
       </c>
     </row>
     <row r="4">
@@ -3850,82 +3850,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>349.6952359953167</v>
+        <v>349.6952359953236</v>
       </c>
       <c r="C4" t="n">
-        <v>173.0542838856624</v>
+        <v>173.0542838856738</v>
       </c>
       <c r="D4" t="n">
-        <v>399.5503495935266</v>
+        <v>399.5503495935279</v>
       </c>
       <c r="E4" t="n">
-        <v>106.7881352382169</v>
+        <v>106.7881352382318</v>
       </c>
       <c r="F4" t="n">
-        <v>524.7869248975701</v>
+        <v>524.7869248975699</v>
       </c>
       <c r="G4" t="n">
-        <v>984.8878975148573</v>
+        <v>984.8878975148809</v>
       </c>
       <c r="H4" t="n">
-        <v>188.8741362907601</v>
+        <v>188.8741362908014</v>
       </c>
       <c r="I4" t="n">
-        <v>406.9773366388869</v>
+        <v>406.977336638887</v>
       </c>
       <c r="J4" t="n">
-        <v>677.6499481480218</v>
+        <v>677.6499481480187</v>
       </c>
       <c r="K4" t="n">
-        <v>401.7672162821901</v>
+        <v>401.7672162822146</v>
       </c>
       <c r="L4" t="n">
-        <v>253.1160921891653</v>
+        <v>253.1160921891681</v>
       </c>
       <c r="M4" t="n">
-        <v>1353.889775492378</v>
+        <v>1353.889775492381</v>
       </c>
       <c r="N4" t="n">
-        <v>233.8924126184696</v>
+        <v>233.8924126184963</v>
       </c>
       <c r="O4" t="n">
-        <v>316.9679670081916</v>
+        <v>316.9679670082061</v>
       </c>
       <c r="P4" t="n">
-        <v>591.7987828212578</v>
+        <v>591.7987828212615</v>
       </c>
       <c r="Q4" t="n">
-        <v>270.0084489249679</v>
+        <v>270.0084489249781</v>
       </c>
       <c r="R4" t="n">
-        <v>286.6341327448027</v>
+        <v>286.6341327448113</v>
       </c>
       <c r="S4" t="n">
-        <v>441.3011010347569</v>
+        <v>441.3011010347782</v>
       </c>
       <c r="T4" t="n">
-        <v>291.8342618222892</v>
+        <v>291.8342618222952</v>
       </c>
       <c r="U4" t="n">
-        <v>279.025972467058</v>
+        <v>279.0259724670697</v>
       </c>
       <c r="V4" t="n">
-        <v>398.4814152531641</v>
+        <v>398.4814152531647</v>
       </c>
       <c r="W4" t="n">
-        <v>438.385661563667</v>
+        <v>438.3856615636739</v>
       </c>
       <c r="X4" t="n">
-        <v>497.813997416515</v>
+        <v>497.8139974165139</v>
       </c>
       <c r="Y4" t="n">
-        <v>1136.237687028496</v>
+        <v>1136.237687028504</v>
       </c>
       <c r="Z4" t="n">
-        <v>361.2538891537737</v>
+        <v>361.2538891537791</v>
       </c>
       <c r="AA4" t="n">
-        <v>332.454248912915</v>
+        <v>332.4542489129153</v>
       </c>
       <c r="AB4" t="n">
         <v>1687.203858413659</v>
@@ -3938,85 +3938,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>128.9431639726333</v>
+        <v>128.9431639726358</v>
       </c>
       <c r="C5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="D5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="E5" t="n">
-        <v>157.9010290745712</v>
+        <v>157.9010290745882</v>
       </c>
       <c r="F5" t="n">
-        <v>138.5923881677271</v>
+        <v>138.5923881677386</v>
       </c>
       <c r="G5" t="n">
-        <v>203.7244712760993</v>
+        <v>203.7244712761096</v>
       </c>
       <c r="H5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="I5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="J5" t="n">
-        <v>190.708168956362</v>
+        <v>190.7081689563835</v>
       </c>
       <c r="K5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="L5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="M5" t="n">
-        <v>190.8812132659521</v>
+        <v>190.8812132659652</v>
       </c>
       <c r="N5" t="n">
-        <v>233.8924126184696</v>
+        <v>142.8688630547605</v>
       </c>
       <c r="O5" t="n">
-        <v>156.0630737792356</v>
+        <v>156.0630737792535</v>
       </c>
       <c r="P5" t="n">
-        <v>152.8288539136086</v>
+        <v>152.8288539136128</v>
       </c>
       <c r="Q5" t="n">
-        <v>116.7709236183999</v>
+        <v>116.7709236184338</v>
       </c>
       <c r="R5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="S5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="T5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="U5" t="n">
-        <v>160.6377920557066</v>
+        <v>160.6377920557194</v>
       </c>
       <c r="V5" t="n">
-        <v>172.8406827589412</v>
+        <v>172.8406827589415</v>
       </c>
       <c r="W5" t="n">
-        <v>190.8933858714792</v>
+        <v>190.893385871486</v>
       </c>
       <c r="X5" t="n">
-        <v>122.4476689114569</v>
+        <v>122.4476689114666</v>
       </c>
       <c r="Y5" t="n">
-        <v>252.4437880546851</v>
+        <v>252.4437880546703</v>
       </c>
       <c r="Z5" t="n">
-        <v>127.7926329076196</v>
+        <v>127.792632907619</v>
       </c>
       <c r="AA5" t="n">
-        <v>190.8812132659427</v>
+        <v>190.8812132659523</v>
       </c>
       <c r="AB5" t="n">
-        <v>255.5806849321424</v>
+        <v>255.5806849321273</v>
       </c>
     </row>
     <row r="6">
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112.9189690456907</v>
+        <v>112.9189690457043</v>
       </c>
       <c r="C6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="D6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="E6" t="n">
-        <v>130.2469707333464</v>
+        <v>130.2469707333637</v>
       </c>
       <c r="F6" t="n">
-        <v>83.51484589757462</v>
+        <v>83.51484589758034</v>
       </c>
       <c r="G6" t="n">
-        <v>135.4461528743138</v>
+        <v>135.4461528743017</v>
       </c>
       <c r="H6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="I6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="J6" t="n">
-        <v>135.273110488547</v>
+        <v>135.2731104885547</v>
       </c>
       <c r="K6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="L6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="M6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="N6" t="n">
-        <v>233.8924126184696</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="O6" t="n">
-        <v>142.9116320982743</v>
+        <v>142.9116320982991</v>
       </c>
       <c r="P6" t="n">
-        <v>144.5352457434197</v>
+        <v>144.5352457434399</v>
       </c>
       <c r="Q6" t="n">
-        <v>135.4461528743138</v>
+        <v>135.4461528743017</v>
       </c>
       <c r="R6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="S6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="T6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="U6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="V6" t="n">
-        <v>160.3436461730319</v>
+        <v>160.3436461730323</v>
       </c>
       <c r="W6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="X6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="Y6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="Z6" t="n">
-        <v>121.8642642209952</v>
+        <v>121.8642642210031</v>
       </c>
       <c r="AA6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
       <c r="AB6" t="n">
-        <v>135.446154798122</v>
+        <v>135.4461547981234</v>
       </c>
     </row>
     <row r="7">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82.44269966957346</v>
+        <v>82.44269966958346</v>
       </c>
       <c r="C7" t="n">
-        <v>87.3880656662958</v>
+        <v>87.38806566629827</v>
       </c>
       <c r="D7" t="n">
-        <v>82.07106670661634</v>
+        <v>82.07106670661473</v>
       </c>
       <c r="E7" t="n">
-        <v>33.79828249175857</v>
+        <v>33.79828249176759</v>
       </c>
       <c r="F7" t="n">
-        <v>79.41071962320179</v>
+        <v>79.41071962320521</v>
       </c>
       <c r="G7" t="n">
-        <v>65.79874709303492</v>
+        <v>65.79874709303996</v>
       </c>
       <c r="H7" t="n">
-        <v>87.06524206704587</v>
+        <v>87.06524206704506</v>
       </c>
       <c r="I7" t="n">
-        <v>82.11199960137205</v>
+        <v>82.11199960138481</v>
       </c>
       <c r="J7" t="n">
-        <v>74.54615206863477</v>
+        <v>74.54615206863521</v>
       </c>
       <c r="K7" t="n">
-        <v>81.69412849560048</v>
+        <v>81.69412849559981</v>
       </c>
       <c r="L7" t="n">
-        <v>85.2087460372688</v>
+        <v>85.20874603727093</v>
       </c>
       <c r="M7" t="n">
-        <v>60.37249081042087</v>
+        <v>60.37249081042361</v>
       </c>
       <c r="N7" t="n">
-        <v>85.81094266073181</v>
+        <v>85.81094266074695</v>
       </c>
       <c r="O7" t="n">
-        <v>83.24779483346592</v>
+        <v>83.24779483347523</v>
       </c>
       <c r="P7" t="n">
-        <v>76.00742531097362</v>
+        <v>76.00742531097549</v>
       </c>
       <c r="Q7" t="n">
-        <v>84.91376058679836</v>
+        <v>84.91376058679785</v>
       </c>
       <c r="R7" t="n">
-        <v>84.89095402487492</v>
+        <v>84.89095402488046</v>
       </c>
       <c r="S7" t="n">
-        <v>80.2568584808362</v>
+        <v>80.25685848082901</v>
       </c>
       <c r="T7" t="n">
-        <v>84.66096741745484</v>
+        <v>84.66096741744626</v>
       </c>
       <c r="U7" t="n">
-        <v>84.51133621414981</v>
+        <v>84.51133621415211</v>
       </c>
       <c r="V7" t="n">
-        <v>46.83242535420369</v>
+        <v>46.83242535420371</v>
       </c>
       <c r="W7" t="n">
-        <v>80.96810923337333</v>
+        <v>80.96810923337486</v>
       </c>
       <c r="X7" t="n">
-        <v>79.67041538298844</v>
+        <v>79.67041538299961</v>
       </c>
       <c r="Y7" t="n">
-        <v>65.02658163249616</v>
+        <v>65.02658163249292</v>
       </c>
       <c r="Z7" t="n">
-        <v>81.77694689622358</v>
+        <v>81.77694689622869</v>
       </c>
       <c r="AA7" t="n">
-        <v>83.46170482981856</v>
+        <v>83.46170482981695</v>
       </c>
       <c r="AB7" t="n">
-        <v>55.17512866658836</v>
+        <v>55.17512866659503</v>
       </c>
     </row>
     <row r="8">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86.50121300925267</v>
+        <v>86.50121300927101</v>
       </c>
       <c r="C8" t="n">
-        <v>87.92468367079455</v>
+        <v>87.92468367079323</v>
       </c>
       <c r="D8" t="n">
-        <v>86.41352592897505</v>
+        <v>86.41352592898069</v>
       </c>
       <c r="E8" t="n">
-        <v>34.85390576531336</v>
+        <v>34.85390576530577</v>
       </c>
       <c r="F8" t="n">
-        <v>85.66549144129556</v>
+        <v>85.66549144130121</v>
       </c>
       <c r="G8" t="n">
-        <v>81.7280482542631</v>
+        <v>81.72804825427134</v>
       </c>
       <c r="H8" t="n">
-        <v>87.83584908094663</v>
+        <v>87.83584908095074</v>
       </c>
       <c r="I8" t="n">
-        <v>86.4274551206874</v>
+        <v>86.42745512069475</v>
       </c>
       <c r="J8" t="n">
-        <v>84.18063784532283</v>
+        <v>84.1806378453237</v>
       </c>
       <c r="K8" t="n">
-        <v>86.3045373186097</v>
+        <v>86.30453731861746</v>
       </c>
       <c r="L8" t="n">
-        <v>87.29914039172334</v>
+        <v>87.29914039171879</v>
       </c>
       <c r="M8" t="n">
-        <v>80.26378451791909</v>
+        <v>80.26378451792607</v>
       </c>
       <c r="N8" t="n">
-        <v>87.47421939622171</v>
+        <v>87.4742193962083</v>
       </c>
       <c r="O8" t="n">
-        <v>86.73110036683713</v>
+        <v>86.73110036684125</v>
       </c>
       <c r="P8" t="n">
-        <v>84.65044548712756</v>
+        <v>84.65044548713288</v>
       </c>
       <c r="Q8" t="n">
-        <v>87.21975612312198</v>
+        <v>87.2197561231132</v>
       </c>
       <c r="R8" t="n">
-        <v>87.21813647739938</v>
+        <v>87.21813647740555</v>
       </c>
       <c r="S8" t="n">
-        <v>85.87876107589436</v>
+        <v>85.87876107589871</v>
       </c>
       <c r="T8" t="n">
-        <v>87.15028778342756</v>
+        <v>87.15028778344058</v>
       </c>
       <c r="U8" t="n">
-        <v>87.09898943612804</v>
+        <v>87.09898943613742</v>
       </c>
       <c r="V8" t="n">
-        <v>52.37142981008712</v>
+        <v>52.37142981008715</v>
       </c>
       <c r="W8" t="n">
-        <v>86.08929659498799</v>
+        <v>86.08929659499555</v>
       </c>
       <c r="X8" t="n">
-        <v>85.72949197397267</v>
+        <v>85.72949197397176</v>
       </c>
       <c r="Y8" t="n">
-        <v>81.54353701528116</v>
+        <v>81.54353701528443</v>
       </c>
       <c r="Z8" t="n">
-        <v>86.31159809190503</v>
+        <v>86.31159809190451</v>
       </c>
       <c r="AA8" t="n">
-        <v>86.80219200961299</v>
+        <v>86.80219200960721</v>
       </c>
       <c r="AB8" t="n">
-        <v>78.76881984887426</v>
+        <v>78.76881984888033</v>
       </c>
     </row>
   </sheetData>
@@ -4446,52 +4446,52 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>87.48321898985499</v>
+        <v>87.48321898985496</v>
       </c>
       <c r="C2" t="n">
-        <v>86.94679972519114</v>
+        <v>86.9467997251911</v>
       </c>
       <c r="D2" t="n">
         <v>87.18158237098385</v>
       </c>
       <c r="E2" t="n">
-        <v>34.78577672723826</v>
+        <v>34.78577672723829</v>
       </c>
       <c r="F2" t="n">
-        <v>87.14910262209972</v>
+        <v>87.14910262209969</v>
       </c>
       <c r="G2" t="n">
-        <v>88.21014600218241</v>
+        <v>88.2101460021824</v>
       </c>
       <c r="H2" t="n">
-        <v>87.49873438165028</v>
+        <v>87.49873438165022</v>
       </c>
       <c r="I2" t="n">
         <v>87.25972147871047</v>
       </c>
       <c r="J2" t="n">
-        <v>87.77763175223133</v>
+        <v>87.77763175223137</v>
       </c>
       <c r="K2" t="n">
-        <v>87.50675786241403</v>
+        <v>87.50675786241398</v>
       </c>
       <c r="L2" t="n">
-        <v>87.5269075796804</v>
+        <v>87.52690757968035</v>
       </c>
       <c r="M2" t="n">
-        <v>89.06437002054145</v>
+        <v>89.06437002054142</v>
       </c>
       <c r="N2" t="n">
-        <v>87.42587685055261</v>
+        <v>87.42587685055256</v>
       </c>
       <c r="O2" t="n">
-        <v>87.40571355834393</v>
+        <v>87.40571355834395</v>
       </c>
       <c r="P2" t="n">
-        <v>87.80827192676263</v>
+        <v>87.80827192676256</v>
       </c>
       <c r="Q2" t="n">
-        <v>87.48988917836702</v>
+        <v>87.48988917836701</v>
       </c>
       <c r="R2" t="n">
         <v>87.2025431012038</v>
@@ -4500,16 +4500,16 @@
         <v>87.57274282820724</v>
       </c>
       <c r="T2" t="n">
-        <v>87.19851355887666</v>
+        <v>87.19851355887664</v>
       </c>
       <c r="U2" t="n">
-        <v>87.53522204152355</v>
+        <v>87.53522204152357</v>
       </c>
       <c r="V2" t="n">
-        <v>53.41468172792669</v>
+        <v>53.41468172792659</v>
       </c>
       <c r="W2" t="n">
-        <v>88.15034781661531</v>
+        <v>88.15034781661535</v>
       </c>
       <c r="X2" t="n">
         <v>87.56645731251197</v>
@@ -4524,7 +4524,7 @@
         <v>87.38906824031142</v>
       </c>
       <c r="AB2" t="n">
-        <v>88.62343175135385</v>
+        <v>88.62343175135386</v>
       </c>
     </row>
     <row r="3">
@@ -4534,85 +4534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87.51076813777983</v>
+        <v>87.51076813777981</v>
       </c>
       <c r="C3" t="n">
-        <v>87.51076445355442</v>
+        <v>87.51076445355437</v>
       </c>
       <c r="D3" t="n">
-        <v>87.51076813777983</v>
+        <v>87.51076813777981</v>
       </c>
       <c r="E3" t="n">
-        <v>34.40624618379394</v>
+        <v>34.40624618379398</v>
       </c>
       <c r="F3" t="n">
-        <v>87.51076676359577</v>
+        <v>87.51076676359574</v>
       </c>
       <c r="G3" t="n">
-        <v>87.5107677153006</v>
+        <v>87.51076771530057</v>
       </c>
       <c r="H3" t="n">
-        <v>87.51076813777983</v>
+        <v>87.51076813777981</v>
       </c>
       <c r="I3" t="n">
-        <v>87.51076813777983</v>
+        <v>87.51076813777981</v>
       </c>
       <c r="J3" t="n">
         <v>87.44576256146627</v>
       </c>
       <c r="K3" t="n">
-        <v>87.51076732953801</v>
+        <v>87.51076732953798</v>
       </c>
       <c r="L3" t="n">
-        <v>87.51076813777983</v>
+        <v>87.51076813777981</v>
       </c>
       <c r="M3" t="n">
-        <v>87.51076718620412</v>
+        <v>87.51076718620408</v>
       </c>
       <c r="N3" t="n">
-        <v>87.51076813777983</v>
+        <v>87.51076813777981</v>
       </c>
       <c r="O3" t="n">
-        <v>87.51076548496803</v>
+        <v>87.51076548496799</v>
       </c>
       <c r="P3" t="n">
-        <v>87.51076747376759</v>
+        <v>87.51076747376754</v>
       </c>
       <c r="Q3" t="n">
-        <v>87.51076810013612</v>
+        <v>87.51076810013609</v>
       </c>
       <c r="R3" t="n">
-        <v>87.51076798836469</v>
+        <v>87.51076798836466</v>
       </c>
       <c r="S3" t="n">
-        <v>87.51076813777983</v>
+        <v>87.51076813777981</v>
       </c>
       <c r="T3" t="n">
-        <v>87.51076698385955</v>
+        <v>87.51076698385951</v>
       </c>
       <c r="U3" t="n">
-        <v>87.51077074322235</v>
+        <v>87.51077074322232</v>
       </c>
       <c r="V3" t="n">
-        <v>53.13584090345903</v>
+        <v>53.13584090345897</v>
       </c>
       <c r="W3" t="n">
-        <v>87.51076813777983</v>
+        <v>87.51076813777981</v>
       </c>
       <c r="X3" t="n">
-        <v>87.51077030188056</v>
+        <v>87.51077030188051</v>
       </c>
       <c r="Y3" t="n">
-        <v>87.51076204668534</v>
+        <v>87.5107620466853</v>
       </c>
       <c r="Z3" t="n">
-        <v>87.5107679322283</v>
+        <v>87.51076793222828</v>
       </c>
       <c r="AA3" t="n">
-        <v>87.51076813777983</v>
+        <v>87.51076813777981</v>
       </c>
       <c r="AB3" t="n">
-        <v>87.51080737372403</v>
+        <v>87.51080737372399</v>
       </c>
     </row>
     <row r="4">
@@ -4625,52 +4625,52 @@
         <v>265.8603402262822</v>
       </c>
       <c r="C4" t="n">
-        <v>140.8365933832609</v>
+        <v>140.8365933832605</v>
       </c>
       <c r="D4" t="n">
         <v>203.8792505293489</v>
       </c>
       <c r="E4" t="n">
-        <v>127.5629316132539</v>
+        <v>127.5629316132538</v>
       </c>
       <c r="F4" t="n">
-        <v>197.6862789255482</v>
+        <v>197.686278925548</v>
       </c>
       <c r="G4" t="n">
-        <v>435.2160672967209</v>
+        <v>435.2160672967203</v>
       </c>
       <c r="H4" t="n">
         <v>303.786520927008</v>
       </c>
       <c r="I4" t="n">
-        <v>227.4992749443257</v>
+        <v>227.4992749443255</v>
       </c>
       <c r="J4" t="n">
-        <v>358.27582458481</v>
+        <v>358.2758245848095</v>
       </c>
       <c r="K4" t="n">
-        <v>289.8569045676235</v>
+        <v>289.8569045676232</v>
       </c>
       <c r="L4" t="n">
-        <v>283.8417707608086</v>
+        <v>283.8417707608087</v>
       </c>
       <c r="M4" t="n">
-        <v>693.2679278271708</v>
+        <v>693.2679278271712</v>
       </c>
       <c r="N4" t="n">
-        <v>264.0610506442066</v>
+        <v>264.0610506442065</v>
       </c>
       <c r="O4" t="n">
-        <v>246.72325374247</v>
+        <v>246.7232537424703</v>
       </c>
       <c r="P4" t="n">
-        <v>348.1838877666311</v>
+        <v>348.1838877666303</v>
       </c>
       <c r="Q4" t="n">
-        <v>280.9352221876143</v>
+        <v>280.9352221876142</v>
       </c>
       <c r="R4" t="n">
-        <v>212.5459681591666</v>
+        <v>212.5459681591663</v>
       </c>
       <c r="S4" t="n">
         <v>280.4095820364392</v>
@@ -4682,25 +4682,25 @@
         <v>287.4600911588598</v>
       </c>
       <c r="V4" t="n">
-        <v>213.4928848315475</v>
+        <v>213.4928848315451</v>
       </c>
       <c r="W4" t="n">
-        <v>460.2267574513914</v>
+        <v>460.2267574513919</v>
       </c>
       <c r="X4" t="n">
-        <v>308.3844718049571</v>
+        <v>308.3844718049572</v>
       </c>
       <c r="Y4" t="n">
-        <v>259.7136590647963</v>
+        <v>259.7136590647955</v>
       </c>
       <c r="Z4" t="n">
-        <v>303.9068770097412</v>
+        <v>303.906877009741</v>
       </c>
       <c r="AA4" t="n">
-        <v>254.0430117918432</v>
+        <v>254.043011791843</v>
       </c>
       <c r="AB4" t="n">
-        <v>623.7864978264292</v>
+        <v>623.7864978264286</v>
       </c>
     </row>
     <row r="5">
@@ -4710,85 +4710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>131.1169215471633</v>
+        <v>131.1169215471632</v>
       </c>
       <c r="C5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="D5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="E5" t="n">
-        <v>161.0524878710732</v>
+        <v>161.0524878710731</v>
       </c>
       <c r="F5" t="n">
-        <v>141.0919314401494</v>
+        <v>141.0919314401493</v>
       </c>
       <c r="G5" t="n">
-        <v>208.4230619240788</v>
+        <v>208.4230619240785</v>
       </c>
       <c r="H5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="I5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="J5" t="n">
-        <v>194.9811188077916</v>
+        <v>194.9811188077915</v>
       </c>
       <c r="K5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="L5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="M5" t="n">
-        <v>195.1461784028577</v>
+        <v>195.1461784028576</v>
       </c>
       <c r="N5" t="n">
-        <v>264.0610506442066</v>
+        <v>145.5127924796944</v>
       </c>
       <c r="O5" t="n">
-        <v>159.1524778936153</v>
+        <v>159.1524778936149</v>
       </c>
       <c r="P5" t="n">
-        <v>155.8090614173556</v>
+        <v>155.8090614173554</v>
       </c>
       <c r="Q5" t="n">
-        <v>118.5337111771807</v>
+        <v>118.5337111771805</v>
       </c>
       <c r="R5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="S5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="T5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="U5" t="n">
-        <v>163.885273692884</v>
+        <v>163.8852736928838</v>
       </c>
       <c r="V5" t="n">
-        <v>176.5885975170357</v>
+        <v>176.5885975170355</v>
       </c>
       <c r="W5" t="n">
-        <v>195.1587619916703</v>
+        <v>195.15876199167</v>
       </c>
       <c r="X5" t="n">
         <v>124.4021197992589</v>
       </c>
       <c r="Y5" t="n">
-        <v>258.7934795157189</v>
+        <v>258.7934795157187</v>
       </c>
       <c r="Z5" t="n">
-        <v>129.9275452279543</v>
+        <v>129.9275452279541</v>
       </c>
       <c r="AA5" t="n">
-        <v>195.1461784028559</v>
+        <v>195.1461784028556</v>
       </c>
       <c r="AB5" t="n">
-        <v>262.0300912328395</v>
+        <v>262.0300912328389</v>
       </c>
     </row>
     <row r="6">
@@ -4798,85 +4798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>115.4933234961387</v>
+        <v>115.4933234961386</v>
       </c>
       <c r="C6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="D6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="E6" t="n">
         <v>133.6066768796406</v>
       </c>
       <c r="F6" t="n">
-        <v>84.75652631003899</v>
+        <v>84.75652631003905</v>
       </c>
       <c r="G6" t="n">
         <v>139.0414999551188</v>
       </c>
       <c r="H6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="I6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="J6" t="n">
-        <v>138.8764377774823</v>
+        <v>138.8764377774825</v>
       </c>
       <c r="K6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="L6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="M6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="N6" t="n">
-        <v>264.0610506442066</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="O6" t="n">
-        <v>146.84533479995</v>
+        <v>146.8453347999502</v>
       </c>
       <c r="P6" t="n">
-        <v>148.542534987416</v>
+        <v>148.5425349874162</v>
       </c>
       <c r="Q6" t="n">
         <v>139.0414999551188</v>
       </c>
       <c r="R6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="S6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="T6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="U6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="V6" t="n">
-        <v>165.1681724569972</v>
+        <v>165.1681724569973</v>
       </c>
       <c r="W6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="X6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="Y6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="Z6" t="n">
-        <v>124.8440435359061</v>
+        <v>124.8440435359062</v>
       </c>
       <c r="AA6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
       <c r="AB6" t="n">
-        <v>139.0414973725468</v>
+        <v>139.0414973725469</v>
       </c>
     </row>
     <row r="7">
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.33109364397447</v>
+        <v>83.33109364397444</v>
       </c>
       <c r="C7" t="n">
-        <v>86.53780632616703</v>
+        <v>86.537806326167</v>
       </c>
       <c r="D7" t="n">
-        <v>85.16381333882683</v>
+        <v>85.16381333882687</v>
       </c>
       <c r="E7" t="n">
-        <v>32.52802181821487</v>
+        <v>32.5280218182149</v>
       </c>
       <c r="F7" t="n">
-        <v>85.3650634092393</v>
+        <v>85.36506340923924</v>
       </c>
       <c r="G7" t="n">
         <v>79.01126428269032</v>
       </c>
       <c r="H7" t="n">
-        <v>83.33512790509469</v>
+        <v>83.33512790509471</v>
       </c>
       <c r="I7" t="n">
-        <v>84.71154199502689</v>
+        <v>84.71154199502692</v>
       </c>
       <c r="J7" t="n">
-        <v>81.16095801849663</v>
+        <v>81.16095801849661</v>
       </c>
       <c r="K7" t="n">
-        <v>83.25292402590696</v>
+        <v>83.25292402590694</v>
       </c>
       <c r="L7" t="n">
-        <v>83.09964868972487</v>
+        <v>83.09964868972483</v>
       </c>
       <c r="M7" t="n">
         <v>74.1864442338867</v>
       </c>
       <c r="N7" t="n">
-        <v>83.71646355867897</v>
+        <v>83.71646355867892</v>
       </c>
       <c r="O7" t="n">
         <v>83.78801008711925</v>
       </c>
       <c r="P7" t="n">
-        <v>81.38500879217861</v>
+        <v>81.38500879217867</v>
       </c>
       <c r="Q7" t="n">
-        <v>83.34702562666055</v>
+        <v>83.34702562666047</v>
       </c>
       <c r="R7" t="n">
-        <v>85.05115007687228</v>
+        <v>85.05115007687235</v>
       </c>
       <c r="S7" t="n">
-        <v>82.81334799241561</v>
+        <v>82.81334799241549</v>
       </c>
       <c r="T7" t="n">
-        <v>85.06624827862142</v>
+        <v>85.06624827862136</v>
       </c>
       <c r="U7" t="n">
         <v>83.04596457477187</v>
       </c>
       <c r="V7" t="n">
-        <v>50.31824021376322</v>
+        <v>50.31824021376318</v>
       </c>
       <c r="W7" t="n">
-        <v>79.42763582709946</v>
+        <v>79.42763582709939</v>
       </c>
       <c r="X7" t="n">
-        <v>82.90487948801049</v>
+        <v>82.90487948801048</v>
       </c>
       <c r="Y7" t="n">
-        <v>83.82120036971077</v>
+        <v>83.82120036971082</v>
       </c>
       <c r="Z7" t="n">
-        <v>82.34850674291638</v>
+        <v>82.34850674291634</v>
       </c>
       <c r="AA7" t="n">
-        <v>83.92369990007984</v>
+        <v>83.92369990007985</v>
       </c>
       <c r="AB7" t="n">
-        <v>76.72082195618987</v>
+        <v>76.72082195618981</v>
       </c>
     </row>
     <row r="8">
@@ -4974,28 +4974,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85.58145377534122</v>
+        <v>85.58145377534123</v>
       </c>
       <c r="C8" t="n">
-        <v>86.50410067659631</v>
+        <v>86.50410067659628</v>
       </c>
       <c r="D8" t="n">
-        <v>86.11371045815913</v>
+        <v>86.11371045815906</v>
       </c>
       <c r="E8" t="n">
-        <v>33.93117865535386</v>
+        <v>33.93117865535391</v>
       </c>
       <c r="F8" t="n">
-        <v>86.17280075791676</v>
+        <v>86.17280075791672</v>
       </c>
       <c r="G8" t="n">
-        <v>84.34284485403444</v>
+        <v>84.3428448540344</v>
       </c>
       <c r="H8" t="n">
-        <v>85.59880476880272</v>
+        <v>85.59880476880274</v>
       </c>
       <c r="I8" t="n">
-        <v>85.98606466315348</v>
+        <v>85.98606466315346</v>
       </c>
       <c r="J8" t="n">
         <v>84.91802565669653</v>
@@ -5004,43 +5004,43 @@
         <v>85.56942559032035</v>
       </c>
       <c r="L8" t="n">
-        <v>85.51983417341179</v>
+        <v>85.51983417341177</v>
       </c>
       <c r="M8" t="n">
-        <v>83.00176061513923</v>
+        <v>83.0017606151392</v>
       </c>
       <c r="N8" t="n">
-        <v>85.69945617533048</v>
+        <v>85.69945617533043</v>
       </c>
       <c r="O8" t="n">
-        <v>85.7118479886053</v>
+        <v>85.71184798860527</v>
       </c>
       <c r="P8" t="n">
-        <v>85.02103220500504</v>
+        <v>85.02103220500501</v>
       </c>
       <c r="Q8" t="n">
-        <v>85.59537308387561</v>
+        <v>85.59537308387566</v>
       </c>
       <c r="R8" t="n">
-        <v>86.08340911313761</v>
+        <v>86.08340911313758</v>
       </c>
       <c r="S8" t="n">
-        <v>85.43540169227674</v>
+        <v>85.43540169227671</v>
       </c>
       <c r="T8" t="n">
-        <v>86.08624975777448</v>
+        <v>86.08624975777435</v>
       </c>
       <c r="U8" t="n">
-        <v>85.5037210063856</v>
+        <v>85.50372100638562</v>
       </c>
       <c r="V8" t="n">
-        <v>52.13266443495441</v>
+        <v>52.13266443495438</v>
       </c>
       <c r="W8" t="n">
-        <v>84.47249685584146</v>
+        <v>84.47249685584147</v>
       </c>
       <c r="X8" t="n">
-        <v>85.47076231409804</v>
+        <v>85.47076231409794</v>
       </c>
       <c r="Y8" t="n">
         <v>85.72819379329077</v>
@@ -5049,10 +5049,10 @@
         <v>85.30051825537731</v>
       </c>
       <c r="AA8" t="n">
-        <v>85.75694076084977</v>
+        <v>85.75694076084966</v>
       </c>
       <c r="AB8" t="n">
-        <v>83.71395400073254</v>
+        <v>83.71395400073251</v>
       </c>
     </row>
   </sheetData>
@@ -5218,85 +5218,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86.78965617885336</v>
+        <v>86.78965617885329</v>
       </c>
       <c r="C2" t="n">
-        <v>86.36328203056064</v>
+        <v>86.3632820305606</v>
       </c>
       <c r="D2" t="n">
-        <v>86.34584640609671</v>
+        <v>86.34584640609664</v>
       </c>
       <c r="E2" t="n">
-        <v>34.23657174213751</v>
+        <v>34.23657174213746</v>
       </c>
       <c r="F2" t="n">
-        <v>86.47343205672718</v>
+        <v>86.47343205672713</v>
       </c>
       <c r="G2" t="n">
-        <v>86.64071952038361</v>
+        <v>86.64071952038357</v>
       </c>
       <c r="H2" t="n">
-        <v>86.72694017419033</v>
+        <v>86.7269401741903</v>
       </c>
       <c r="I2" t="n">
-        <v>86.61636727525504</v>
+        <v>86.61636727525507</v>
       </c>
       <c r="J2" t="n">
-        <v>86.61376472476772</v>
+        <v>86.61376472476768</v>
       </c>
       <c r="K2" t="n">
-        <v>86.60207296114412</v>
+        <v>86.60207296114409</v>
       </c>
       <c r="L2" t="n">
-        <v>86.50394214976646</v>
+        <v>86.50394214976642</v>
       </c>
       <c r="M2" t="n">
-        <v>86.47429863806525</v>
+        <v>86.47429863806522</v>
       </c>
       <c r="N2" t="n">
-        <v>86.67554206013548</v>
+        <v>86.67554206013543</v>
       </c>
       <c r="O2" t="n">
-        <v>86.91369545734553</v>
+        <v>86.91369545734547</v>
       </c>
       <c r="P2" t="n">
-        <v>86.66140360691048</v>
+        <v>86.66140360691044</v>
       </c>
       <c r="Q2" t="n">
-        <v>86.6965971654472</v>
+        <v>86.69659716544717</v>
       </c>
       <c r="R2" t="n">
-        <v>86.55711874071363</v>
+        <v>86.55711874071361</v>
       </c>
       <c r="S2" t="n">
-        <v>86.62609630864023</v>
+        <v>86.62609630864021</v>
       </c>
       <c r="T2" t="n">
-        <v>86.3831355494569</v>
+        <v>86.3831355494568</v>
       </c>
       <c r="U2" t="n">
         <v>86.58693930544763</v>
       </c>
       <c r="V2" t="n">
-        <v>53.03514580449738</v>
+        <v>53.0351458044974</v>
       </c>
       <c r="W2" t="n">
-        <v>87.04806866088617</v>
+        <v>87.04806866088613</v>
       </c>
       <c r="X2" t="n">
         <v>87.5216400692411</v>
       </c>
       <c r="Y2" t="n">
-        <v>86.99298573858349</v>
+        <v>86.99298573858344</v>
       </c>
       <c r="Z2" t="n">
-        <v>86.72542031119924</v>
+        <v>86.7254203111992</v>
       </c>
       <c r="AA2" t="n">
-        <v>86.71860014480268</v>
+        <v>86.71860014480264</v>
       </c>
       <c r="AB2" t="n">
-        <v>86.45394867431837</v>
+        <v>86.45394867431831</v>
       </c>
     </row>
     <row r="3">
@@ -5315,7 +5315,7 @@
         <v>86.85537345433994</v>
       </c>
       <c r="E3" t="n">
-        <v>33.9952381767829</v>
+        <v>33.99523817678289</v>
       </c>
       <c r="F3" t="n">
         <v>86.855371514815</v>
@@ -5330,7 +5330,7 @@
         <v>86.85537345433994</v>
       </c>
       <c r="J3" t="n">
-        <v>86.82155633641676</v>
+        <v>86.8215563364168</v>
       </c>
       <c r="K3" t="n">
         <v>86.85537230790605</v>
@@ -5345,7 +5345,7 @@
         <v>86.85537345433994</v>
       </c>
       <c r="O3" t="n">
-        <v>86.85537049196377</v>
+        <v>86.85537049196375</v>
       </c>
       <c r="P3" t="n">
         <v>86.85537311935948</v>
@@ -5366,7 +5366,7 @@
         <v>86.85537752761984</v>
       </c>
       <c r="V3" t="n">
-        <v>52.6682165607187</v>
+        <v>52.66821656071857</v>
       </c>
       <c r="W3" t="n">
         <v>86.85537345433994</v>
@@ -5384,7 +5384,7 @@
         <v>86.85537345433994</v>
       </c>
       <c r="AB3" t="n">
-        <v>86.85541269028414</v>
+        <v>86.85541269028413</v>
       </c>
     </row>
     <row r="4">
@@ -5394,85 +5394,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>239.6051872406019</v>
+        <v>239.6051872406024</v>
       </c>
       <c r="C4" t="n">
-        <v>152.0111639567094</v>
+        <v>152.0111639567092</v>
       </c>
       <c r="D4" t="n">
-        <v>149.0170458772228</v>
+        <v>149.0170458772226</v>
       </c>
       <c r="E4" t="n">
-        <v>85.81322471562449</v>
+        <v>85.81322471562436</v>
       </c>
       <c r="F4" t="n">
-        <v>178.582476402271</v>
+        <v>178.5824764022709</v>
       </c>
       <c r="G4" t="n">
-        <v>209.379380675994</v>
+        <v>209.3793806759946</v>
       </c>
       <c r="H4" t="n">
         <v>250.8752718524103</v>
       </c>
       <c r="I4" t="n">
-        <v>215.6603810861073</v>
+        <v>215.660381086107</v>
       </c>
       <c r="J4" t="n">
-        <v>213.0898914690509</v>
+        <v>213.0898914690513</v>
       </c>
       <c r="K4" t="n">
-        <v>211.3735614049141</v>
+        <v>211.373561404914</v>
       </c>
       <c r="L4" t="n">
-        <v>187.7983694980684</v>
+        <v>187.798369498068</v>
       </c>
       <c r="M4" t="n">
-        <v>189.0888975830175</v>
+        <v>189.0888975830173</v>
       </c>
       <c r="N4" t="n">
-        <v>221.0291786478981</v>
+        <v>221.0291786478979</v>
       </c>
       <c r="O4" t="n">
-        <v>265.4813412304123</v>
+        <v>265.4813412304125</v>
       </c>
       <c r="P4" t="n">
-        <v>208.4941358578687</v>
+        <v>208.4941358578689</v>
       </c>
       <c r="Q4" t="n">
-        <v>222.6228987406344</v>
+        <v>222.6228987406343</v>
       </c>
       <c r="R4" t="n">
-        <v>201.9177831089651</v>
+        <v>201.9177831089648</v>
       </c>
       <c r="S4" t="n">
-        <v>200.9774076727565</v>
+        <v>200.9774076727566</v>
       </c>
       <c r="T4" t="n">
-        <v>158.9587116879574</v>
+        <v>158.9587116879572</v>
       </c>
       <c r="U4" t="n">
-        <v>201.1934669366878</v>
+        <v>201.1934669366876</v>
       </c>
       <c r="V4" t="n">
-        <v>218.7939132829462</v>
+        <v>218.7939132829478</v>
       </c>
       <c r="W4" t="n">
-        <v>309.9343499526528</v>
+        <v>309.9343499526522</v>
       </c>
       <c r="X4" t="n">
-        <v>428.2070645884031</v>
+        <v>428.2070645884033</v>
       </c>
       <c r="Y4" t="n">
-        <v>303.0144240923485</v>
+        <v>303.0144240923489</v>
       </c>
       <c r="Z4" t="n">
-        <v>222.3763697564778</v>
+        <v>222.3763697564774</v>
       </c>
       <c r="AA4" t="n">
-        <v>232.8618899727204</v>
+        <v>232.8618899727209</v>
       </c>
       <c r="AB4" t="n">
-        <v>177.8888159138369</v>
+        <v>177.8888159138367</v>
       </c>
     </row>
     <row r="5">
@@ -5482,85 +5482,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>122.4982550446899</v>
+        <v>122.4982550446895</v>
       </c>
       <c r="C5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="D5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="E5" t="n">
-        <v>149.8899473516087</v>
+        <v>149.8899473516082</v>
       </c>
       <c r="F5" t="n">
-        <v>131.6256053942053</v>
+        <v>131.6256053942049</v>
       </c>
       <c r="G5" t="n">
-        <v>193.235049790314</v>
+        <v>193.2350497903133</v>
       </c>
       <c r="H5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="I5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="J5" t="n">
-        <v>180.927802443027</v>
+        <v>180.9278024430264</v>
       </c>
       <c r="K5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="L5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="M5" t="n">
-        <v>181.0864134733861</v>
+        <v>181.0864134733854</v>
       </c>
       <c r="N5" t="n">
-        <v>221.0291786478981</v>
+        <v>135.6707891070816</v>
       </c>
       <c r="O5" t="n">
-        <v>148.151397022973</v>
+        <v>148.1513970229723</v>
       </c>
       <c r="P5" t="n">
-        <v>145.0920984487176</v>
+        <v>145.0920984487171</v>
       </c>
       <c r="Q5" t="n">
-        <v>110.9843447026065</v>
+        <v>110.9843447026062</v>
       </c>
       <c r="R5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="S5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="T5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="U5" t="n">
-        <v>152.4859595936701</v>
+        <v>152.4859595936697</v>
       </c>
       <c r="V5" t="n">
-        <v>164.0623394602262</v>
+        <v>164.0623394602258</v>
       </c>
       <c r="W5" t="n">
-        <v>181.0979277304703</v>
+        <v>181.0979277304697</v>
       </c>
       <c r="X5" t="n">
-        <v>116.3540658422356</v>
+        <v>116.3540658422352</v>
       </c>
       <c r="Y5" t="n">
-        <v>239.331834476146</v>
+        <v>239.3318344761451</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.4099499222152</v>
+        <v>121.4099499222148</v>
       </c>
       <c r="AA5" t="n">
-        <v>181.0864134733874</v>
+        <v>181.0864134733868</v>
       </c>
       <c r="AB5" t="n">
-        <v>242.2866440191505</v>
+        <v>242.2866440191498</v>
       </c>
     </row>
     <row r="6">
@@ -5570,85 +5570,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>102.0264245214665</v>
+        <v>102.0264245214663</v>
       </c>
       <c r="C6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="D6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="E6" t="n">
-        <v>117.2867532477485</v>
+        <v>117.2867532477482</v>
       </c>
       <c r="F6" t="n">
-        <v>76.13096391171433</v>
+        <v>76.13096391171425</v>
       </c>
       <c r="G6" t="n">
-        <v>121.8655402313081</v>
+        <v>121.865540231308</v>
       </c>
       <c r="H6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="I6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="J6" t="n">
-        <v>121.7069227884059</v>
+        <v>121.7069227884055</v>
       </c>
       <c r="K6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="L6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="M6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="N6" t="n">
-        <v>221.0291786478981</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="O6" t="n">
-        <v>128.4401972004738</v>
+        <v>128.4401972004735</v>
       </c>
       <c r="P6" t="n">
-        <v>129.8700722891249</v>
+        <v>129.8700722891247</v>
       </c>
       <c r="Q6" t="n">
-        <v>121.8655402313081</v>
+        <v>121.865540231308</v>
       </c>
       <c r="R6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="S6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="T6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="U6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="V6" t="n">
-        <v>143.753203590847</v>
+        <v>143.7532035908468</v>
       </c>
       <c r="W6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="X6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="Y6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="Z6" t="n">
         <v>109.9043176212754</v>
       </c>
       <c r="AA6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
       <c r="AB6" t="n">
-        <v>121.8655338187662</v>
+        <v>121.8655338187661</v>
       </c>
     </row>
     <row r="7">
@@ -5658,85 +5658,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82.94384805336385</v>
+        <v>82.94384805336381</v>
       </c>
       <c r="C7" t="n">
-        <v>85.50138943962287</v>
+        <v>85.50138943962288</v>
       </c>
       <c r="D7" t="n">
-        <v>85.60521505755749</v>
+        <v>85.60521505755743</v>
       </c>
       <c r="E7" t="n">
-        <v>32.95287679720779</v>
+        <v>32.95287679720776</v>
       </c>
       <c r="F7" t="n">
-        <v>84.86809465391063</v>
+        <v>84.86809465391065</v>
       </c>
       <c r="G7" t="n">
-        <v>83.83163521503585</v>
+        <v>83.83163521503592</v>
       </c>
       <c r="H7" t="n">
-        <v>83.39711552274912</v>
+        <v>83.3971155227491</v>
       </c>
       <c r="I7" t="n">
-        <v>84.02611709852094</v>
+        <v>84.02611709852087</v>
       </c>
       <c r="J7" t="n">
         <v>83.7690699454251</v>
       </c>
       <c r="K7" t="n">
-        <v>84.10032224349564</v>
+        <v>84.10032224349561</v>
       </c>
       <c r="L7" t="n">
-        <v>84.65809321853497</v>
+        <v>84.65809321853502</v>
       </c>
       <c r="M7" t="n">
-        <v>84.86074995426119</v>
+        <v>84.86074995426118</v>
       </c>
       <c r="N7" t="n">
-        <v>83.66015062760994</v>
+        <v>83.66015062760999</v>
       </c>
       <c r="O7" t="n">
-        <v>82.20072488867989</v>
+        <v>82.20072488867987</v>
       </c>
       <c r="P7" t="n">
-        <v>83.70042447518919</v>
+        <v>83.70042447518921</v>
       </c>
       <c r="Q7" t="n">
-        <v>83.5419803295658</v>
+        <v>83.54198032956585</v>
       </c>
       <c r="R7" t="n">
-        <v>84.37789297940822</v>
+        <v>84.3778929794082</v>
       </c>
       <c r="S7" t="n">
-        <v>83.9262636176868</v>
+        <v>83.92626361768684</v>
       </c>
       <c r="T7" t="n">
-        <v>85.38776747045449</v>
+        <v>85.38776747045452</v>
       </c>
       <c r="U7" t="n">
         <v>84.16467618999303</v>
       </c>
       <c r="V7" t="n">
-        <v>49.35987454192171</v>
+        <v>49.35987454192161</v>
       </c>
       <c r="W7" t="n">
-        <v>81.45049357454477</v>
+        <v>81.45049357454474</v>
       </c>
       <c r="X7" t="n">
-        <v>78.71019862717017</v>
+        <v>78.71019862717021</v>
       </c>
       <c r="Y7" t="n">
-        <v>81.7839035130373</v>
+        <v>81.78390351303727</v>
       </c>
       <c r="Z7" t="n">
-        <v>83.33001761878828</v>
+        <v>83.33001761878826</v>
       </c>
       <c r="AA7" t="n">
-        <v>83.39791374129483</v>
+        <v>83.39791374129474</v>
       </c>
       <c r="AB7" t="n">
-        <v>84.97265313037994</v>
+        <v>84.97265313037991</v>
       </c>
     </row>
     <row r="8">
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85.00989965611734</v>
+        <v>85.00989965611733</v>
       </c>
       <c r="C8" t="n">
-        <v>85.74721674947432</v>
+        <v>85.74721674947426</v>
       </c>
       <c r="D8" t="n">
-        <v>85.77702035154226</v>
+        <v>85.77702035154222</v>
       </c>
       <c r="E8" t="n">
-        <v>33.7622939926222</v>
+        <v>33.76229399262219</v>
       </c>
       <c r="F8" t="n">
-        <v>85.56921475194015</v>
+        <v>85.56921475194008</v>
       </c>
       <c r="G8" t="n">
-        <v>85.26490934655391</v>
+        <v>85.26490934655398</v>
       </c>
       <c r="H8" t="n">
-        <v>85.15342179450241</v>
+        <v>85.15342179450231</v>
       </c>
       <c r="I8" t="n">
-        <v>85.32904661705243</v>
+        <v>85.32904661705244</v>
       </c>
       <c r="J8" t="n">
-        <v>85.22487368916953</v>
+        <v>85.22487368916944</v>
       </c>
       <c r="K8" t="n">
-        <v>85.34851640201374</v>
+        <v>85.34851640201373</v>
       </c>
       <c r="L8" t="n">
-        <v>85.50417264015856</v>
+        <v>85.50417264015852</v>
       </c>
       <c r="M8" t="n">
-        <v>85.56673976017518</v>
+        <v>85.56673976017521</v>
       </c>
       <c r="N8" t="n">
-        <v>85.22170549140239</v>
+        <v>85.22170549140228</v>
       </c>
       <c r="O8" t="n">
         <v>84.79581687437597</v>
       </c>
       <c r="P8" t="n">
-        <v>85.22589191958819</v>
+        <v>85.22589191958822</v>
       </c>
       <c r="Q8" t="n">
-        <v>85.18899275164566</v>
+        <v>85.18899275164564</v>
       </c>
       <c r="R8" t="n">
-        <v>85.42985527550924</v>
+        <v>85.4298552755092</v>
       </c>
       <c r="S8" t="n">
-        <v>85.29334199844385</v>
+        <v>85.29334199844384</v>
       </c>
       <c r="T8" t="n">
-        <v>85.71537169603657</v>
+        <v>85.7153716960366</v>
       </c>
       <c r="U8" t="n">
-        <v>85.36266162207109</v>
+        <v>85.36266162207106</v>
       </c>
       <c r="V8" t="n">
-        <v>51.52983964288431</v>
+        <v>51.52983964288433</v>
       </c>
       <c r="W8" t="n">
-        <v>84.58883109124913</v>
+        <v>84.58883109124915</v>
       </c>
       <c r="X8" t="n">
-        <v>83.81554781235479</v>
+        <v>83.81554781235477</v>
       </c>
       <c r="Y8" t="n">
-        <v>84.68545408466885</v>
+        <v>84.68545408466883</v>
       </c>
       <c r="Z8" t="n">
-        <v>85.12137232864178</v>
+        <v>85.12137232864174</v>
       </c>
       <c r="AA8" t="n">
         <v>85.14544495709671</v>
       </c>
       <c r="AB8" t="n">
-        <v>85.5972870745633</v>
+        <v>85.59728707456318</v>
       </c>
     </row>
   </sheetData>
@@ -5990,85 +5990,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86.4494422680748</v>
+        <v>86.44944226807468</v>
       </c>
       <c r="C2" t="n">
-        <v>86.13395023890837</v>
+        <v>86.13395023890823</v>
       </c>
       <c r="D2" t="n">
-        <v>86.2346072955451</v>
+        <v>86.23460729554499</v>
       </c>
       <c r="E2" t="n">
-        <v>34.22163949221851</v>
+        <v>34.22163949221848</v>
       </c>
       <c r="F2" t="n">
-        <v>86.26930208423644</v>
+        <v>86.26930208423632</v>
       </c>
       <c r="G2" t="n">
-        <v>86.37587921696684</v>
+        <v>86.3758792169666</v>
       </c>
       <c r="H2" t="n">
-        <v>86.45377104882481</v>
+        <v>86.45377104882471</v>
       </c>
       <c r="I2" t="n">
-        <v>86.57021159498059</v>
+        <v>86.57021159498048</v>
       </c>
       <c r="J2" t="n">
-        <v>86.36634040027458</v>
+        <v>86.36634040027452</v>
       </c>
       <c r="K2" t="n">
-        <v>86.38395774604285</v>
+        <v>86.38395774604281</v>
       </c>
       <c r="L2" t="n">
-        <v>86.28828789600421</v>
+        <v>86.28828789600418</v>
       </c>
       <c r="M2" t="n">
-        <v>86.31229005998176</v>
+        <v>86.31229005998168</v>
       </c>
       <c r="N2" t="n">
-        <v>86.3388309222051</v>
+        <v>86.33883092220495</v>
       </c>
       <c r="O2" t="n">
-        <v>86.65107794794687</v>
+        <v>86.65107794794683</v>
       </c>
       <c r="P2" t="n">
-        <v>86.49270114104746</v>
+        <v>86.49270114104738</v>
       </c>
       <c r="Q2" t="n">
-        <v>86.33143621916702</v>
+        <v>86.33143621916693</v>
       </c>
       <c r="R2" t="n">
-        <v>86.5999805052072</v>
+        <v>86.5999805052071</v>
       </c>
       <c r="S2" t="n">
-        <v>86.38250549230918</v>
+        <v>86.38250549230906</v>
       </c>
       <c r="T2" t="n">
-        <v>86.21981301203458</v>
+        <v>86.21981301203451</v>
       </c>
       <c r="U2" t="n">
-        <v>86.38006666986188</v>
+        <v>86.38006666986185</v>
       </c>
       <c r="V2" t="n">
-        <v>52.8402174665032</v>
+        <v>52.84021746650321</v>
       </c>
       <c r="W2" t="n">
-        <v>86.77093919585931</v>
+        <v>86.7709391958592</v>
       </c>
       <c r="X2" t="n">
-        <v>87.57322234849536</v>
+        <v>87.57322234849529</v>
       </c>
       <c r="Y2" t="n">
-        <v>86.71058011194667</v>
+        <v>86.7105801119465</v>
       </c>
       <c r="Z2" t="n">
-        <v>86.32139598257136</v>
+        <v>86.32139598257129</v>
       </c>
       <c r="AA2" t="n">
-        <v>86.5926488953141</v>
+        <v>86.59264889531407</v>
       </c>
       <c r="AB2" t="n">
-        <v>86.30607026481898</v>
+        <v>86.30607026481894</v>
       </c>
     </row>
     <row r="3">
@@ -6078,85 +6078,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>86.67730292280845</v>
+        <v>86.67730292280844</v>
       </c>
       <c r="C3" t="n">
-        <v>86.67729906873615</v>
+        <v>86.67729906873613</v>
       </c>
       <c r="D3" t="n">
-        <v>86.67730292280845</v>
+        <v>86.67730292280844</v>
       </c>
       <c r="E3" t="n">
-        <v>33.94790660445486</v>
+        <v>33.94790660445481</v>
       </c>
       <c r="F3" t="n">
-        <v>86.67730034853641</v>
+        <v>86.67730034853639</v>
       </c>
       <c r="G3" t="n">
-        <v>86.67730169531762</v>
+        <v>86.67730169531761</v>
       </c>
       <c r="H3" t="n">
-        <v>86.67730292280845</v>
+        <v>86.67730292280844</v>
       </c>
       <c r="I3" t="n">
-        <v>86.67730292280845</v>
+        <v>86.67730292280844</v>
       </c>
       <c r="J3" t="n">
-        <v>86.64643731926819</v>
+        <v>86.64643731926812</v>
       </c>
       <c r="K3" t="n">
-        <v>86.6773014531274</v>
+        <v>86.67730145312737</v>
       </c>
       <c r="L3" t="n">
-        <v>86.67730292280845</v>
+        <v>86.67730292280844</v>
       </c>
       <c r="M3" t="n">
-        <v>86.67729625148289</v>
+        <v>86.67729625148286</v>
       </c>
       <c r="N3" t="n">
-        <v>86.67730292280845</v>
+        <v>86.67730292280844</v>
       </c>
       <c r="O3" t="n">
-        <v>86.67729953388763</v>
+        <v>86.67729953388762</v>
       </c>
       <c r="P3" t="n">
-        <v>86.67729654345607</v>
+        <v>86.67729654345604</v>
       </c>
       <c r="Q3" t="n">
-        <v>86.67730288516474</v>
+        <v>86.67730288516472</v>
       </c>
       <c r="R3" t="n">
-        <v>86.67731120055477</v>
+        <v>86.67731120055475</v>
       </c>
       <c r="S3" t="n">
-        <v>86.67730292280845</v>
+        <v>86.67730292280844</v>
       </c>
       <c r="T3" t="n">
-        <v>86.67729804247554</v>
+        <v>86.67729804247551</v>
       </c>
       <c r="U3" t="n">
-        <v>86.67731450352154</v>
+        <v>86.67731450352153</v>
       </c>
       <c r="V3" t="n">
-        <v>52.51961544634562</v>
+        <v>52.51961544634564</v>
       </c>
       <c r="W3" t="n">
-        <v>86.67730292280845</v>
+        <v>86.67730292280844</v>
       </c>
       <c r="X3" t="n">
-        <v>86.67731476522923</v>
+        <v>86.67731476522921</v>
       </c>
       <c r="Y3" t="n">
-        <v>86.67729007760234</v>
+        <v>86.67729007760232</v>
       </c>
       <c r="Z3" t="n">
-        <v>86.67730258273316</v>
+        <v>86.67730258273315</v>
       </c>
       <c r="AA3" t="n">
-        <v>86.67730292280845</v>
+        <v>86.67730292280844</v>
       </c>
       <c r="AB3" t="n">
-        <v>86.67734215875265</v>
+        <v>86.67734215875264</v>
       </c>
     </row>
     <row r="4">
@@ -6166,46 +6166,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>200.8830085006546</v>
+        <v>200.8830085006545</v>
       </c>
       <c r="C4" t="n">
         <v>137.4170306028424</v>
       </c>
       <c r="D4" t="n">
-        <v>162.6769454919038</v>
+        <v>162.6769454919037</v>
       </c>
       <c r="E4" t="n">
-        <v>98.73593351582781</v>
+        <v>98.73593351582784</v>
       </c>
       <c r="F4" t="n">
-        <v>171.1633724511447</v>
+        <v>171.1633724511448</v>
       </c>
       <c r="G4" t="n">
-        <v>188.0284823715655</v>
+        <v>188.0284823715444</v>
       </c>
       <c r="H4" t="n">
-        <v>224.6579113376993</v>
+        <v>224.6579113376994</v>
       </c>
       <c r="I4" t="n">
-        <v>248.8441064713166</v>
+        <v>248.8441064713164</v>
       </c>
       <c r="J4" t="n">
-        <v>196.1681144650351</v>
+        <v>196.1681144650306</v>
       </c>
       <c r="K4" t="n">
-        <v>199.7656116269966</v>
+        <v>199.7656116269969</v>
       </c>
       <c r="L4" t="n">
         <v>175.3552490962806</v>
       </c>
       <c r="M4" t="n">
-        <v>186.8785341914478</v>
+        <v>186.8785341914481</v>
       </c>
       <c r="N4" t="n">
-        <v>182.1154705515552</v>
+        <v>182.1154705515551</v>
       </c>
       <c r="O4" t="n">
-        <v>246.2110734708331</v>
+        <v>246.211073470833</v>
       </c>
       <c r="P4" t="n">
         <v>209.8066877749947</v>
@@ -6214,37 +6214,37 @@
         <v>180.8871569135985</v>
       </c>
       <c r="R4" t="n">
-        <v>259.3841713215162</v>
+        <v>259.3841713215157</v>
       </c>
       <c r="S4" t="n">
         <v>186.7932643116058</v>
       </c>
       <c r="T4" t="n">
-        <v>158.5242291411583</v>
+        <v>158.5242291411582</v>
       </c>
       <c r="U4" t="n">
-        <v>192.7578764404621</v>
+        <v>192.757876440462</v>
       </c>
       <c r="V4" t="n">
-        <v>207.3896472039431</v>
+        <v>207.3896472039435</v>
       </c>
       <c r="W4" t="n">
-        <v>286.9271712305754</v>
+        <v>286.9271712305757</v>
       </c>
       <c r="X4" t="n">
-        <v>477.9728475650045</v>
+        <v>477.9728475650065</v>
       </c>
       <c r="Y4" t="n">
-        <v>276.6769405336455</v>
+        <v>276.676940533647</v>
       </c>
       <c r="Z4" t="n">
-        <v>172.056294353769</v>
+        <v>172.0562943537689</v>
       </c>
       <c r="AA4" t="n">
-        <v>245.4313330491122</v>
+        <v>245.4313330491123</v>
       </c>
       <c r="AB4" t="n">
-        <v>185.1496796968966</v>
+        <v>185.1496796968964</v>
       </c>
     </row>
     <row r="5">
@@ -6263,13 +6263,13 @@
         <v>180.518097691018</v>
       </c>
       <c r="E5" t="n">
-        <v>149.4267663115994</v>
+        <v>149.4267663115992</v>
       </c>
       <c r="F5" t="n">
         <v>131.2239767390133</v>
       </c>
       <c r="G5" t="n">
-        <v>192.6257920709872</v>
+        <v>192.6257920709874</v>
       </c>
       <c r="H5" t="n">
         <v>180.518097691018</v>
@@ -6278,7 +6278,7 @@
         <v>180.518097691018</v>
       </c>
       <c r="J5" t="n">
-        <v>180.3601019148566</v>
+        <v>180.3601019148568</v>
       </c>
       <c r="K5" t="n">
         <v>180.518097691018</v>
@@ -6287,19 +6287,19 @@
         <v>180.518097691018</v>
       </c>
       <c r="M5" t="n">
-        <v>180.5180976910167</v>
+        <v>180.5180976910168</v>
       </c>
       <c r="N5" t="n">
-        <v>182.1154705515552</v>
+        <v>135.2555278389733</v>
       </c>
       <c r="O5" t="n">
-        <v>147.6940750454478</v>
+        <v>147.6940750454477</v>
       </c>
       <c r="P5" t="n">
-        <v>144.6450865673934</v>
+        <v>144.6450865673932</v>
       </c>
       <c r="Q5" t="n">
-        <v>110.6522788503092</v>
+        <v>110.6522788503094</v>
       </c>
       <c r="R5" t="n">
         <v>180.518097691018</v>
@@ -6311,10 +6311,10 @@
         <v>180.518097691018</v>
       </c>
       <c r="U5" t="n">
-        <v>152.014575678556</v>
+        <v>152.0145756785562</v>
       </c>
       <c r="V5" t="n">
-        <v>163.5525382887696</v>
+        <v>163.5525382887697</v>
       </c>
       <c r="W5" t="n">
         <v>180.5295731441931</v>
@@ -6323,16 +6323,16 @@
         <v>116.0039035733709</v>
       </c>
       <c r="Y5" t="n">
-        <v>238.5681605619894</v>
+        <v>238.5681605619893</v>
       </c>
       <c r="Z5" t="n">
-        <v>121.0427488942225</v>
+        <v>121.0427488942226</v>
       </c>
       <c r="AA5" t="n">
         <v>180.518097691018</v>
       </c>
       <c r="AB5" t="n">
-        <v>241.5120782582231</v>
+        <v>241.5120782582233</v>
       </c>
     </row>
     <row r="6">
@@ -6342,7 +6342,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>98.39427676838011</v>
+        <v>98.39427676838001</v>
       </c>
       <c r="C6" t="n">
         <v>117.2455244275366</v>
@@ -6351,13 +6351,13 @@
         <v>117.2455244275366</v>
       </c>
       <c r="E6" t="n">
-        <v>112.8947373860409</v>
+        <v>112.8947373860408</v>
       </c>
       <c r="F6" t="n">
         <v>73.78824674877609</v>
       </c>
       <c r="G6" t="n">
-        <v>117.2455296607462</v>
+        <v>117.2455296607461</v>
       </c>
       <c r="H6" t="n">
         <v>117.2455244275366</v>
@@ -6366,7 +6366,7 @@
         <v>117.2455244275366</v>
       </c>
       <c r="J6" t="n">
-        <v>117.0875286513753</v>
+        <v>117.087528651375</v>
       </c>
       <c r="K6" t="n">
         <v>117.2455244275366</v>
@@ -6378,16 +6378,16 @@
         <v>117.2455244275366</v>
       </c>
       <c r="N6" t="n">
-        <v>182.1154705515552</v>
+        <v>117.2455244275366</v>
       </c>
       <c r="O6" t="n">
-        <v>123.4928101856967</v>
+        <v>123.4928101856964</v>
       </c>
       <c r="P6" t="n">
-        <v>124.8514865145647</v>
+        <v>124.8514865145642</v>
       </c>
       <c r="Q6" t="n">
-        <v>117.2455296607462</v>
+        <v>117.2455296607461</v>
       </c>
       <c r="R6" t="n">
         <v>117.2455244275366</v>
@@ -6402,7 +6402,7 @@
         <v>117.2455244275366</v>
       </c>
       <c r="V6" t="n">
-        <v>137.9971527147434</v>
+        <v>137.9971527147433</v>
       </c>
       <c r="W6" t="n">
         <v>117.2455244275366</v>
@@ -6414,7 +6414,7 @@
         <v>117.2455244275366</v>
       </c>
       <c r="Z6" t="n">
-        <v>105.8799004854622</v>
+        <v>105.8799004854619</v>
       </c>
       <c r="AA6" t="n">
         <v>117.2455244275366</v>
@@ -6430,55 +6430,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.74271063070026</v>
+        <v>83.74271063070023</v>
       </c>
       <c r="C7" t="n">
-        <v>85.63606909568701</v>
+        <v>85.63606909568706</v>
       </c>
       <c r="D7" t="n">
-        <v>85.04780065866842</v>
+        <v>85.04780065866839</v>
       </c>
       <c r="E7" t="n">
-        <v>32.71434257850158</v>
+        <v>32.71434257850155</v>
       </c>
       <c r="F7" t="n">
-        <v>84.85398302620172</v>
+        <v>84.85398302620167</v>
       </c>
       <c r="G7" t="n">
-        <v>84.18179049855425</v>
+        <v>84.18179049855421</v>
       </c>
       <c r="H7" t="n">
-        <v>83.78437259971011</v>
+        <v>83.78437259971008</v>
       </c>
       <c r="I7" t="n">
-        <v>83.0888980542417</v>
+        <v>83.08889805424164</v>
       </c>
       <c r="J7" t="n">
-        <v>84.03908516561241</v>
+        <v>84.03908516561235</v>
       </c>
       <c r="K7" t="n">
-        <v>84.16928577092121</v>
+        <v>84.16928577092119</v>
       </c>
       <c r="L7" t="n">
         <v>84.71444793225072</v>
       </c>
       <c r="M7" t="n">
-        <v>84.60100413492864</v>
+        <v>84.6010041349286</v>
       </c>
       <c r="N7" t="n">
-        <v>84.4274286430341</v>
+        <v>84.42742864303402</v>
       </c>
       <c r="O7" t="n">
-        <v>82.53851146249862</v>
+        <v>82.53851146249859</v>
       </c>
       <c r="P7" t="n">
-        <v>83.47881101147819</v>
+        <v>83.47881101147811</v>
       </c>
       <c r="Q7" t="n">
         <v>84.47475443580321</v>
       </c>
       <c r="R7" t="n">
-        <v>82.9229042053104</v>
+        <v>82.92290420531036</v>
       </c>
       <c r="S7" t="n">
         <v>84.14905696493865</v>
@@ -6487,28 +6487,28 @@
         <v>85.1354710801057</v>
       </c>
       <c r="U7" t="n">
-        <v>84.16934577000272</v>
+        <v>84.16934577000268</v>
       </c>
       <c r="V7" t="n">
-        <v>49.49685351724705</v>
+        <v>49.49685351724708</v>
       </c>
       <c r="W7" t="n">
-        <v>81.86928220227884</v>
+        <v>81.86928220227875</v>
       </c>
       <c r="X7" t="n">
-        <v>77.19768134710033</v>
+        <v>77.19768134710026</v>
       </c>
       <c r="Y7" t="n">
-        <v>82.23278242090741</v>
+        <v>82.23278242090738</v>
       </c>
       <c r="Z7" t="n">
-        <v>84.50699667909494</v>
+        <v>84.5069966790949</v>
       </c>
       <c r="AA7" t="n">
-        <v>82.92469230269212</v>
+        <v>82.92469230269211</v>
       </c>
       <c r="AB7" t="n">
-        <v>84.62989225182548</v>
+        <v>84.62989225182547</v>
       </c>
     </row>
     <row r="8">
@@ -6518,85 +6518,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>85.11419342317484</v>
+        <v>85.11419342317471</v>
       </c>
       <c r="C8" t="n">
-        <v>85.66018728296795</v>
+        <v>85.6601872829679</v>
       </c>
       <c r="D8" t="n">
-        <v>85.49317857244576</v>
+        <v>85.49317857244573</v>
       </c>
       <c r="E8" t="n">
-        <v>33.66036392927449</v>
+        <v>33.66036392927447</v>
       </c>
       <c r="F8" t="n">
-        <v>85.43968689200655</v>
+        <v>85.43968689200646</v>
       </c>
       <c r="G8" t="n">
-        <v>85.24041366971711</v>
+        <v>85.24041366971706</v>
       </c>
       <c r="H8" t="n">
-        <v>85.13747853259314</v>
+        <v>85.13747853259311</v>
       </c>
       <c r="I8" t="n">
-        <v>84.93747594421487</v>
+        <v>84.93747594421481</v>
       </c>
       <c r="J8" t="n">
-        <v>85.17998686122287</v>
+        <v>85.17998686122283</v>
       </c>
       <c r="K8" t="n">
-        <v>85.2428026180673</v>
+        <v>85.24280261806729</v>
       </c>
       <c r="L8" t="n">
-        <v>85.39518262005271</v>
+        <v>85.39518262005264</v>
       </c>
       <c r="M8" t="n">
-        <v>85.36757053019922</v>
+        <v>85.36757053019912</v>
       </c>
       <c r="N8" t="n">
-        <v>85.31513095498384</v>
+        <v>85.31513095498374</v>
       </c>
       <c r="O8" t="n">
-        <v>84.76791618592976</v>
+        <v>84.76791618592981</v>
       </c>
       <c r="P8" t="n">
-        <v>85.03738003102882</v>
+        <v>85.03738003102876</v>
       </c>
       <c r="Q8" t="n">
-        <v>85.32926965560205</v>
+        <v>85.32926965560202</v>
       </c>
       <c r="R8" t="n">
-        <v>84.8917133577858</v>
+        <v>84.89171335778578</v>
       </c>
       <c r="S8" t="n">
-        <v>85.23214552443656</v>
+        <v>85.2321455244365</v>
       </c>
       <c r="T8" t="n">
-        <v>85.51827683064529</v>
+        <v>85.51827683064526</v>
       </c>
       <c r="U8" t="n">
-        <v>85.23893290368872</v>
+        <v>85.23893290368866</v>
       </c>
       <c r="V8" t="n">
-        <v>51.46485115579263</v>
+        <v>51.46485115579267</v>
       </c>
       <c r="W8" t="n">
-        <v>84.58327444576531</v>
+        <v>84.58327444576526</v>
       </c>
       <c r="X8" t="n">
-        <v>83.25995893344749</v>
+        <v>83.25995893344742</v>
       </c>
       <c r="Y8" t="n">
-        <v>84.6883149643449</v>
+        <v>84.68831496434483</v>
       </c>
       <c r="Z8" t="n">
-        <v>85.3338998800614</v>
+        <v>85.33389988006135</v>
       </c>
       <c r="AA8" t="n">
-        <v>84.88519910430067</v>
+        <v>84.88519910430051</v>
       </c>
       <c r="AB8" t="n">
-        <v>85.37447403233139</v>
+        <v>85.37447403233134</v>
       </c>
     </row>
   </sheetData>
@@ -6762,85 +6762,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>89.21995997673545</v>
+        <v>89.21995997673551</v>
       </c>
       <c r="C2" t="n">
-        <v>88.55651430305669</v>
+        <v>88.55651430305694</v>
       </c>
       <c r="D2" t="n">
-        <v>89.09146803142634</v>
+        <v>89.09146803142647</v>
       </c>
       <c r="E2" t="n">
-        <v>35.73799848242281</v>
+        <v>35.73799848242293</v>
       </c>
       <c r="F2" t="n">
-        <v>89.01663271919986</v>
+        <v>89.01663271919965</v>
       </c>
       <c r="G2" t="n">
-        <v>92.88068752234898</v>
+        <v>92.88068752234901</v>
       </c>
       <c r="H2" t="n">
-        <v>88.67911282218431</v>
+        <v>88.67911282218435</v>
       </c>
       <c r="I2" t="n">
-        <v>88.97277082676133</v>
+        <v>88.97277082676149</v>
       </c>
       <c r="J2" t="n">
-        <v>90.79650674108673</v>
+        <v>90.79650674108666</v>
       </c>
       <c r="K2" t="n">
-        <v>89.24042615892485</v>
+        <v>89.24042615892502</v>
       </c>
       <c r="L2" t="n">
-        <v>89.0966874470203</v>
+        <v>89.09668744702063</v>
       </c>
       <c r="M2" t="n">
-        <v>94.7468443037052</v>
+        <v>94.74684430370529</v>
       </c>
       <c r="N2" t="n">
-        <v>89.23778479763884</v>
+        <v>89.23778479763891</v>
       </c>
       <c r="O2" t="n">
-        <v>89.28825232118487</v>
+        <v>89.28825232118513</v>
       </c>
       <c r="P2" t="n">
-        <v>90.29602847878516</v>
+        <v>90.2960284787854</v>
       </c>
       <c r="Q2" t="n">
-        <v>89.20897619828936</v>
+        <v>89.20897619829009</v>
       </c>
       <c r="R2" t="n">
-        <v>88.78639278851918</v>
+        <v>88.78639278851956</v>
       </c>
       <c r="S2" t="n">
-        <v>89.59089742608023</v>
+        <v>89.59089742608003</v>
       </c>
       <c r="T2" t="n">
-        <v>88.86935907980342</v>
+        <v>88.86935907980343</v>
       </c>
       <c r="U2" t="n">
-        <v>89.72665751182254</v>
+        <v>89.72665751182262</v>
       </c>
       <c r="V2" t="n">
-        <v>54.75195621333012</v>
+        <v>54.75195621333077</v>
       </c>
       <c r="W2" t="n">
-        <v>89.73829207039948</v>
+        <v>89.73829207039986</v>
       </c>
       <c r="X2" t="n">
-        <v>89.61131683497022</v>
+        <v>89.61131683497004</v>
       </c>
       <c r="Y2" t="n">
-        <v>89.93963120119564</v>
+        <v>89.93963120119602</v>
       </c>
       <c r="Z2" t="n">
-        <v>89.61012918709953</v>
+        <v>89.6101291870996</v>
       </c>
       <c r="AA2" t="n">
-        <v>89.27988083410452</v>
+        <v>89.27988083410483</v>
       </c>
       <c r="AB2" t="n">
-        <v>94.25623288178322</v>
+        <v>94.2562328817833</v>
       </c>
     </row>
     <row r="3">
@@ -6850,85 +6850,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>89.04688383461907</v>
+        <v>89.04688383461945</v>
       </c>
       <c r="C3" t="n">
-        <v>89.04688015039365</v>
+        <v>89.04688015039403</v>
       </c>
       <c r="D3" t="n">
-        <v>89.04688383461907</v>
+        <v>89.04688383461945</v>
       </c>
       <c r="E3" t="n">
-        <v>35.28157332693986</v>
+        <v>35.28157332693988</v>
       </c>
       <c r="F3" t="n">
-        <v>89.046882460435</v>
+        <v>89.0468824604354</v>
       </c>
       <c r="G3" t="n">
-        <v>89.04688341213983</v>
+        <v>89.04688341214023</v>
       </c>
       <c r="H3" t="n">
-        <v>89.04688383461907</v>
+        <v>89.04688383461945</v>
       </c>
       <c r="I3" t="n">
-        <v>89.04688383461907</v>
+        <v>89.04688383461945</v>
       </c>
       <c r="J3" t="n">
-        <v>88.90177749651862</v>
+        <v>88.90177749651886</v>
       </c>
       <c r="K3" t="n">
-        <v>89.04688302637724</v>
+        <v>89.04688302637763</v>
       </c>
       <c r="L3" t="n">
-        <v>89.04688383461907</v>
+        <v>89.04688383461945</v>
       </c>
       <c r="M3" t="n">
-        <v>89.04688288304335</v>
+        <v>89.04688288304374</v>
       </c>
       <c r="N3" t="n">
-        <v>89.04688383461907</v>
+        <v>89.04688383461945</v>
       </c>
       <c r="O3" t="n">
-        <v>89.04688118180727</v>
+        <v>89.04688118180765</v>
       </c>
       <c r="P3" t="n">
-        <v>89.04688317060682</v>
+        <v>89.0468831706072</v>
       </c>
       <c r="Q3" t="n">
-        <v>89.04688379697535</v>
+        <v>89.04688379697575</v>
       </c>
       <c r="R3" t="n">
-        <v>89.04688368520392</v>
+        <v>89.04688368520431</v>
       </c>
       <c r="S3" t="n">
-        <v>89.04688383461907</v>
+        <v>89.04688383461945</v>
       </c>
       <c r="T3" t="n">
-        <v>89.04688268069879</v>
+        <v>89.04688268069917</v>
       </c>
       <c r="U3" t="n">
-        <v>89.04688644006158</v>
+        <v>89.04688644006197</v>
       </c>
       <c r="V3" t="n">
-        <v>54.29254301849706</v>
+        <v>54.2925430184974</v>
       </c>
       <c r="W3" t="n">
-        <v>89.04688383461907</v>
+        <v>89.04688383461945</v>
       </c>
       <c r="X3" t="n">
-        <v>89.04688599871979</v>
+        <v>89.04688599872017</v>
       </c>
       <c r="Y3" t="n">
-        <v>89.04687774352458</v>
+        <v>89.04687774352496</v>
       </c>
       <c r="Z3" t="n">
-        <v>89.04688362906754</v>
+        <v>89.04688362906792</v>
       </c>
       <c r="AA3" t="n">
-        <v>89.04688383461907</v>
+        <v>89.04688383461945</v>
       </c>
       <c r="AB3" t="n">
-        <v>89.04692307056327</v>
+        <v>89.04692307056365</v>
       </c>
     </row>
     <row r="4">
@@ -6938,82 +6938,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>320.6416778377858</v>
+        <v>320.6416778377882</v>
       </c>
       <c r="C4" t="n">
-        <v>165.6166846291639</v>
+        <v>165.616684629165</v>
       </c>
       <c r="D4" t="n">
-        <v>313.8705289760331</v>
+        <v>313.8705289760342</v>
       </c>
       <c r="E4" t="n">
-        <v>149.619162261451</v>
+        <v>149.6191622614515</v>
       </c>
       <c r="F4" t="n">
         <v>295.4394920487362</v>
       </c>
       <c r="G4" t="n">
-        <v>1217.005323331714</v>
+        <v>1217.005323331717</v>
       </c>
       <c r="H4" t="n">
-        <v>204.3224882636347</v>
+        <v>204.3224882636357</v>
       </c>
       <c r="I4" t="n">
-        <v>282.5236419394386</v>
+        <v>282.5236419394392</v>
       </c>
       <c r="J4" t="n">
-        <v>759.9813729131051</v>
+        <v>759.981372913107</v>
       </c>
       <c r="K4" t="n">
-        <v>345.552837617169</v>
+        <v>345.5528376171695</v>
       </c>
       <c r="L4" t="n">
-        <v>300.7116124815398</v>
+        <v>300.711612481549</v>
       </c>
       <c r="M4" t="n">
-        <v>1792.234360159418</v>
+        <v>1792.234360159421</v>
       </c>
       <c r="N4" t="n">
-        <v>347.5899552816244</v>
+        <v>347.5899552816241</v>
       </c>
       <c r="O4" t="n">
-        <v>335.2423426324771</v>
+        <v>335.2423426324772</v>
       </c>
       <c r="P4" t="n">
-        <v>597.1897676269247</v>
+        <v>597.1897676269242</v>
       </c>
       <c r="Q4" t="n">
-        <v>337.5366077097649</v>
+        <v>337.5366077097656</v>
       </c>
       <c r="R4" t="n">
-        <v>231.0977611640295</v>
+        <v>231.09776116403</v>
       </c>
       <c r="S4" t="n">
-        <v>407.3212275558773</v>
+        <v>407.3212275558806</v>
       </c>
       <c r="T4" t="n">
-        <v>251.5730836151045</v>
+        <v>251.5730836151055</v>
       </c>
       <c r="U4" t="n">
-        <v>464.7287542818247</v>
+        <v>464.7287542818265</v>
       </c>
       <c r="V4" t="n">
-        <v>261.9395273022214</v>
+        <v>261.939527302223</v>
       </c>
       <c r="W4" t="n">
-        <v>478.7839284539548</v>
+        <v>478.7839284539559</v>
       </c>
       <c r="X4" t="n">
-        <v>456.0427496522412</v>
+        <v>456.0427496522473</v>
       </c>
       <c r="Y4" t="n">
-        <v>531.1085119617609</v>
+        <v>531.1085119617613</v>
       </c>
       <c r="Z4" t="n">
-        <v>419.3941490049081</v>
+        <v>419.3941490049082</v>
       </c>
       <c r="AA4" t="n">
-        <v>354.7536439888464</v>
+        <v>354.7536439888465</v>
       </c>
       <c r="AB4" t="n">
         <v>1863.003546186635</v>
@@ -7026,85 +7026,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>135.641464637053</v>
+        <v>135.6414646370536</v>
       </c>
       <c r="C5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405625</v>
       </c>
       <c r="D5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405625</v>
       </c>
       <c r="E5" t="n">
-        <v>166.7578942212675</v>
+        <v>166.7578942212687</v>
       </c>
       <c r="F5" t="n">
-        <v>146.0099570708534</v>
+        <v>146.0099570708535</v>
       </c>
       <c r="G5" t="n">
-        <v>215.9970873574457</v>
+        <v>215.9970873574465</v>
       </c>
       <c r="H5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405624</v>
       </c>
       <c r="I5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405625</v>
       </c>
       <c r="J5" t="n">
-        <v>202.0145020052848</v>
+        <v>202.0145020052857</v>
       </c>
       <c r="K5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405625</v>
       </c>
       <c r="L5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405625</v>
       </c>
       <c r="M5" t="n">
-        <v>202.1964728405681</v>
+        <v>202.1964728405685</v>
       </c>
       <c r="N5" t="n">
-        <v>347.5899552816244</v>
+        <v>150.6052070736226</v>
       </c>
       <c r="O5" t="n">
-        <v>164.7829348681192</v>
+        <v>164.7829348681195</v>
       </c>
       <c r="P5" t="n">
-        <v>161.3076312035066</v>
+        <v>161.3076312035069</v>
       </c>
       <c r="Q5" t="n">
-        <v>122.5618864800342</v>
+        <v>122.561886480034</v>
       </c>
       <c r="R5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405624</v>
       </c>
       <c r="S5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405622</v>
       </c>
       <c r="T5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405625</v>
       </c>
       <c r="U5" t="n">
-        <v>169.6953848477754</v>
+        <v>169.695384847776</v>
       </c>
       <c r="V5" t="n">
-        <v>182.832322874526</v>
+        <v>182.8323228745263</v>
       </c>
       <c r="W5" t="n">
-        <v>202.2095528109662</v>
+        <v>202.2095528109664</v>
       </c>
       <c r="X5" t="n">
-        <v>128.6617852313116</v>
+        <v>128.661785231311</v>
       </c>
       <c r="Y5" t="n">
-        <v>268.3424156130645</v>
+        <v>268.3424156130654</v>
       </c>
       <c r="Z5" t="n">
-        <v>134.4051711899312</v>
+        <v>134.405171189931</v>
       </c>
       <c r="AA5" t="n">
-        <v>202.196472840562</v>
+        <v>202.1964728405624</v>
       </c>
       <c r="AB5" t="n">
-        <v>271.7187441523547</v>
+        <v>271.7187441523526</v>
       </c>
     </row>
     <row r="6">
@@ -7114,85 +7114,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>128.8348110042012</v>
+        <v>128.8348110042008</v>
       </c>
       <c r="C6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="D6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="E6" t="n">
-        <v>149.6693876564818</v>
+        <v>149.66938765648</v>
       </c>
       <c r="F6" t="n">
-        <v>93.48033282112786</v>
+        <v>93.48033282112792</v>
       </c>
       <c r="G6" t="n">
-        <v>155.9207004620241</v>
+        <v>155.9207004620245</v>
       </c>
       <c r="H6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="I6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="J6" t="n">
-        <v>155.7387356210404</v>
+        <v>155.7387356210394</v>
       </c>
       <c r="K6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="L6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="M6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="N6" t="n">
-        <v>347.5899552816244</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="O6" t="n">
-        <v>164.8969287624325</v>
+        <v>164.8969287624329</v>
       </c>
       <c r="P6" t="n">
-        <v>166.8491044116022</v>
+        <v>166.8491044116033</v>
       </c>
       <c r="Q6" t="n">
-        <v>155.9207004620241</v>
+        <v>155.9207004620245</v>
       </c>
       <c r="R6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="S6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="T6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="U6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="V6" t="n">
-        <v>186.0217257838767</v>
+        <v>186.0217257838773</v>
       </c>
       <c r="W6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="X6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="Y6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="Z6" t="n">
-        <v>139.5903176902236</v>
+        <v>139.5903176902232</v>
       </c>
       <c r="AA6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
       <c r="AB6" t="n">
-        <v>155.9207064563174</v>
+        <v>155.9207064563178</v>
       </c>
     </row>
     <row r="7">
@@ -7202,85 +7202,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.6019474434998</v>
+        <v>83.60194744349975</v>
       </c>
       <c r="C7" t="n">
-        <v>87.5716429657336</v>
+        <v>87.57164296573353</v>
       </c>
       <c r="D7" t="n">
-        <v>84.43997122562075</v>
+        <v>84.43997122562094</v>
       </c>
       <c r="E7" t="n">
-        <v>32.93662572400716</v>
+        <v>32.93662572400741</v>
       </c>
       <c r="F7" t="n">
-        <v>84.89914224335817</v>
+        <v>84.89914224335814</v>
       </c>
       <c r="G7" t="n">
-        <v>61.83883653649423</v>
+        <v>61.8388365364943</v>
       </c>
       <c r="H7" t="n">
-        <v>86.8708280967043</v>
+        <v>86.87082809670474</v>
       </c>
       <c r="I7" t="n">
-        <v>85.14274868563636</v>
+        <v>85.14274868563638</v>
       </c>
       <c r="J7" t="n">
-        <v>73.29818157724532</v>
+        <v>73.29818157724544</v>
       </c>
       <c r="K7" t="n">
-        <v>83.55953876878941</v>
+        <v>83.55953876878969</v>
       </c>
       <c r="L7" t="n">
-        <v>84.36549573416428</v>
+        <v>84.3654957341643</v>
       </c>
       <c r="M7" t="n">
-        <v>51.45698591116984</v>
+        <v>51.45698591116988</v>
       </c>
       <c r="N7" t="n">
-        <v>83.55939198452175</v>
+        <v>83.55939198452229</v>
       </c>
       <c r="O7" t="n">
-        <v>83.18916436327989</v>
+        <v>83.18916436327982</v>
       </c>
       <c r="P7" t="n">
         <v>77.1765973967352</v>
       </c>
       <c r="Q7" t="n">
-        <v>83.7378691841329</v>
+        <v>83.73786918413299</v>
       </c>
       <c r="R7" t="n">
-        <v>86.23845746336278</v>
+        <v>86.23845746336272</v>
       </c>
       <c r="S7" t="n">
-        <v>81.41910164372032</v>
+        <v>81.41910164372069</v>
       </c>
       <c r="T7" t="n">
-        <v>85.74313780675116</v>
+        <v>85.74313780675141</v>
       </c>
       <c r="U7" t="n">
-        <v>80.63274402344324</v>
+        <v>80.63274402344335</v>
       </c>
       <c r="V7" t="n">
-        <v>50.34338373438885</v>
+        <v>50.34338373438912</v>
       </c>
       <c r="W7" t="n">
-        <v>80.58672954743176</v>
+        <v>80.58672954743207</v>
       </c>
       <c r="X7" t="n">
-        <v>81.38748768723543</v>
+        <v>81.38748768723546</v>
       </c>
       <c r="Y7" t="n">
-        <v>79.41413051303978</v>
+        <v>79.41413051304038</v>
       </c>
       <c r="Z7" t="n">
-        <v>81.28947806035281</v>
+        <v>81.28947806035276</v>
       </c>
       <c r="AA7" t="n">
-        <v>83.29703223034439</v>
+        <v>83.29703223034502</v>
       </c>
       <c r="AB7" t="n">
-        <v>54.19538590907597</v>
+        <v>54.19538590907629</v>
       </c>
     </row>
     <row r="8">
@@ -7290,82 +7290,82 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86.74249656679346</v>
+        <v>86.74249656679319</v>
       </c>
       <c r="C8" t="n">
-        <v>87.88527668273444</v>
+        <v>87.88527668273461</v>
       </c>
       <c r="D8" t="n">
-        <v>86.99530811297274</v>
+        <v>86.99530811297291</v>
       </c>
       <c r="E8" t="n">
-        <v>34.6710398501838</v>
+        <v>34.6710398501839</v>
       </c>
       <c r="F8" t="n">
-        <v>87.12939770236619</v>
+        <v>87.12939770236638</v>
       </c>
       <c r="G8" t="n">
-        <v>80.5009394870295</v>
+        <v>80.50093948702937</v>
       </c>
       <c r="H8" t="n">
-        <v>87.68900052675497</v>
+        <v>87.68900052675534</v>
       </c>
       <c r="I8" t="n">
-        <v>87.19637689223377</v>
+        <v>87.1963768922339</v>
       </c>
       <c r="J8" t="n">
-        <v>83.69682087210765</v>
+        <v>83.69682087210793</v>
       </c>
       <c r="K8" t="n">
-        <v>86.74366703459376</v>
+        <v>86.74366703459367</v>
       </c>
       <c r="L8" t="n">
-        <v>86.96664094261466</v>
+        <v>86.96664094261462</v>
       </c>
       <c r="M8" t="n">
-        <v>77.64332138960884</v>
+        <v>77.64332138960891</v>
       </c>
       <c r="N8" t="n">
-        <v>86.74095851824568</v>
+        <v>86.74095851824605</v>
       </c>
       <c r="O8" t="n">
-        <v>86.62297250131898</v>
+        <v>86.62297250131954</v>
       </c>
       <c r="P8" t="n">
-        <v>84.8950106233173</v>
+        <v>84.89501062331767</v>
       </c>
       <c r="Q8" t="n">
-        <v>86.79335763062042</v>
+        <v>86.79335763062087</v>
       </c>
       <c r="R8" t="n">
-        <v>87.50854990765816</v>
+        <v>87.50854990765822</v>
       </c>
       <c r="S8" t="n">
-        <v>86.12023222092181</v>
+        <v>86.12023222092176</v>
       </c>
       <c r="T8" t="n">
-        <v>87.36614463374701</v>
+        <v>87.36614463374754</v>
       </c>
       <c r="U8" t="n">
-        <v>85.89819589798032</v>
+        <v>85.89819589798054</v>
       </c>
       <c r="V8" t="n">
-        <v>52.95507615383703</v>
+        <v>52.95507615383711</v>
       </c>
       <c r="W8" t="n">
-        <v>85.88889490881726</v>
+        <v>85.88889490881706</v>
       </c>
       <c r="X8" t="n">
-        <v>86.12626619419076</v>
+        <v>86.12626619419105</v>
       </c>
       <c r="Y8" t="n">
-        <v>85.55670051358106</v>
+        <v>85.55670051358089</v>
       </c>
       <c r="Z8" t="n">
-        <v>86.08048493194964</v>
+        <v>86.08048493194994</v>
       </c>
       <c r="AA8" t="n">
-        <v>86.66368003046981</v>
+        <v>86.66368003046995</v>
       </c>
       <c r="AB8" t="n">
         <v>78.39867240804757</v>
@@ -7537,37 +7537,37 @@
         <v>87.9592109696348</v>
       </c>
       <c r="C2" t="n">
-        <v>87.54250799475668</v>
+        <v>87.54250799475665</v>
       </c>
       <c r="D2" t="n">
-        <v>87.59001505531472</v>
+        <v>87.59001505531474</v>
       </c>
       <c r="E2" t="n">
         <v>35.02086443179836</v>
       </c>
       <c r="F2" t="n">
-        <v>87.52184681864267</v>
+        <v>87.52184681864273</v>
       </c>
       <c r="G2" t="n">
-        <v>90.87877820396744</v>
+        <v>90.87877820396743</v>
       </c>
       <c r="H2" t="n">
         <v>87.67154133099085</v>
       </c>
       <c r="I2" t="n">
-        <v>87.70582309778061</v>
+        <v>87.70582309778065</v>
       </c>
       <c r="J2" t="n">
-        <v>88.67396897829818</v>
+        <v>88.67396897829821</v>
       </c>
       <c r="K2" t="n">
-        <v>87.8605721115224</v>
+        <v>87.86057211152243</v>
       </c>
       <c r="L2" t="n">
-        <v>87.78883291946947</v>
+        <v>87.78883291946948</v>
       </c>
       <c r="M2" t="n">
-        <v>88.18096391701312</v>
+        <v>88.18096391701309</v>
       </c>
       <c r="N2" t="n">
         <v>87.84973524492942</v>
@@ -7576,31 +7576,31 @@
         <v>87.86772961398972</v>
       </c>
       <c r="P2" t="n">
-        <v>88.44861398357915</v>
+        <v>88.44861398357918</v>
       </c>
       <c r="Q2" t="n">
-        <v>87.99204203992596</v>
+        <v>87.99204203992599</v>
       </c>
       <c r="R2" t="n">
         <v>87.68263810666329</v>
       </c>
       <c r="S2" t="n">
-        <v>87.79198555490534</v>
+        <v>87.79198555490532</v>
       </c>
       <c r="T2" t="n">
-        <v>87.5425037848411</v>
+        <v>87.542503784841</v>
       </c>
       <c r="U2" t="n">
-        <v>87.85561093406341</v>
+        <v>87.85561093406339</v>
       </c>
       <c r="V2" t="n">
-        <v>53.83093625443293</v>
+        <v>53.83093625443291</v>
       </c>
       <c r="W2" t="n">
-        <v>88.32753224871387</v>
+        <v>88.32753224871391</v>
       </c>
       <c r="X2" t="n">
-        <v>88.58831748352149</v>
+        <v>88.58831748352151</v>
       </c>
       <c r="Y2" t="n">
         <v>89.7257504118737</v>
@@ -7609,7 +7609,7 @@
         <v>87.83926346175907</v>
       </c>
       <c r="AA2" t="n">
-        <v>87.76164093604081</v>
+        <v>87.76164093604082</v>
       </c>
       <c r="AB2" t="n">
         <v>90.89388730672192</v>
@@ -7631,7 +7631,7 @@
         <v>88.00044124457368</v>
       </c>
       <c r="E3" t="n">
-        <v>34.71028931074919</v>
+        <v>34.71028931074918</v>
       </c>
       <c r="F3" t="n">
         <v>88.00043930504874</v>
@@ -7646,7 +7646,7 @@
         <v>88.00044124457368</v>
       </c>
       <c r="J3" t="n">
-        <v>87.88563974351555</v>
+        <v>87.88563974351553</v>
       </c>
       <c r="K3" t="n">
         <v>88.00044009813979</v>
@@ -7670,7 +7670,7 @@
         <v>88.00044120692996</v>
       </c>
       <c r="R3" t="n">
-        <v>88.00044553871641</v>
+        <v>88.00044553871639</v>
       </c>
       <c r="S3" t="n">
         <v>88.00044124457368</v>
@@ -7682,7 +7682,7 @@
         <v>88.00044531785358</v>
       </c>
       <c r="V3" t="n">
-        <v>53.50491109438575</v>
+        <v>53.50491109438572</v>
       </c>
       <c r="W3" t="n">
         <v>88.00044124457368</v>
@@ -7694,7 +7694,7 @@
         <v>88.00043392331996</v>
       </c>
       <c r="Z3" t="n">
-        <v>88.00044089894756</v>
+        <v>88.00044089894755</v>
       </c>
       <c r="AA3" t="n">
         <v>88.00044124457368</v>
@@ -7713,28 +7713,28 @@
         <v>248.4022405390421</v>
       </c>
       <c r="C4" t="n">
-        <v>164.0017965665833</v>
+        <v>164.0017965665834</v>
       </c>
       <c r="D4" t="n">
-        <v>173.4202698685172</v>
+        <v>173.4202698685174</v>
       </c>
       <c r="E4" t="n">
-        <v>103.5691975744251</v>
+        <v>103.5691975744253</v>
       </c>
       <c r="F4" t="n">
         <v>157.5048494043087</v>
       </c>
       <c r="G4" t="n">
-        <v>884.656295913255</v>
+        <v>884.6562959132507</v>
       </c>
       <c r="H4" t="n">
-        <v>198.9276126518448</v>
+        <v>198.9276126518449</v>
       </c>
       <c r="I4" t="n">
-        <v>203.2527723061324</v>
+        <v>203.2527723061325</v>
       </c>
       <c r="J4" t="n">
-        <v>435.8768391935014</v>
+        <v>435.8768391935025</v>
       </c>
       <c r="K4" t="n">
         <v>241.6563785003641</v>
@@ -7743,49 +7743,49 @@
         <v>217.1231843857592</v>
       </c>
       <c r="M4" t="n">
-        <v>323.0883178196642</v>
+        <v>323.088317819664</v>
       </c>
       <c r="N4" t="n">
-        <v>234.7467019374949</v>
+        <v>234.7467019374953</v>
       </c>
       <c r="O4" t="n">
-        <v>226.8694538478956</v>
+        <v>226.8694538478972</v>
       </c>
       <c r="P4" t="n">
-        <v>360.3418518146265</v>
+        <v>360.341851814626</v>
       </c>
       <c r="Q4" t="n">
         <v>263.3325543575519</v>
       </c>
       <c r="R4" t="n">
-        <v>198.6502936055652</v>
+        <v>198.6502936055655</v>
       </c>
       <c r="S4" t="n">
-        <v>210.1229573903275</v>
+        <v>210.1229573903274</v>
       </c>
       <c r="T4" t="n">
-        <v>160.1150222456571</v>
+        <v>160.1150222456563</v>
       </c>
       <c r="U4" t="n">
-        <v>230.8438998114011</v>
+        <v>230.8438998114009</v>
       </c>
       <c r="V4" t="n">
-        <v>213.1425290861636</v>
+        <v>213.1425290861634</v>
       </c>
       <c r="W4" t="n">
         <v>352.5924621977071</v>
       </c>
       <c r="X4" t="n">
-        <v>421.4757776228872</v>
+        <v>421.4757776228861</v>
       </c>
       <c r="Y4" t="n">
-        <v>702.1920135203302</v>
+        <v>702.192013520328</v>
       </c>
       <c r="Z4" t="n">
-        <v>219.1088193864924</v>
+        <v>219.1088193864925</v>
       </c>
       <c r="AA4" t="n">
-        <v>209.9430219260852</v>
+        <v>209.9430219260848</v>
       </c>
       <c r="AB4" t="n">
         <v>1070.723577089366</v>
@@ -7798,85 +7798,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>125.6489891756024</v>
+        <v>125.6489891756025</v>
       </c>
       <c r="C5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="D5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="E5" t="n">
-        <v>153.8933842123363</v>
+        <v>153.8933842123364</v>
       </c>
       <c r="F5" t="n">
-        <v>135.0604737241645</v>
+        <v>135.0604737241647</v>
       </c>
       <c r="G5" t="n">
-        <v>198.5878186580926</v>
+        <v>198.5878186580929</v>
       </c>
       <c r="H5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="I5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="J5" t="n">
-        <v>185.8856184010803</v>
+        <v>185.8856184010804</v>
       </c>
       <c r="K5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="L5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="M5" t="n">
-        <v>186.0609955818097</v>
+        <v>186.0609955818098</v>
       </c>
       <c r="N5" t="n">
-        <v>234.7467019374949</v>
+        <v>139.2315839096073</v>
       </c>
       <c r="O5" t="n">
-        <v>152.1007128524288</v>
+        <v>152.1007128524291</v>
       </c>
       <c r="P5" t="n">
-        <v>148.9461783865372</v>
+        <v>148.9461783865375</v>
       </c>
       <c r="Q5" t="n">
         <v>113.7766510788846</v>
       </c>
       <c r="R5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="S5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="T5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="U5" t="n">
         <v>156.5606868370463</v>
       </c>
       <c r="V5" t="n">
-        <v>168.4206271425988</v>
+        <v>168.420627142599</v>
       </c>
       <c r="W5" t="n">
-        <v>186.0728682764378</v>
+        <v>186.072868276438</v>
       </c>
       <c r="X5" t="n">
-        <v>119.3135315091708</v>
+        <v>119.313531509171</v>
       </c>
       <c r="Y5" t="n">
-        <v>246.103303360143</v>
+        <v>246.1033033601434</v>
       </c>
       <c r="Z5" t="n">
-        <v>124.5268051406672</v>
+        <v>124.5268051406673</v>
       </c>
       <c r="AA5" t="n">
-        <v>186.0609955818092</v>
+        <v>186.0609955818093</v>
       </c>
       <c r="AB5" t="n">
-        <v>249.1663878469764</v>
+        <v>249.1663878469771</v>
       </c>
     </row>
     <row r="6">
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111.6466491272581</v>
+        <v>111.6466491272582</v>
       </c>
       <c r="C6" t="n">
         <v>134.068762554934</v>
@@ -7895,13 +7895,13 @@
         <v>134.068762554934</v>
       </c>
       <c r="E6" t="n">
-        <v>128.8938371851296</v>
+        <v>128.8938371851297</v>
       </c>
       <c r="F6" t="n">
-        <v>82.37965973322591</v>
+        <v>82.37965973322594</v>
       </c>
       <c r="G6" t="n">
-        <v>134.0687715917757</v>
+        <v>134.0687715917759</v>
       </c>
       <c r="H6" t="n">
         <v>134.068762554934</v>
@@ -7916,22 +7916,22 @@
         <v>134.068762554934</v>
       </c>
       <c r="L6" t="n">
-        <v>134.068762554934</v>
+        <v>134.0687625549341</v>
       </c>
       <c r="M6" t="n">
         <v>134.068762554934</v>
       </c>
       <c r="N6" t="n">
-        <v>234.7467019374949</v>
+        <v>134.068762554934</v>
       </c>
       <c r="O6" t="n">
-        <v>141.4994336172823</v>
+        <v>141.4994336172824</v>
       </c>
       <c r="P6" t="n">
-        <v>143.1154751191143</v>
+        <v>143.1154751191145</v>
       </c>
       <c r="Q6" t="n">
-        <v>134.0687715917757</v>
+        <v>134.0687715917759</v>
       </c>
       <c r="R6" t="n">
         <v>134.068762554934</v>
@@ -7946,7 +7946,7 @@
         <v>134.068762554934</v>
       </c>
       <c r="V6" t="n">
-        <v>158.8300079312861</v>
+        <v>158.8300079312859</v>
       </c>
       <c r="W6" t="n">
         <v>134.068762554934</v>
@@ -7958,7 +7958,7 @@
         <v>134.068762554934</v>
       </c>
       <c r="Z6" t="n">
-        <v>120.5502255985961</v>
+        <v>120.550225598596</v>
       </c>
       <c r="AA6" t="n">
         <v>134.068762554934</v>
@@ -7974,85 +7974,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.89226320933146</v>
+        <v>83.89226320933152</v>
       </c>
       <c r="C7" t="n">
-        <v>86.39590381943614</v>
+        <v>86.3959038194361</v>
       </c>
       <c r="D7" t="n">
-        <v>86.11961655246299</v>
+        <v>86.119616552463</v>
       </c>
       <c r="E7" t="n">
-        <v>33.24633690613074</v>
+        <v>33.24633690613075</v>
       </c>
       <c r="F7" t="n">
-        <v>86.52661621323453</v>
+        <v>86.5266162132345</v>
       </c>
       <c r="G7" t="n">
-        <v>66.53524646702044</v>
+        <v>66.53524646702039</v>
       </c>
       <c r="H7" t="n">
-        <v>85.65866756839387</v>
+        <v>85.65866756839385</v>
       </c>
       <c r="I7" t="n">
-        <v>85.44623923381634</v>
+        <v>85.4462392338163</v>
       </c>
       <c r="J7" t="n">
-        <v>78.86903087087074</v>
+        <v>78.86903087087079</v>
       </c>
       <c r="K7" t="n">
         <v>84.52976835403121</v>
       </c>
       <c r="L7" t="n">
-        <v>84.9258988384198</v>
+        <v>84.92589883841978</v>
       </c>
       <c r="M7" t="n">
-        <v>82.67873949474954</v>
+        <v>82.67873949474959</v>
       </c>
       <c r="N7" t="n">
-        <v>84.58349880669786</v>
+        <v>84.58349880669788</v>
       </c>
       <c r="O7" t="n">
-        <v>84.43249092423692</v>
+        <v>84.43249092423697</v>
       </c>
       <c r="P7" t="n">
-        <v>80.96664005454942</v>
+        <v>80.96664005454943</v>
       </c>
       <c r="Q7" t="n">
-        <v>83.75364740729869</v>
+        <v>83.75364740729874</v>
       </c>
       <c r="R7" t="n">
-        <v>85.58703553516278</v>
+        <v>85.58703553516284</v>
       </c>
       <c r="S7" t="n">
-        <v>84.89702758304861</v>
+        <v>84.89702758304864</v>
       </c>
       <c r="T7" t="n">
-        <v>86.39897553943239</v>
+        <v>86.39897553943236</v>
       </c>
       <c r="U7" t="n">
-        <v>84.52758604532885</v>
+        <v>84.52758604532886</v>
       </c>
       <c r="V7" t="n">
-        <v>50.39434310622831</v>
+        <v>50.3943431062283</v>
       </c>
       <c r="W7" t="n">
-        <v>81.75179506259538</v>
+        <v>81.75179506259529</v>
       </c>
       <c r="X7" t="n">
-        <v>80.26465342676421</v>
+        <v>80.26465342676417</v>
       </c>
       <c r="Y7" t="n">
-        <v>73.52307277934173</v>
+        <v>73.52307277934175</v>
       </c>
       <c r="Z7" t="n">
-        <v>84.60972243364365</v>
+        <v>84.60972243364364</v>
       </c>
       <c r="AA7" t="n">
-        <v>85.0941290395952</v>
+        <v>85.09412903959526</v>
       </c>
       <c r="AB7" t="n">
-        <v>66.77215389190815</v>
+        <v>66.7721538919081</v>
       </c>
     </row>
     <row r="8">
@@ -8062,10 +8062,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86.08997687161306</v>
+        <v>86.08997687161302</v>
       </c>
       <c r="C8" t="n">
-        <v>86.8124401134626</v>
+        <v>86.81244011346263</v>
       </c>
       <c r="D8" t="n">
         <v>86.73423382657175</v>
@@ -8074,70 +8074,70 @@
         <v>34.35476142235748</v>
       </c>
       <c r="F8" t="n">
-        <v>86.85125261507169</v>
+        <v>86.8512526150717</v>
       </c>
       <c r="G8" t="n">
-        <v>81.11204653579954</v>
+        <v>81.11204653579955</v>
       </c>
       <c r="H8" t="n">
         <v>86.60602684553928</v>
       </c>
       <c r="I8" t="n">
-        <v>86.54365304312721</v>
+        <v>86.54365304312725</v>
       </c>
       <c r="J8" t="n">
         <v>84.57138320701719</v>
       </c>
       <c r="K8" t="n">
-        <v>86.28140540757842</v>
+        <v>86.28140540757846</v>
       </c>
       <c r="L8" t="n">
-        <v>86.38990632668417</v>
+        <v>86.38990632668413</v>
       </c>
       <c r="M8" t="n">
         <v>85.75957383271952</v>
       </c>
       <c r="N8" t="n">
-        <v>86.29501554654652</v>
+        <v>86.29501554654649</v>
       </c>
       <c r="O8" t="n">
-        <v>86.24430219574407</v>
+        <v>86.24430219574413</v>
       </c>
       <c r="P8" t="n">
-        <v>85.24821217914095</v>
+        <v>85.24821217914089</v>
       </c>
       <c r="Q8" t="n">
-        <v>86.05973732736491</v>
+        <v>86.05973732736501</v>
       </c>
       <c r="R8" t="n">
-        <v>86.58452886396509</v>
+        <v>86.58452886396508</v>
       </c>
       <c r="S8" t="n">
         <v>86.37992244891899</v>
       </c>
       <c r="T8" t="n">
-        <v>86.81383333166379</v>
+        <v>86.8138333316637</v>
       </c>
       <c r="U8" t="n">
-        <v>86.27544889771882</v>
+        <v>86.27544889771875</v>
       </c>
       <c r="V8" t="n">
         <v>52.4156179070293</v>
       </c>
       <c r="W8" t="n">
-        <v>85.48437832265986</v>
+        <v>85.48437832265991</v>
       </c>
       <c r="X8" t="n">
-        <v>85.06849762053318</v>
+        <v>85.06849762053307</v>
       </c>
       <c r="Y8" t="n">
-        <v>83.13850495475126</v>
+        <v>83.13850495475117</v>
       </c>
       <c r="Z8" t="n">
         <v>86.29647575446724</v>
       </c>
       <c r="AA8" t="n">
-        <v>86.4392596209082</v>
+        <v>86.43925962090823</v>
       </c>
       <c r="AB8" t="n">
         <v>81.23493105824168</v>
